--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -32,7 +32,7 @@
     <t>Actualización:</t>
   </si>
   <si>
-    <t>7/3/2026, 7:47:19 p. m.</t>
+    <t>7/3/2026, 8:27:28 p. m.</t>
   </si>
   <si>
     <t>ACCESORIOS</t>
@@ -89,10 +89,10 @@
     <t>U. x Caja</t>
   </si>
   <si>
-    <t>Stock VES</t>
-  </si>
-  <si>
-    <t>Alerta</t>
+    <t>Stock</t>
+  </si>
+  <si>
+    <t>Estado</t>
   </si>
   <si>
     <t>79102</t>
@@ -104,7 +104,7 @@
     <t>BORRADOR BLANCO CHICO VINIFAN DISPLAY X 30 NEW</t>
   </si>
   <si>
-    <t>🔴</t>
+    <t>✗ AGOTADO</t>
   </si>
   <si>
     <t>79101</t>
@@ -113,7 +113,7 @@
     <t>BORRADOR BLANCO GRANDE VINIFAN DISPLAY X 20 NEW</t>
   </si>
   <si>
-    <t>🟢</t>
+    <t>✓ OK</t>
   </si>
   <si>
     <t>79112</t>
@@ -194,7 +194,7 @@
     <t>TAJADOR VINIFAN SIMPLE BUHO CON BORRADOR DISPLAY X16</t>
   </si>
   <si>
-    <t>🟡</t>
+    <t>⚠ BAJO</t>
   </si>
   <si>
     <t>79159</t>
@@ -6636,7 +6636,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -6654,6 +6654,22 @@
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFDC2626"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF065F46"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFD97706"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="6">
@@ -6696,7 +6712,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -6705,13 +6721,19 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -7184,13 +7206,12 @@
   <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7235,7 +7256,7 @@
       <c r="F2" s="5">
         <v>10869</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7258,7 +7279,7 @@
       <c r="F3" s="5">
         <v>12288</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7281,7 +7302,7 @@
       <c r="F4" s="5">
         <v>11433</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7304,7 +7325,7 @@
       <c r="F5" s="5">
         <v>3374</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7327,7 +7348,7 @@
       <c r="F6" s="5">
         <v>12286</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7350,7 +7371,7 @@
       <c r="F7" s="5">
         <v>1527</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7373,7 +7394,7 @@
       <c r="F8" s="5">
         <v>13274</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7396,7 +7417,7 @@
       <c r="F9" s="5">
         <v>2039</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7442,7 +7463,7 @@
       <c r="F11" s="5">
         <v>31</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7465,7 +7486,7 @@
       <c r="F12" s="5">
         <v>10</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7488,7 +7509,7 @@
       <c r="F13" s="5">
         <v>1737</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7511,7 +7532,7 @@
       <c r="F14" s="5">
         <v>16202</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7534,7 +7555,7 @@
       <c r="F15" s="5">
         <v>40069</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7557,7 +7578,7 @@
       <c r="F16" s="5">
         <v>2310</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7580,7 +7601,7 @@
       <c r="F17" s="5">
         <v>14034</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7603,7 +7624,7 @@
       <c r="F18" s="5">
         <v>854</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7626,7 +7647,7 @@
       <c r="F19" s="5">
         <v>14019</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7649,7 +7670,7 @@
       <c r="F20" s="5">
         <v>2954</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7672,7 +7693,7 @@
       <c r="F21" s="5">
         <v>47755</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7695,7 +7716,7 @@
       <c r="F22" s="5">
         <v>24084</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7718,7 +7739,7 @@
       <c r="F23" s="5">
         <v>1775</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7787,7 +7808,7 @@
       <c r="F26" s="5">
         <v>3104</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7833,7 +7854,7 @@
       <c r="F28" s="5">
         <v>24419</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7856,7 +7877,7 @@
       <c r="F29" s="5">
         <v>2569</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7902,7 +7923,7 @@
       <c r="F31" s="5">
         <v>1351</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7918,13 +7939,12 @@
   <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7969,7 +7989,7 @@
       <c r="F2" s="5">
         <v>39219</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7992,7 +8012,7 @@
       <c r="F3" s="5">
         <v>34348</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8015,7 +8035,7 @@
       <c r="F4" s="5">
         <v>22249</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8038,7 +8058,7 @@
       <c r="F5" s="5">
         <v>65701</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8061,7 +8081,7 @@
       <c r="F6" s="5">
         <v>94120</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8084,7 +8104,7 @@
       <c r="F7" s="5">
         <v>57680</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8107,7 +8127,7 @@
       <c r="F8" s="5">
         <v>1979</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8130,7 +8150,7 @@
       <c r="F9" s="5">
         <v>22934</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8150,10 +8170,10 @@
       <c r="E10">
         <v>36</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="7">
         <v>2</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -8199,7 +8219,7 @@
       <c r="F12" s="5">
         <v>38568</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8222,7 +8242,7 @@
       <c r="F13" s="5">
         <v>92920</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8245,7 +8265,7 @@
       <c r="F14" s="5">
         <v>91858</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8268,7 +8288,7 @@
       <c r="F15" s="5">
         <v>12961</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8291,7 +8311,7 @@
       <c r="F16" s="5">
         <v>16266</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8311,10 +8331,10 @@
       <c r="E17">
         <v>72</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="7">
         <v>1</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -8337,7 +8357,7 @@
       <c r="F18" s="5">
         <v>12708</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8360,7 +8380,7 @@
       <c r="F19" s="5">
         <v>2515</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8383,7 +8403,7 @@
       <c r="F20" s="5">
         <v>14675</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8403,10 +8423,10 @@
       <c r="E21">
         <v>144</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="7">
         <v>6</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -8429,7 +8449,7 @@
       <c r="F22" s="5">
         <v>13954</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8445,13 +8465,12 @@
   <dimension ref="A1:G191"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8496,7 +8515,7 @@
       <c r="F2" s="5">
         <v>243</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8519,7 +8538,7 @@
       <c r="F3" s="5">
         <v>2050</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8542,7 +8561,7 @@
       <c r="F4" s="5">
         <v>15</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8565,7 +8584,7 @@
       <c r="F5" s="5">
         <v>3800</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8588,7 +8607,7 @@
       <c r="F6" s="5">
         <v>606</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8634,7 +8653,7 @@
       <c r="F8" s="5">
         <v>4742</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8657,7 +8676,7 @@
       <c r="F9" s="5">
         <v>1463</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8680,7 +8699,7 @@
       <c r="F10" s="5">
         <v>1496</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8703,7 +8722,7 @@
       <c r="F11" s="5">
         <v>180</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8726,7 +8745,7 @@
       <c r="F12" s="5">
         <v>1426</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8749,7 +8768,7 @@
       <c r="F13" s="5">
         <v>168</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8772,7 +8791,7 @@
       <c r="F14" s="5">
         <v>182</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8792,10 +8811,10 @@
       <c r="E15">
         <v>36</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="7">
         <v>1</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -8818,7 +8837,7 @@
       <c r="F16" s="5">
         <v>1012</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8841,7 +8860,7 @@
       <c r="F17" s="5">
         <v>76</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8887,7 +8906,7 @@
       <c r="F19" s="5">
         <v>3828</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8910,7 +8929,7 @@
       <c r="F20" s="5">
         <v>3206</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8933,7 +8952,7 @@
       <c r="F21" s="5">
         <v>8229</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8956,7 +8975,7 @@
       <c r="F22" s="5">
         <v>1330</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9045,10 +9064,10 @@
       <c r="E26">
         <v>48</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F26" s="7">
         <v>1</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -9091,10 +9110,10 @@
       <c r="E28">
         <v>36</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F28" s="7">
         <v>1</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -9117,7 +9136,7 @@
       <c r="F29" s="5">
         <v>3043</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9186,7 +9205,7 @@
       <c r="F32" s="5">
         <v>3505</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="G32" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9209,7 +9228,7 @@
       <c r="F33" s="5">
         <v>2922</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="G33" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9232,7 +9251,7 @@
       <c r="F34" s="5">
         <v>263</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="G34" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9255,7 +9274,7 @@
       <c r="F35" s="5">
         <v>518</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G35" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9278,7 +9297,7 @@
       <c r="F36" s="5">
         <v>873</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="G36" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9301,7 +9320,7 @@
       <c r="F37" s="5">
         <v>7641</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="G37" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9324,7 +9343,7 @@
       <c r="F38" s="5">
         <v>1483</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="G38" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9390,10 +9409,10 @@
       <c r="E41">
         <v>48</v>
       </c>
-      <c r="F41" s="6">
+      <c r="F41" s="7">
         <v>5</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="G41" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -9416,7 +9435,7 @@
       <c r="F42" s="5">
         <v>39</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="G42" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9462,7 +9481,7 @@
       <c r="F44" s="5">
         <v>6524</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="G44" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9531,7 +9550,7 @@
       <c r="F47" s="5">
         <v>11965</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="G47" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9574,10 +9593,10 @@
       <c r="E49">
         <v>48</v>
       </c>
-      <c r="F49" s="6">
+      <c r="F49" s="7">
         <v>6</v>
       </c>
-      <c r="G49" s="4" t="s">
+      <c r="G49" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -9600,7 +9619,7 @@
       <c r="F50" s="5">
         <v>5578</v>
       </c>
-      <c r="G50" s="4" t="s">
+      <c r="G50" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9646,7 +9665,7 @@
       <c r="F52" s="5">
         <v>117</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="G52" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9666,10 +9685,10 @@
       <c r="E53">
         <v>48</v>
       </c>
-      <c r="F53" s="6">
+      <c r="F53" s="7">
         <v>1</v>
       </c>
-      <c r="G53" s="4" t="s">
+      <c r="G53" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -9692,7 +9711,7 @@
       <c r="F54" s="5">
         <v>162</v>
       </c>
-      <c r="G54" s="4" t="s">
+      <c r="G54" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9715,7 +9734,7 @@
       <c r="F55" s="5">
         <v>1955</v>
       </c>
-      <c r="G55" s="4" t="s">
+      <c r="G55" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9738,7 +9757,7 @@
       <c r="F56" s="5">
         <v>196</v>
       </c>
-      <c r="G56" s="4" t="s">
+      <c r="G56" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9761,7 +9780,7 @@
       <c r="F57" s="5">
         <v>2190</v>
       </c>
-      <c r="G57" s="4" t="s">
+      <c r="G57" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9830,7 +9849,7 @@
       <c r="F60" s="5">
         <v>1377</v>
       </c>
-      <c r="G60" s="4" t="s">
+      <c r="G60" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9876,7 +9895,7 @@
       <c r="F62" s="5">
         <v>915</v>
       </c>
-      <c r="G62" s="4" t="s">
+      <c r="G62" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9899,7 +9918,7 @@
       <c r="F63" s="5">
         <v>798</v>
       </c>
-      <c r="G63" s="4" t="s">
+      <c r="G63" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9922,7 +9941,7 @@
       <c r="F64" s="5">
         <v>418</v>
       </c>
-      <c r="G64" s="4" t="s">
+      <c r="G64" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9945,7 +9964,7 @@
       <c r="F65" s="5">
         <v>1218</v>
       </c>
-      <c r="G65" s="4" t="s">
+      <c r="G65" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9968,7 +9987,7 @@
       <c r="F66" s="5">
         <v>5188</v>
       </c>
-      <c r="G66" s="4" t="s">
+      <c r="G66" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -9991,7 +10010,7 @@
       <c r="F67" s="5">
         <v>1226</v>
       </c>
-      <c r="G67" s="4" t="s">
+      <c r="G67" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10014,7 +10033,7 @@
       <c r="F68" s="5">
         <v>2119</v>
       </c>
-      <c r="G68" s="4" t="s">
+      <c r="G68" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10037,7 +10056,7 @@
       <c r="F69" s="5">
         <v>1118</v>
       </c>
-      <c r="G69" s="4" t="s">
+      <c r="G69" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10060,7 +10079,7 @@
       <c r="F70" s="5">
         <v>4180</v>
       </c>
-      <c r="G70" s="4" t="s">
+      <c r="G70" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10083,7 +10102,7 @@
       <c r="F71" s="5">
         <v>5085</v>
       </c>
-      <c r="G71" s="4" t="s">
+      <c r="G71" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10129,7 +10148,7 @@
       <c r="F73" s="5">
         <v>13274</v>
       </c>
-      <c r="G73" s="4" t="s">
+      <c r="G73" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10152,7 +10171,7 @@
       <c r="F74" s="5">
         <v>1302</v>
       </c>
-      <c r="G74" s="4" t="s">
+      <c r="G74" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10175,7 +10194,7 @@
       <c r="F75" s="5">
         <v>4399</v>
       </c>
-      <c r="G75" s="4" t="s">
+      <c r="G75" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10198,7 +10217,7 @@
       <c r="F76" s="5">
         <v>8596</v>
       </c>
-      <c r="G76" s="4" t="s">
+      <c r="G76" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10221,7 +10240,7 @@
       <c r="F77" s="5">
         <v>3977</v>
       </c>
-      <c r="G77" s="4" t="s">
+      <c r="G77" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10244,7 +10263,7 @@
       <c r="F78" s="5">
         <v>6465</v>
       </c>
-      <c r="G78" s="4" t="s">
+      <c r="G78" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10267,7 +10286,7 @@
       <c r="F79" s="5">
         <v>5202</v>
       </c>
-      <c r="G79" s="4" t="s">
+      <c r="G79" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10290,7 +10309,7 @@
       <c r="F80" s="5">
         <v>18</v>
       </c>
-      <c r="G80" s="4" t="s">
+      <c r="G80" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10310,10 +10329,10 @@
       <c r="E81">
         <v>60</v>
       </c>
-      <c r="F81" s="6">
+      <c r="F81" s="7">
         <v>5</v>
       </c>
-      <c r="G81" s="4" t="s">
+      <c r="G81" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -10336,7 +10355,7 @@
       <c r="F82" s="5">
         <v>1124</v>
       </c>
-      <c r="G82" s="4" t="s">
+      <c r="G82" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10359,7 +10378,7 @@
       <c r="F83" s="5">
         <v>1037</v>
       </c>
-      <c r="G83" s="4" t="s">
+      <c r="G83" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10405,7 +10424,7 @@
       <c r="F85" s="5">
         <v>154</v>
       </c>
-      <c r="G85" s="4" t="s">
+      <c r="G85" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10428,7 +10447,7 @@
       <c r="F86" s="5">
         <v>333</v>
       </c>
-      <c r="G86" s="4" t="s">
+      <c r="G86" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10451,7 +10470,7 @@
       <c r="F87" s="5">
         <v>1531</v>
       </c>
-      <c r="G87" s="4" t="s">
+      <c r="G87" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10520,7 +10539,7 @@
       <c r="F90" s="5">
         <v>734</v>
       </c>
-      <c r="G90" s="4" t="s">
+      <c r="G90" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10543,7 +10562,7 @@
       <c r="F91" s="5">
         <v>1518</v>
       </c>
-      <c r="G91" s="4" t="s">
+      <c r="G91" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10566,7 +10585,7 @@
       <c r="F92" s="5">
         <v>1372</v>
       </c>
-      <c r="G92" s="4" t="s">
+      <c r="G92" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10589,7 +10608,7 @@
       <c r="F93" s="5">
         <v>1251</v>
       </c>
-      <c r="G93" s="4" t="s">
+      <c r="G93" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10612,7 +10631,7 @@
       <c r="F94" s="5">
         <v>1822</v>
       </c>
-      <c r="G94" s="4" t="s">
+      <c r="G94" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10658,7 +10677,7 @@
       <c r="F96" s="5">
         <v>2485</v>
       </c>
-      <c r="G96" s="4" t="s">
+      <c r="G96" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10681,7 +10700,7 @@
       <c r="F97" s="5">
         <v>5025</v>
       </c>
-      <c r="G97" s="4" t="s">
+      <c r="G97" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10704,7 +10723,7 @@
       <c r="F98" s="5">
         <v>3434</v>
       </c>
-      <c r="G98" s="4" t="s">
+      <c r="G98" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10727,7 +10746,7 @@
       <c r="F99" s="5">
         <v>3915</v>
       </c>
-      <c r="G99" s="4" t="s">
+      <c r="G99" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10750,7 +10769,7 @@
       <c r="F100" s="5">
         <v>1544</v>
       </c>
-      <c r="G100" s="4" t="s">
+      <c r="G100" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10773,7 +10792,7 @@
       <c r="F101" s="5">
         <v>5802</v>
       </c>
-      <c r="G101" s="4" t="s">
+      <c r="G101" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10796,7 +10815,7 @@
       <c r="F102" s="5">
         <v>3253</v>
       </c>
-      <c r="G102" s="4" t="s">
+      <c r="G102" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10819,7 +10838,7 @@
       <c r="F103" s="5">
         <v>1816</v>
       </c>
-      <c r="G103" s="4" t="s">
+      <c r="G103" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10842,7 +10861,7 @@
       <c r="F104" s="5">
         <v>368</v>
       </c>
-      <c r="G104" s="4" t="s">
+      <c r="G104" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10888,7 +10907,7 @@
       <c r="F106" s="5">
         <v>852</v>
       </c>
-      <c r="G106" s="4" t="s">
+      <c r="G106" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10911,7 +10930,7 @@
       <c r="F107" s="5">
         <v>5594</v>
       </c>
-      <c r="G107" s="4" t="s">
+      <c r="G107" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10934,7 +10953,7 @@
       <c r="F108" s="5">
         <v>1998</v>
       </c>
-      <c r="G108" s="4" t="s">
+      <c r="G108" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10957,7 +10976,7 @@
       <c r="F109" s="5">
         <v>1725</v>
       </c>
-      <c r="G109" s="4" t="s">
+      <c r="G109" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -10980,7 +10999,7 @@
       <c r="F110" s="5">
         <v>1887</v>
       </c>
-      <c r="G110" s="4" t="s">
+      <c r="G110" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11003,7 +11022,7 @@
       <c r="F111" s="5">
         <v>6130</v>
       </c>
-      <c r="G111" s="4" t="s">
+      <c r="G111" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11026,7 +11045,7 @@
       <c r="F112" s="5">
         <v>7112</v>
       </c>
-      <c r="G112" s="4" t="s">
+      <c r="G112" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11049,7 +11068,7 @@
       <c r="F113" s="5">
         <v>6610</v>
       </c>
-      <c r="G113" s="4" t="s">
+      <c r="G113" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11072,7 +11091,7 @@
       <c r="F114" s="5">
         <v>11151</v>
       </c>
-      <c r="G114" s="4" t="s">
+      <c r="G114" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11095,7 +11114,7 @@
       <c r="F115" s="5">
         <v>239</v>
       </c>
-      <c r="G115" s="4" t="s">
+      <c r="G115" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11118,7 +11137,7 @@
       <c r="F116" s="5">
         <v>85</v>
       </c>
-      <c r="G116" s="4" t="s">
+      <c r="G116" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11141,7 +11160,7 @@
       <c r="F117" s="5">
         <v>273</v>
       </c>
-      <c r="G117" s="4" t="s">
+      <c r="G117" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11164,7 +11183,7 @@
       <c r="F118" s="5">
         <v>272</v>
       </c>
-      <c r="G118" s="4" t="s">
+      <c r="G118" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11210,7 +11229,7 @@
       <c r="F120" s="5">
         <v>261</v>
       </c>
-      <c r="G120" s="4" t="s">
+      <c r="G120" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11256,7 +11275,7 @@
       <c r="F122" s="5">
         <v>2925</v>
       </c>
-      <c r="G122" s="4" t="s">
+      <c r="G122" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11279,7 +11298,7 @@
       <c r="F123" s="5">
         <v>10</v>
       </c>
-      <c r="G123" s="4" t="s">
+      <c r="G123" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11302,7 +11321,7 @@
       <c r="F124" s="5">
         <v>2515</v>
       </c>
-      <c r="G124" s="4" t="s">
+      <c r="G124" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11325,7 +11344,7 @@
       <c r="F125" s="5">
         <v>969</v>
       </c>
-      <c r="G125" s="4" t="s">
+      <c r="G125" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11348,7 +11367,7 @@
       <c r="F126" s="5">
         <v>2200</v>
       </c>
-      <c r="G126" s="4" t="s">
+      <c r="G126" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11371,7 +11390,7 @@
       <c r="F127" s="5">
         <v>155</v>
       </c>
-      <c r="G127" s="4" t="s">
+      <c r="G127" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11394,7 +11413,7 @@
       <c r="F128" s="5">
         <v>519</v>
       </c>
-      <c r="G128" s="4" t="s">
+      <c r="G128" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11417,7 +11436,7 @@
       <c r="F129" s="5">
         <v>1067</v>
       </c>
-      <c r="G129" s="4" t="s">
+      <c r="G129" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11440,7 +11459,7 @@
       <c r="F130" s="5">
         <v>884</v>
       </c>
-      <c r="G130" s="4" t="s">
+      <c r="G130" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11463,7 +11482,7 @@
       <c r="F131" s="5">
         <v>55</v>
       </c>
-      <c r="G131" s="4" t="s">
+      <c r="G131" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11486,7 +11505,7 @@
       <c r="F132" s="5">
         <v>233</v>
       </c>
-      <c r="G132" s="4" t="s">
+      <c r="G132" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11509,7 +11528,7 @@
       <c r="F133" s="5">
         <v>6592</v>
       </c>
-      <c r="G133" s="4" t="s">
+      <c r="G133" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11532,7 +11551,7 @@
       <c r="F134" s="5">
         <v>1017</v>
       </c>
-      <c r="G134" s="4" t="s">
+      <c r="G134" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11552,10 +11571,10 @@
       <c r="E135">
         <v>120</v>
       </c>
-      <c r="F135" s="6">
+      <c r="F135" s="7">
         <v>2</v>
       </c>
-      <c r="G135" s="4" t="s">
+      <c r="G135" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -11578,7 +11597,7 @@
       <c r="F136" s="5">
         <v>4015</v>
       </c>
-      <c r="G136" s="4" t="s">
+      <c r="G136" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11601,7 +11620,7 @@
       <c r="F137" s="5">
         <v>1904</v>
       </c>
-      <c r="G137" s="4" t="s">
+      <c r="G137" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11624,7 +11643,7 @@
       <c r="F138" s="5">
         <v>10</v>
       </c>
-      <c r="G138" s="4" t="s">
+      <c r="G138" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11647,7 +11666,7 @@
       <c r="F139" s="5">
         <v>4463</v>
       </c>
-      <c r="G139" s="4" t="s">
+      <c r="G139" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11667,10 +11686,10 @@
       <c r="E140">
         <v>120</v>
       </c>
-      <c r="F140" s="6">
+      <c r="F140" s="7">
         <v>3</v>
       </c>
-      <c r="G140" s="4" t="s">
+      <c r="G140" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -11693,7 +11712,7 @@
       <c r="F141" s="5">
         <v>4217</v>
       </c>
-      <c r="G141" s="4" t="s">
+      <c r="G141" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11716,7 +11735,7 @@
       <c r="F142" s="5">
         <v>3364</v>
       </c>
-      <c r="G142" s="4" t="s">
+      <c r="G142" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11739,7 +11758,7 @@
       <c r="F143" s="5">
         <v>514</v>
       </c>
-      <c r="G143" s="4" t="s">
+      <c r="G143" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11782,10 +11801,10 @@
       <c r="E145">
         <v>120</v>
       </c>
-      <c r="F145" s="6">
+      <c r="F145" s="7">
         <v>1</v>
       </c>
-      <c r="G145" s="4" t="s">
+      <c r="G145" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -11808,7 +11827,7 @@
       <c r="F146" s="5">
         <v>752</v>
       </c>
-      <c r="G146" s="4" t="s">
+      <c r="G146" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11831,7 +11850,7 @@
       <c r="F147" s="5">
         <v>1964</v>
       </c>
-      <c r="G147" s="4" t="s">
+      <c r="G147" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11854,7 +11873,7 @@
       <c r="F148" s="5">
         <v>397</v>
       </c>
-      <c r="G148" s="4" t="s">
+      <c r="G148" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11874,10 +11893,10 @@
       <c r="E149">
         <v>120</v>
       </c>
-      <c r="F149" s="6">
+      <c r="F149" s="7">
         <v>1</v>
       </c>
-      <c r="G149" s="4" t="s">
+      <c r="G149" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -11900,7 +11919,7 @@
       <c r="F150" s="5">
         <v>386</v>
       </c>
-      <c r="G150" s="4" t="s">
+      <c r="G150" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11923,7 +11942,7 @@
       <c r="F151" s="5">
         <v>2007</v>
       </c>
-      <c r="G151" s="4" t="s">
+      <c r="G151" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -11943,10 +11962,10 @@
       <c r="E152">
         <v>120</v>
       </c>
-      <c r="F152" s="6">
+      <c r="F152" s="7">
         <v>2</v>
       </c>
-      <c r="G152" s="4" t="s">
+      <c r="G152" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -11992,7 +12011,7 @@
       <c r="F154" s="5">
         <v>3277</v>
       </c>
-      <c r="G154" s="4" t="s">
+      <c r="G154" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -12015,7 +12034,7 @@
       <c r="F155" s="5">
         <v>908</v>
       </c>
-      <c r="G155" s="4" t="s">
+      <c r="G155" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -12038,7 +12057,7 @@
       <c r="F156" s="5">
         <v>306</v>
       </c>
-      <c r="G156" s="4" t="s">
+      <c r="G156" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -12061,7 +12080,7 @@
       <c r="F157" s="5">
         <v>3114</v>
       </c>
-      <c r="G157" s="4" t="s">
+      <c r="G157" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -12084,7 +12103,7 @@
       <c r="F158" s="5">
         <v>1101</v>
       </c>
-      <c r="G158" s="4" t="s">
+      <c r="G158" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -12107,7 +12126,7 @@
       <c r="F159" s="5">
         <v>3978</v>
       </c>
-      <c r="G159" s="4" t="s">
+      <c r="G159" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -12127,10 +12146,10 @@
       <c r="E160">
         <v>120</v>
       </c>
-      <c r="F160" s="6">
+      <c r="F160" s="7">
         <v>6</v>
       </c>
-      <c r="G160" s="4" t="s">
+      <c r="G160" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -12153,7 +12172,7 @@
       <c r="F161" s="5">
         <v>1926</v>
       </c>
-      <c r="G161" s="4" t="s">
+      <c r="G161" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -12176,7 +12195,7 @@
       <c r="F162" s="5">
         <v>4672</v>
       </c>
-      <c r="G162" s="4" t="s">
+      <c r="G162" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -12199,7 +12218,7 @@
       <c r="F163" s="5">
         <v>4562</v>
       </c>
-      <c r="G163" s="4" t="s">
+      <c r="G163" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -12222,7 +12241,7 @@
       <c r="F164" s="5">
         <v>264</v>
       </c>
-      <c r="G164" s="4" t="s">
+      <c r="G164" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -12245,7 +12264,7 @@
       <c r="F165" s="5">
         <v>1260</v>
       </c>
-      <c r="G165" s="4" t="s">
+      <c r="G165" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -12268,7 +12287,7 @@
       <c r="F166" s="5">
         <v>3735</v>
       </c>
-      <c r="G166" s="4" t="s">
+      <c r="G166" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -12291,7 +12310,7 @@
       <c r="F167" s="5">
         <v>764</v>
       </c>
-      <c r="G167" s="4" t="s">
+      <c r="G167" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -12314,7 +12333,7 @@
       <c r="F168" s="5">
         <v>157</v>
       </c>
-      <c r="G168" s="4" t="s">
+      <c r="G168" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -12337,7 +12356,7 @@
       <c r="F169" s="5">
         <v>703</v>
       </c>
-      <c r="G169" s="4" t="s">
+      <c r="G169" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -12383,7 +12402,7 @@
       <c r="F171" s="5">
         <v>7702</v>
       </c>
-      <c r="G171" s="4" t="s">
+      <c r="G171" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -12406,7 +12425,7 @@
       <c r="F172" s="5">
         <v>2089</v>
       </c>
-      <c r="G172" s="4" t="s">
+      <c r="G172" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -12429,7 +12448,7 @@
       <c r="F173" s="5">
         <v>232</v>
       </c>
-      <c r="G173" s="4" t="s">
+      <c r="G173" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -12452,7 +12471,7 @@
       <c r="F174" s="5">
         <v>147</v>
       </c>
-      <c r="G174" s="4" t="s">
+      <c r="G174" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -12475,7 +12494,7 @@
       <c r="F175" s="5">
         <v>22</v>
       </c>
-      <c r="G175" s="4" t="s">
+      <c r="G175" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -12544,7 +12563,7 @@
       <c r="F178" s="5">
         <v>163</v>
       </c>
-      <c r="G178" s="4" t="s">
+      <c r="G178" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -12564,10 +12583,10 @@
       <c r="E179">
         <v>12</v>
       </c>
-      <c r="F179" s="6">
+      <c r="F179" s="7">
         <v>1</v>
       </c>
-      <c r="G179" s="4" t="s">
+      <c r="G179" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -12636,7 +12655,7 @@
       <c r="F182" s="5">
         <v>211</v>
       </c>
-      <c r="G182" s="4" t="s">
+      <c r="G182" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -12659,7 +12678,7 @@
       <c r="F183" s="5">
         <v>53</v>
       </c>
-      <c r="G183" s="4" t="s">
+      <c r="G183" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -12682,7 +12701,7 @@
       <c r="F184" s="5">
         <v>11</v>
       </c>
-      <c r="G184" s="4" t="s">
+      <c r="G184" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -12705,7 +12724,7 @@
       <c r="F185" s="5">
         <v>76950</v>
       </c>
-      <c r="G185" s="4" t="s">
+      <c r="G185" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -12728,7 +12747,7 @@
       <c r="F186" s="5">
         <v>72165</v>
       </c>
-      <c r="G186" s="4" t="s">
+      <c r="G186" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -12751,7 +12770,7 @@
       <c r="F187" s="5">
         <v>3620</v>
       </c>
-      <c r="G187" s="4" t="s">
+      <c r="G187" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -12774,7 +12793,7 @@
       <c r="F188" s="5">
         <v>1816</v>
       </c>
-      <c r="G188" s="4" t="s">
+      <c r="G188" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -12797,7 +12816,7 @@
       <c r="F189" s="5">
         <v>8964</v>
       </c>
-      <c r="G189" s="4" t="s">
+      <c r="G189" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -12843,7 +12862,7 @@
       <c r="F191" s="5">
         <v>8040</v>
       </c>
-      <c r="G191" s="4" t="s">
+      <c r="G191" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -12859,13 +12878,12 @@
   <dimension ref="A1:G77"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -12910,7 +12928,7 @@
       <c r="F2" s="5">
         <v>25237</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -12979,7 +12997,7 @@
       <c r="F5" s="5">
         <v>2283</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13002,7 +13020,7 @@
       <c r="F6" s="5">
         <v>115</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13025,7 +13043,7 @@
       <c r="F7" s="5">
         <v>104351</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13048,7 +13066,7 @@
       <c r="F8" s="5">
         <v>15582</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13094,7 +13112,7 @@
       <c r="F10" s="5">
         <v>2060</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13117,7 +13135,7 @@
       <c r="F11" s="5">
         <v>53217</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13140,7 +13158,7 @@
       <c r="F12" s="5">
         <v>16099</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13163,7 +13181,7 @@
       <c r="F13" s="5">
         <v>1939</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13186,7 +13204,7 @@
       <c r="F14" s="5">
         <v>10060</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13209,7 +13227,7 @@
       <c r="F15" s="5">
         <v>5472</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13232,7 +13250,7 @@
       <c r="F16" s="5">
         <v>15417</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13255,7 +13273,7 @@
       <c r="F17" s="5">
         <v>98197</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13278,7 +13296,7 @@
       <c r="F18" s="5">
         <v>8012</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13301,7 +13319,7 @@
       <c r="F19" s="5">
         <v>5063</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13370,7 +13388,7 @@
       <c r="F22" s="5">
         <v>4895</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13393,7 +13411,7 @@
       <c r="F23" s="5">
         <v>13509</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13416,7 +13434,7 @@
       <c r="F24" s="5">
         <v>12442</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13439,7 +13457,7 @@
       <c r="F25" s="5">
         <v>18308</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13462,7 +13480,7 @@
       <c r="F26" s="5">
         <v>32615</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13485,7 +13503,7 @@
       <c r="F27" s="5">
         <v>71458</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13508,7 +13526,7 @@
       <c r="F28" s="5">
         <v>32648</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13531,7 +13549,7 @@
       <c r="F29" s="5">
         <v>51222</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13554,7 +13572,7 @@
       <c r="F30" s="5">
         <v>34883</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G30" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13577,7 +13595,7 @@
       <c r="F31" s="5">
         <v>13091</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13600,7 +13618,7 @@
       <c r="F32" s="5">
         <v>11641</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="G32" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13623,7 +13641,7 @@
       <c r="F33" s="5">
         <v>7951</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="G33" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13646,7 +13664,7 @@
       <c r="F34" s="5">
         <v>48805</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="G34" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13669,7 +13687,7 @@
       <c r="F35" s="5">
         <v>2304</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G35" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13692,7 +13710,7 @@
       <c r="F36" s="5">
         <v>54994</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="G36" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13715,7 +13733,7 @@
       <c r="F37" s="5">
         <v>1469</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="G37" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13738,7 +13756,7 @@
       <c r="F38" s="5">
         <v>63</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="G38" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13761,7 +13779,7 @@
       <c r="F39" s="5">
         <v>6556</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="G39" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13784,7 +13802,7 @@
       <c r="F40" s="5">
         <v>40056</v>
       </c>
-      <c r="G40" s="4" t="s">
+      <c r="G40" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13807,7 +13825,7 @@
       <c r="F41" s="5">
         <v>2846</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="G41" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13830,7 +13848,7 @@
       <c r="F42" s="5">
         <v>981</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="G42" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13876,7 +13894,7 @@
       <c r="F44" s="5">
         <v>125</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="G44" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13899,7 +13917,7 @@
       <c r="F45" s="5">
         <v>25169</v>
       </c>
-      <c r="G45" s="4" t="s">
+      <c r="G45" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13922,7 +13940,7 @@
       <c r="F46" s="5">
         <v>2201</v>
       </c>
-      <c r="G46" s="4" t="s">
+      <c r="G46" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13945,7 +13963,7 @@
       <c r="F47" s="5">
         <v>8672</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="G47" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13968,7 +13986,7 @@
       <c r="F48" s="5">
         <v>49384</v>
       </c>
-      <c r="G48" s="4" t="s">
+      <c r="G48" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -13991,7 +14009,7 @@
       <c r="F49" s="5">
         <v>38451</v>
       </c>
-      <c r="G49" s="4" t="s">
+      <c r="G49" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -14014,7 +14032,7 @@
       <c r="F50" s="5">
         <v>10954</v>
       </c>
-      <c r="G50" s="4" t="s">
+      <c r="G50" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -14037,7 +14055,7 @@
       <c r="F51" s="5">
         <v>27538</v>
       </c>
-      <c r="G51" s="4" t="s">
+      <c r="G51" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -14060,7 +14078,7 @@
       <c r="F52" s="5">
         <v>11816</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="G52" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -14083,7 +14101,7 @@
       <c r="F53" s="5">
         <v>41666</v>
       </c>
-      <c r="G53" s="4" t="s">
+      <c r="G53" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -14106,7 +14124,7 @@
       <c r="F54" s="5">
         <v>43030</v>
       </c>
-      <c r="G54" s="4" t="s">
+      <c r="G54" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -14129,7 +14147,7 @@
       <c r="F55" s="5">
         <v>11280</v>
       </c>
-      <c r="G55" s="4" t="s">
+      <c r="G55" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -14152,7 +14170,7 @@
       <c r="F56" s="5">
         <v>33274</v>
       </c>
-      <c r="G56" s="4" t="s">
+      <c r="G56" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -14175,7 +14193,7 @@
       <c r="F57" s="5">
         <v>34223</v>
       </c>
-      <c r="G57" s="4" t="s">
+      <c r="G57" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -14198,7 +14216,7 @@
       <c r="F58" s="5">
         <v>37101</v>
       </c>
-      <c r="G58" s="4" t="s">
+      <c r="G58" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -14221,7 +14239,7 @@
       <c r="F59" s="5">
         <v>124</v>
       </c>
-      <c r="G59" s="4" t="s">
+      <c r="G59" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -14244,7 +14262,7 @@
       <c r="F60" s="5">
         <v>8941</v>
       </c>
-      <c r="G60" s="4" t="s">
+      <c r="G60" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -14264,10 +14282,10 @@
       <c r="E61">
         <v>12</v>
       </c>
-      <c r="F61" s="6">
+      <c r="F61" s="7">
         <v>1</v>
       </c>
-      <c r="G61" s="4" t="s">
+      <c r="G61" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -14310,10 +14328,10 @@
       <c r="E63">
         <v>12</v>
       </c>
-      <c r="F63" s="6">
+      <c r="F63" s="7">
         <v>4</v>
       </c>
-      <c r="G63" s="4" t="s">
+      <c r="G63" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -14333,10 +14351,10 @@
       <c r="E64">
         <v>12</v>
       </c>
-      <c r="F64" s="6">
+      <c r="F64" s="7">
         <v>9</v>
       </c>
-      <c r="G64" s="4" t="s">
+      <c r="G64" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -14356,10 +14374,10 @@
       <c r="E65">
         <v>12</v>
       </c>
-      <c r="F65" s="6">
+      <c r="F65" s="7">
         <v>3</v>
       </c>
-      <c r="G65" s="4" t="s">
+      <c r="G65" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -14382,7 +14400,7 @@
       <c r="F66" s="5">
         <v>604</v>
       </c>
-      <c r="G66" s="4" t="s">
+      <c r="G66" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -14520,7 +14538,7 @@
       <c r="F72" s="5">
         <v>6387</v>
       </c>
-      <c r="G72" s="4" t="s">
+      <c r="G72" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -14543,7 +14561,7 @@
       <c r="F73" s="5">
         <v>4504</v>
       </c>
-      <c r="G73" s="4" t="s">
+      <c r="G73" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -14566,7 +14584,7 @@
       <c r="F74" s="5">
         <v>10923</v>
       </c>
-      <c r="G74" s="4" t="s">
+      <c r="G74" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -14589,7 +14607,7 @@
       <c r="F75" s="5">
         <v>3061</v>
       </c>
-      <c r="G75" s="4" t="s">
+      <c r="G75" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -14612,7 +14630,7 @@
       <c r="F76" s="5">
         <v>5087</v>
       </c>
-      <c r="G76" s="4" t="s">
+      <c r="G76" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -14635,7 +14653,7 @@
       <c r="F77" s="5">
         <v>5923</v>
       </c>
-      <c r="G77" s="4" t="s">
+      <c r="G77" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -14651,13 +14669,12 @@
   <dimension ref="A1:G197"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -14702,7 +14719,7 @@
       <c r="F2" s="5">
         <v>6770</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -14725,7 +14742,7 @@
       <c r="F3" s="5">
         <v>27406</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -14748,7 +14765,7 @@
       <c r="F4" s="5">
         <v>7881</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -14771,7 +14788,7 @@
       <c r="F5" s="5">
         <v>20889</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -14794,7 +14811,7 @@
       <c r="F6" s="5">
         <v>36483</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -14817,7 +14834,7 @@
       <c r="F7" s="5">
         <v>1031</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -14840,7 +14857,7 @@
       <c r="F8" s="5">
         <v>268</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -14863,7 +14880,7 @@
       <c r="F9" s="5">
         <v>253</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -14886,7 +14903,7 @@
       <c r="F10" s="5">
         <v>59</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -14932,7 +14949,7 @@
       <c r="F12" s="5">
         <v>132</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -14955,7 +14972,7 @@
       <c r="F13" s="5">
         <v>191</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -14978,7 +14995,7 @@
       <c r="F14" s="5">
         <v>189</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15001,7 +15018,7 @@
       <c r="F15" s="5">
         <v>84</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15024,7 +15041,7 @@
       <c r="F16" s="5">
         <v>692</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15047,7 +15064,7 @@
       <c r="F17" s="5">
         <v>257</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15070,7 +15087,7 @@
       <c r="F18" s="5">
         <v>983</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15093,7 +15110,7 @@
       <c r="F19" s="5">
         <v>195</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15116,7 +15133,7 @@
       <c r="F20" s="5">
         <v>75</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15139,7 +15156,7 @@
       <c r="F21" s="5">
         <v>439</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15162,7 +15179,7 @@
       <c r="F22" s="5">
         <v>2053</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15182,10 +15199,10 @@
       <c r="E23">
         <v>60</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="7">
         <v>3</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -15208,7 +15225,7 @@
       <c r="F24" s="5">
         <v>113</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15231,7 +15248,7 @@
       <c r="F25" s="5">
         <v>348</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15254,7 +15271,7 @@
       <c r="F26" s="5">
         <v>123</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15277,7 +15294,7 @@
       <c r="F27" s="5">
         <v>160</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15300,7 +15317,7 @@
       <c r="F28" s="5">
         <v>9252</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15323,7 +15340,7 @@
       <c r="F29" s="5">
         <v>94</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15346,7 +15363,7 @@
       <c r="F30" s="5">
         <v>56</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G30" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15369,7 +15386,7 @@
       <c r="F31" s="5">
         <v>3120</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15392,7 +15409,7 @@
       <c r="F32" s="5">
         <v>1445</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="G32" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15438,7 +15455,7 @@
       <c r="F34" s="5">
         <v>907</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="G34" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15484,7 +15501,7 @@
       <c r="F36" s="5">
         <v>118</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="G36" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15507,7 +15524,7 @@
       <c r="F37" s="5">
         <v>944</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="G37" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15530,7 +15547,7 @@
       <c r="F38" s="5">
         <v>123</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="G38" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15553,7 +15570,7 @@
       <c r="F39" s="5">
         <v>278</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="G39" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15576,7 +15593,7 @@
       <c r="F40" s="5">
         <v>245</v>
       </c>
-      <c r="G40" s="4" t="s">
+      <c r="G40" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15599,7 +15616,7 @@
       <c r="F41" s="5">
         <v>107</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="G41" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15622,7 +15639,7 @@
       <c r="F42" s="5">
         <v>273</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="G42" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15645,7 +15662,7 @@
       <c r="F43" s="5">
         <v>2865</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="G43" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15668,7 +15685,7 @@
       <c r="F44" s="5">
         <v>1090</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="G44" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15691,7 +15708,7 @@
       <c r="F45" s="5">
         <v>163</v>
       </c>
-      <c r="G45" s="4" t="s">
+      <c r="G45" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15714,7 +15731,7 @@
       <c r="F46" s="5">
         <v>1475</v>
       </c>
-      <c r="G46" s="4" t="s">
+      <c r="G46" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15737,7 +15754,7 @@
       <c r="F47" s="5">
         <v>164</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="G47" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15760,7 +15777,7 @@
       <c r="F48" s="5">
         <v>140</v>
       </c>
-      <c r="G48" s="4" t="s">
+      <c r="G48" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15783,7 +15800,7 @@
       <c r="F49" s="5">
         <v>261</v>
       </c>
-      <c r="G49" s="4" t="s">
+      <c r="G49" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15806,7 +15823,7 @@
       <c r="F50" s="5">
         <v>291</v>
       </c>
-      <c r="G50" s="4" t="s">
+      <c r="G50" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15829,7 +15846,7 @@
       <c r="F51" s="5">
         <v>10</v>
       </c>
-      <c r="G51" s="4" t="s">
+      <c r="G51" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15852,7 +15869,7 @@
       <c r="F52" s="5">
         <v>82</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="G52" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15875,7 +15892,7 @@
       <c r="F53" s="5">
         <v>27</v>
       </c>
-      <c r="G53" s="4" t="s">
+      <c r="G53" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15898,7 +15915,7 @@
       <c r="F54" s="5">
         <v>2462</v>
       </c>
-      <c r="G54" s="4" t="s">
+      <c r="G54" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15921,7 +15938,7 @@
       <c r="F55" s="5">
         <v>208</v>
       </c>
-      <c r="G55" s="4" t="s">
+      <c r="G55" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15967,7 +15984,7 @@
       <c r="F57" s="5">
         <v>4873</v>
       </c>
-      <c r="G57" s="4" t="s">
+      <c r="G57" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -15990,7 +16007,7 @@
       <c r="F58" s="5">
         <v>201</v>
       </c>
-      <c r="G58" s="4" t="s">
+      <c r="G58" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -16059,7 +16076,7 @@
       <c r="F61" s="5">
         <v>300</v>
       </c>
-      <c r="G61" s="4" t="s">
+      <c r="G61" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -16082,7 +16099,7 @@
       <c r="F62" s="5">
         <v>198</v>
       </c>
-      <c r="G62" s="4" t="s">
+      <c r="G62" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -16105,7 +16122,7 @@
       <c r="F63" s="5">
         <v>7884</v>
       </c>
-      <c r="G63" s="4" t="s">
+      <c r="G63" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -16128,7 +16145,7 @@
       <c r="F64" s="5">
         <v>513</v>
       </c>
-      <c r="G64" s="4" t="s">
+      <c r="G64" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -16151,7 +16168,7 @@
       <c r="F65" s="5">
         <v>65</v>
       </c>
-      <c r="G65" s="4" t="s">
+      <c r="G65" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -16174,7 +16191,7 @@
       <c r="F66" s="5">
         <v>69</v>
       </c>
-      <c r="G66" s="4" t="s">
+      <c r="G66" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -16220,7 +16237,7 @@
       <c r="F68" s="5">
         <v>55</v>
       </c>
-      <c r="G68" s="4" t="s">
+      <c r="G68" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -16243,7 +16260,7 @@
       <c r="F69" s="5">
         <v>4170</v>
       </c>
-      <c r="G69" s="4" t="s">
+      <c r="G69" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -16266,7 +16283,7 @@
       <c r="F70" s="5">
         <v>130</v>
       </c>
-      <c r="G70" s="4" t="s">
+      <c r="G70" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -16312,7 +16329,7 @@
       <c r="F72" s="5">
         <v>412</v>
       </c>
-      <c r="G72" s="4" t="s">
+      <c r="G72" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -16335,7 +16352,7 @@
       <c r="F73" s="5">
         <v>500</v>
       </c>
-      <c r="G73" s="4" t="s">
+      <c r="G73" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -16358,7 +16375,7 @@
       <c r="F74" s="5">
         <v>1529</v>
       </c>
-      <c r="G74" s="4" t="s">
+      <c r="G74" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -16381,7 +16398,7 @@
       <c r="F75" s="5">
         <v>4001</v>
       </c>
-      <c r="G75" s="4" t="s">
+      <c r="G75" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -16427,7 +16444,7 @@
       <c r="F77" s="5">
         <v>539</v>
       </c>
-      <c r="G77" s="4" t="s">
+      <c r="G77" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -16450,7 +16467,7 @@
       <c r="F78" s="5">
         <v>114</v>
       </c>
-      <c r="G78" s="4" t="s">
+      <c r="G78" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -16470,10 +16487,10 @@
       <c r="E79">
         <v>120</v>
       </c>
-      <c r="F79" s="6">
+      <c r="F79" s="7">
         <v>4</v>
       </c>
-      <c r="G79" s="4" t="s">
+      <c r="G79" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -16496,7 +16513,7 @@
       <c r="F80" s="5">
         <v>12</v>
       </c>
-      <c r="G80" s="4" t="s">
+      <c r="G80" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -16519,7 +16536,7 @@
       <c r="F81" s="5">
         <v>469</v>
       </c>
-      <c r="G81" s="4" t="s">
+      <c r="G81" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -16542,7 +16559,7 @@
       <c r="F82" s="5">
         <v>2766</v>
       </c>
-      <c r="G82" s="4" t="s">
+      <c r="G82" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -16588,7 +16605,7 @@
       <c r="F84" s="5">
         <v>80</v>
       </c>
-      <c r="G84" s="4" t="s">
+      <c r="G84" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -16703,7 +16720,7 @@
       <c r="F89" s="5">
         <v>1473</v>
       </c>
-      <c r="G89" s="4" t="s">
+      <c r="G89" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -16726,7 +16743,7 @@
       <c r="F90" s="5">
         <v>108017</v>
       </c>
-      <c r="G90" s="4" t="s">
+      <c r="G90" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -16749,7 +16766,7 @@
       <c r="F91" s="5">
         <v>68</v>
       </c>
-      <c r="G91" s="4" t="s">
+      <c r="G91" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -16772,7 +16789,7 @@
       <c r="F92" s="5">
         <v>336</v>
       </c>
-      <c r="G92" s="4" t="s">
+      <c r="G92" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -16795,7 +16812,7 @@
       <c r="F93" s="5">
         <v>283</v>
       </c>
-      <c r="G93" s="4" t="s">
+      <c r="G93" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -16818,7 +16835,7 @@
       <c r="F94" s="5">
         <v>126</v>
       </c>
-      <c r="G94" s="4" t="s">
+      <c r="G94" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -16884,10 +16901,10 @@
       <c r="E97">
         <v>10</v>
       </c>
-      <c r="F97" s="6">
+      <c r="F97" s="7">
         <v>7</v>
       </c>
-      <c r="G97" s="4" t="s">
+      <c r="G97" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -16956,7 +16973,7 @@
       <c r="F100" s="5">
         <v>379</v>
       </c>
-      <c r="G100" s="4" t="s">
+      <c r="G100" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -16979,7 +16996,7 @@
       <c r="F101" s="5">
         <v>385</v>
       </c>
-      <c r="G101" s="4" t="s">
+      <c r="G101" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17002,7 +17019,7 @@
       <c r="F102" s="5">
         <v>379</v>
       </c>
-      <c r="G102" s="4" t="s">
+      <c r="G102" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17025,7 +17042,7 @@
       <c r="F103" s="5">
         <v>391</v>
       </c>
-      <c r="G103" s="4" t="s">
+      <c r="G103" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17045,10 +17062,10 @@
       <c r="E104">
         <v>200</v>
       </c>
-      <c r="F104" s="6">
+      <c r="F104" s="7">
         <v>4</v>
       </c>
-      <c r="G104" s="4" t="s">
+      <c r="G104" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -17071,7 +17088,7 @@
       <c r="F105" s="5">
         <v>354</v>
       </c>
-      <c r="G105" s="4" t="s">
+      <c r="G105" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17094,7 +17111,7 @@
       <c r="F106" s="5">
         <v>15</v>
       </c>
-      <c r="G106" s="4" t="s">
+      <c r="G106" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17114,10 +17131,10 @@
       <c r="E107">
         <v>120</v>
       </c>
-      <c r="F107" s="6">
+      <c r="F107" s="7">
         <v>1</v>
       </c>
-      <c r="G107" s="4" t="s">
+      <c r="G107" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -17140,7 +17157,7 @@
       <c r="F108" s="5">
         <v>79</v>
       </c>
-      <c r="G108" s="4" t="s">
+      <c r="G108" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17186,7 +17203,7 @@
       <c r="F110" s="5">
         <v>1093</v>
       </c>
-      <c r="G110" s="4" t="s">
+      <c r="G110" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17278,7 +17295,7 @@
       <c r="F114" s="5">
         <v>39</v>
       </c>
-      <c r="G114" s="4" t="s">
+      <c r="G114" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17301,7 +17318,7 @@
       <c r="F115" s="5">
         <v>312</v>
       </c>
-      <c r="G115" s="4" t="s">
+      <c r="G115" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17344,10 +17361,10 @@
       <c r="E117">
         <v>5</v>
       </c>
-      <c r="F117" s="6">
+      <c r="F117" s="7">
         <v>2</v>
       </c>
-      <c r="G117" s="4" t="s">
+      <c r="G117" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -17370,7 +17387,7 @@
       <c r="F118" s="5">
         <v>314</v>
       </c>
-      <c r="G118" s="4" t="s">
+      <c r="G118" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17390,10 +17407,10 @@
       <c r="E119">
         <v>10</v>
       </c>
-      <c r="F119" s="6">
+      <c r="F119" s="7">
         <v>6</v>
       </c>
-      <c r="G119" s="4" t="s">
+      <c r="G119" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -17416,7 +17433,7 @@
       <c r="F120" s="5">
         <v>36</v>
       </c>
-      <c r="G120" s="4" t="s">
+      <c r="G120" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17485,7 +17502,7 @@
       <c r="F123" s="5">
         <v>127</v>
       </c>
-      <c r="G123" s="4" t="s">
+      <c r="G123" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17508,7 +17525,7 @@
       <c r="F124" s="5">
         <v>37</v>
       </c>
-      <c r="G124" s="4" t="s">
+      <c r="G124" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17554,7 +17571,7 @@
       <c r="F126" s="5">
         <v>17</v>
       </c>
-      <c r="G126" s="4" t="s">
+      <c r="G126" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17577,7 +17594,7 @@
       <c r="F127" s="5">
         <v>24</v>
       </c>
-      <c r="G127" s="4" t="s">
+      <c r="G127" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17600,7 +17617,7 @@
       <c r="F128" s="5">
         <v>18</v>
       </c>
-      <c r="G128" s="4" t="s">
+      <c r="G128" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17620,10 +17637,10 @@
       <c r="E129">
         <v>1</v>
       </c>
-      <c r="F129" s="6">
+      <c r="F129" s="7">
         <v>4</v>
       </c>
-      <c r="G129" s="4" t="s">
+      <c r="G129" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -17643,10 +17660,10 @@
       <c r="E130">
         <v>60</v>
       </c>
-      <c r="F130" s="6">
+      <c r="F130" s="7">
         <v>3</v>
       </c>
-      <c r="G130" s="4" t="s">
+      <c r="G130" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -17669,7 +17686,7 @@
       <c r="F131" s="5">
         <v>357</v>
       </c>
-      <c r="G131" s="4" t="s">
+      <c r="G131" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17692,7 +17709,7 @@
       <c r="F132" s="5">
         <v>58</v>
       </c>
-      <c r="G132" s="4" t="s">
+      <c r="G132" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17715,7 +17732,7 @@
       <c r="F133" s="5">
         <v>138</v>
       </c>
-      <c r="G133" s="4" t="s">
+      <c r="G133" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17738,7 +17755,7 @@
       <c r="F134" s="5">
         <v>480</v>
       </c>
-      <c r="G134" s="4" t="s">
+      <c r="G134" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17761,7 +17778,7 @@
       <c r="F135" s="5">
         <v>521</v>
       </c>
-      <c r="G135" s="4" t="s">
+      <c r="G135" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17784,7 +17801,7 @@
       <c r="F136" s="5">
         <v>480</v>
       </c>
-      <c r="G136" s="4" t="s">
+      <c r="G136" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17807,7 +17824,7 @@
       <c r="F137" s="5">
         <v>1601</v>
       </c>
-      <c r="G137" s="4" t="s">
+      <c r="G137" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17830,7 +17847,7 @@
       <c r="F138" s="5">
         <v>1130</v>
       </c>
-      <c r="G138" s="4" t="s">
+      <c r="G138" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17853,7 +17870,7 @@
       <c r="F139" s="5">
         <v>566</v>
       </c>
-      <c r="G139" s="4" t="s">
+      <c r="G139" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17876,7 +17893,7 @@
       <c r="F140" s="5">
         <v>252</v>
       </c>
-      <c r="G140" s="4" t="s">
+      <c r="G140" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17899,7 +17916,7 @@
       <c r="F141" s="5">
         <v>108</v>
       </c>
-      <c r="G141" s="4" t="s">
+      <c r="G141" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17922,7 +17939,7 @@
       <c r="F142" s="5">
         <v>122</v>
       </c>
-      <c r="G142" s="4" t="s">
+      <c r="G142" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17945,7 +17962,7 @@
       <c r="F143" s="5">
         <v>15</v>
       </c>
-      <c r="G143" s="4" t="s">
+      <c r="G143" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -17991,7 +18008,7 @@
       <c r="F145" s="5">
         <v>10</v>
       </c>
-      <c r="G145" s="4" t="s">
+      <c r="G145" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18014,7 +18031,7 @@
       <c r="F146" s="5">
         <v>34</v>
       </c>
-      <c r="G146" s="4" t="s">
+      <c r="G146" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18060,7 +18077,7 @@
       <c r="F148" s="5">
         <v>30</v>
       </c>
-      <c r="G148" s="4" t="s">
+      <c r="G148" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18083,7 +18100,7 @@
       <c r="F149" s="5">
         <v>147</v>
       </c>
-      <c r="G149" s="4" t="s">
+      <c r="G149" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18106,7 +18123,7 @@
       <c r="F150" s="5">
         <v>222</v>
       </c>
-      <c r="G150" s="4" t="s">
+      <c r="G150" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18129,7 +18146,7 @@
       <c r="F151" s="5">
         <v>311</v>
       </c>
-      <c r="G151" s="4" t="s">
+      <c r="G151" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18149,10 +18166,10 @@
       <c r="E152">
         <v>20</v>
       </c>
-      <c r="F152" s="6">
+      <c r="F152" s="7">
         <v>8</v>
       </c>
-      <c r="G152" s="4" t="s">
+      <c r="G152" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -18175,7 +18192,7 @@
       <c r="F153" s="5">
         <v>640</v>
       </c>
-      <c r="G153" s="4" t="s">
+      <c r="G153" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18198,7 +18215,7 @@
       <c r="F154" s="5">
         <v>121</v>
       </c>
-      <c r="G154" s="4" t="s">
+      <c r="G154" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18221,7 +18238,7 @@
       <c r="F155" s="5">
         <v>855</v>
       </c>
-      <c r="G155" s="4" t="s">
+      <c r="G155" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18267,7 +18284,7 @@
       <c r="F157" s="5">
         <v>66</v>
       </c>
-      <c r="G157" s="4" t="s">
+      <c r="G157" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18290,7 +18307,7 @@
       <c r="F158" s="5">
         <v>30</v>
       </c>
-      <c r="G158" s="4" t="s">
+      <c r="G158" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18313,7 +18330,7 @@
       <c r="F159" s="5">
         <v>83</v>
       </c>
-      <c r="G159" s="4" t="s">
+      <c r="G159" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18336,7 +18353,7 @@
       <c r="F160" s="5">
         <v>10</v>
       </c>
-      <c r="G160" s="4" t="s">
+      <c r="G160" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18359,7 +18376,7 @@
       <c r="F161" s="5">
         <v>51</v>
       </c>
-      <c r="G161" s="4" t="s">
+      <c r="G161" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18382,7 +18399,7 @@
       <c r="F162" s="5">
         <v>74</v>
       </c>
-      <c r="G162" s="4" t="s">
+      <c r="G162" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18405,7 +18422,7 @@
       <c r="F163" s="5">
         <v>11</v>
       </c>
-      <c r="G163" s="4" t="s">
+      <c r="G163" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18425,10 +18442,10 @@
       <c r="E164">
         <v>10</v>
       </c>
-      <c r="F164" s="6">
+      <c r="F164" s="7">
         <v>4</v>
       </c>
-      <c r="G164" s="4" t="s">
+      <c r="G164" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -18451,7 +18468,7 @@
       <c r="F165" s="5">
         <v>35</v>
       </c>
-      <c r="G165" s="4" t="s">
+      <c r="G165" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18474,7 +18491,7 @@
       <c r="F166" s="5">
         <v>62</v>
       </c>
-      <c r="G166" s="4" t="s">
+      <c r="G166" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18497,7 +18514,7 @@
       <c r="F167" s="5">
         <v>28</v>
       </c>
-      <c r="G167" s="4" t="s">
+      <c r="G167" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18520,7 +18537,7 @@
       <c r="F168" s="5">
         <v>920</v>
       </c>
-      <c r="G168" s="4" t="s">
+      <c r="G168" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18543,7 +18560,7 @@
       <c r="F169" s="5">
         <v>102</v>
       </c>
-      <c r="G169" s="4" t="s">
+      <c r="G169" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18566,7 +18583,7 @@
       <c r="F170" s="5">
         <v>211</v>
       </c>
-      <c r="G170" s="4" t="s">
+      <c r="G170" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18589,7 +18606,7 @@
       <c r="F171" s="5">
         <v>753</v>
       </c>
-      <c r="G171" s="4" t="s">
+      <c r="G171" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18612,7 +18629,7 @@
       <c r="F172" s="5">
         <v>31</v>
       </c>
-      <c r="G172" s="4" t="s">
+      <c r="G172" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18635,7 +18652,7 @@
       <c r="F173" s="5">
         <v>93</v>
       </c>
-      <c r="G173" s="4" t="s">
+      <c r="G173" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18658,7 +18675,7 @@
       <c r="F174" s="5">
         <v>378</v>
       </c>
-      <c r="G174" s="4" t="s">
+      <c r="G174" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18681,7 +18698,7 @@
       <c r="F175" s="5">
         <v>94</v>
       </c>
-      <c r="G175" s="4" t="s">
+      <c r="G175" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18704,7 +18721,7 @@
       <c r="F176" s="5">
         <v>103</v>
       </c>
-      <c r="G176" s="4" t="s">
+      <c r="G176" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18727,7 +18744,7 @@
       <c r="F177" s="5">
         <v>93</v>
       </c>
-      <c r="G177" s="4" t="s">
+      <c r="G177" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18750,7 +18767,7 @@
       <c r="F178" s="5">
         <v>68</v>
       </c>
-      <c r="G178" s="4" t="s">
+      <c r="G178" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18773,7 +18790,7 @@
       <c r="F179" s="5">
         <v>77</v>
       </c>
-      <c r="G179" s="4" t="s">
+      <c r="G179" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18816,10 +18833,10 @@
       <c r="E181">
         <v>12</v>
       </c>
-      <c r="F181" s="6">
+      <c r="F181" s="7">
         <v>4</v>
       </c>
-      <c r="G181" s="4" t="s">
+      <c r="G181" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -18839,10 +18856,10 @@
       <c r="E182">
         <v>6</v>
       </c>
-      <c r="F182" s="6">
+      <c r="F182" s="7">
         <v>6</v>
       </c>
-      <c r="G182" s="4" t="s">
+      <c r="G182" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -18865,7 +18882,7 @@
       <c r="F183" s="5">
         <v>233</v>
       </c>
-      <c r="G183" s="4" t="s">
+      <c r="G183" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18888,7 +18905,7 @@
       <c r="F184" s="5">
         <v>3763</v>
       </c>
-      <c r="G184" s="4" t="s">
+      <c r="G184" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18911,7 +18928,7 @@
       <c r="F185" s="5">
         <v>144</v>
       </c>
-      <c r="G185" s="4" t="s">
+      <c r="G185" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18934,7 +18951,7 @@
       <c r="F186" s="5">
         <v>40</v>
       </c>
-      <c r="G186" s="4" t="s">
+      <c r="G186" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18957,7 +18974,7 @@
       <c r="F187" s="5">
         <v>20</v>
       </c>
-      <c r="G187" s="4" t="s">
+      <c r="G187" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -18980,7 +18997,7 @@
       <c r="F188" s="5">
         <v>17</v>
       </c>
-      <c r="G188" s="4" t="s">
+      <c r="G188" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19003,7 +19020,7 @@
       <c r="F189" s="5">
         <v>380</v>
       </c>
-      <c r="G189" s="4" t="s">
+      <c r="G189" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19026,7 +19043,7 @@
       <c r="F190" s="5">
         <v>1181</v>
       </c>
-      <c r="G190" s="4" t="s">
+      <c r="G190" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19049,7 +19066,7 @@
       <c r="F191" s="5">
         <v>1873</v>
       </c>
-      <c r="G191" s="4" t="s">
+      <c r="G191" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19072,7 +19089,7 @@
       <c r="F192" s="5">
         <v>1210</v>
       </c>
-      <c r="G192" s="4" t="s">
+      <c r="G192" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19095,7 +19112,7 @@
       <c r="F193" s="5">
         <v>19771</v>
       </c>
-      <c r="G193" s="4" t="s">
+      <c r="G193" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19118,7 +19135,7 @@
       <c r="F194" s="5">
         <v>1181</v>
       </c>
-      <c r="G194" s="4" t="s">
+      <c r="G194" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19141,7 +19158,7 @@
       <c r="F195" s="5">
         <v>454</v>
       </c>
-      <c r="G195" s="4" t="s">
+      <c r="G195" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19164,7 +19181,7 @@
       <c r="F196" s="5">
         <v>880</v>
       </c>
-      <c r="G196" s="4" t="s">
+      <c r="G196" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19187,7 +19204,7 @@
       <c r="F197" s="5">
         <v>1247</v>
       </c>
-      <c r="G197" s="4" t="s">
+      <c r="G197" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19203,13 +19220,12 @@
   <dimension ref="A1:G96"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -19277,7 +19293,7 @@
       <c r="F3" s="5">
         <v>2704</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19300,7 +19316,7 @@
       <c r="F4" s="5">
         <v>11531</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19323,7 +19339,7 @@
       <c r="F5" s="5">
         <v>24538</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19346,7 +19362,7 @@
       <c r="F6" s="5">
         <v>10280</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19392,7 +19408,7 @@
       <c r="F8" s="5">
         <v>17903</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19415,7 +19431,7 @@
       <c r="F9" s="5">
         <v>8629</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19438,7 +19454,7 @@
       <c r="F10" s="5">
         <v>11508</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19461,7 +19477,7 @@
       <c r="F11" s="5">
         <v>13176</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19484,7 +19500,7 @@
       <c r="F12" s="5">
         <v>3711</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19530,7 +19546,7 @@
       <c r="F14" s="5">
         <v>3130</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19573,10 +19589,10 @@
       <c r="E16">
         <v>24</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="7">
         <v>3</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -19645,7 +19661,7 @@
       <c r="F19" s="5">
         <v>4472</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19668,7 +19684,7 @@
       <c r="F20" s="5">
         <v>5426</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19691,7 +19707,7 @@
       <c r="F21" s="5">
         <v>35636</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19714,7 +19730,7 @@
       <c r="F22" s="5">
         <v>15899</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19737,7 +19753,7 @@
       <c r="F23" s="5">
         <v>709</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19760,7 +19776,7 @@
       <c r="F24" s="5">
         <v>3515</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19783,7 +19799,7 @@
       <c r="F25" s="5">
         <v>13017</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19806,7 +19822,7 @@
       <c r="F26" s="5">
         <v>5421</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19852,7 +19868,7 @@
       <c r="F28" s="5">
         <v>3656</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19875,7 +19891,7 @@
       <c r="F29" s="5">
         <v>5347</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19898,7 +19914,7 @@
       <c r="F30" s="5">
         <v>5915</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G30" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19921,7 +19937,7 @@
       <c r="F31" s="5">
         <v>157701</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19967,7 +19983,7 @@
       <c r="F33" s="5">
         <v>40364</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="G33" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -19990,7 +20006,7 @@
       <c r="F34" s="5">
         <v>48824</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="G34" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20013,7 +20029,7 @@
       <c r="F35" s="5">
         <v>568</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G35" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20036,7 +20052,7 @@
       <c r="F36" s="5">
         <v>27575</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="G36" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20059,7 +20075,7 @@
       <c r="F37" s="5">
         <v>11422</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="G37" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20082,7 +20098,7 @@
       <c r="F38" s="5">
         <v>101264</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="G38" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20105,7 +20121,7 @@
       <c r="F39" s="5">
         <v>16352</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="G39" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20128,7 +20144,7 @@
       <c r="F40" s="5">
         <v>2448</v>
       </c>
-      <c r="G40" s="4" t="s">
+      <c r="G40" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20151,7 +20167,7 @@
       <c r="F41" s="5">
         <v>7902</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="G41" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20174,7 +20190,7 @@
       <c r="F42" s="5">
         <v>11077</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="G42" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20197,7 +20213,7 @@
       <c r="F43" s="5">
         <v>9827</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="G43" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20220,7 +20236,7 @@
       <c r="F44" s="5">
         <v>10489</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="G44" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20243,7 +20259,7 @@
       <c r="F45" s="5">
         <v>10890</v>
       </c>
-      <c r="G45" s="4" t="s">
+      <c r="G45" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20266,7 +20282,7 @@
       <c r="F46" s="5">
         <v>8923</v>
       </c>
-      <c r="G46" s="4" t="s">
+      <c r="G46" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20289,7 +20305,7 @@
       <c r="F47" s="5">
         <v>4057</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="G47" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20312,7 +20328,7 @@
       <c r="F48" s="5">
         <v>10180</v>
       </c>
-      <c r="G48" s="4" t="s">
+      <c r="G48" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20335,7 +20351,7 @@
       <c r="F49" s="5">
         <v>15509</v>
       </c>
-      <c r="G49" s="4" t="s">
+      <c r="G49" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20358,7 +20374,7 @@
       <c r="F50" s="5">
         <v>5674</v>
       </c>
-      <c r="G50" s="4" t="s">
+      <c r="G50" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20381,7 +20397,7 @@
       <c r="F51" s="5">
         <v>5151</v>
       </c>
-      <c r="G51" s="4" t="s">
+      <c r="G51" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20404,7 +20420,7 @@
       <c r="F52" s="5">
         <v>6599</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="G52" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20427,7 +20443,7 @@
       <c r="F53" s="5">
         <v>6337</v>
       </c>
-      <c r="G53" s="4" t="s">
+      <c r="G53" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20496,7 +20512,7 @@
       <c r="F56" s="5">
         <v>19</v>
       </c>
-      <c r="G56" s="4" t="s">
+      <c r="G56" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20565,7 +20581,7 @@
       <c r="F59" s="5">
         <v>4562</v>
       </c>
-      <c r="G59" s="4" t="s">
+      <c r="G59" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20588,7 +20604,7 @@
       <c r="F60" s="5">
         <v>3902</v>
       </c>
-      <c r="G60" s="4" t="s">
+      <c r="G60" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20611,7 +20627,7 @@
       <c r="F61" s="5">
         <v>3341</v>
       </c>
-      <c r="G61" s="4" t="s">
+      <c r="G61" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20657,7 +20673,7 @@
       <c r="F63" s="5">
         <v>9089</v>
       </c>
-      <c r="G63" s="4" t="s">
+      <c r="G63" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20680,7 +20696,7 @@
       <c r="F64" s="5">
         <v>7640</v>
       </c>
-      <c r="G64" s="4" t="s">
+      <c r="G64" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20700,10 +20716,10 @@
       <c r="E65">
         <v>12</v>
       </c>
-      <c r="F65" s="6">
+      <c r="F65" s="7">
         <v>5</v>
       </c>
-      <c r="G65" s="4" t="s">
+      <c r="G65" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -20726,7 +20742,7 @@
       <c r="F66" s="5">
         <v>429</v>
       </c>
-      <c r="G66" s="4" t="s">
+      <c r="G66" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20749,7 +20765,7 @@
       <c r="F67" s="5">
         <v>274</v>
       </c>
-      <c r="G67" s="4" t="s">
+      <c r="G67" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20769,10 +20785,10 @@
       <c r="E68">
         <v>12</v>
       </c>
-      <c r="F68" s="6">
+      <c r="F68" s="7">
         <v>4</v>
       </c>
-      <c r="G68" s="4" t="s">
+      <c r="G68" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -20795,7 +20811,7 @@
       <c r="F69" s="5">
         <v>699</v>
       </c>
-      <c r="G69" s="4" t="s">
+      <c r="G69" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20818,7 +20834,7 @@
       <c r="F70" s="5">
         <v>22</v>
       </c>
-      <c r="G70" s="4" t="s">
+      <c r="G70" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20887,7 +20903,7 @@
       <c r="F73" s="5">
         <v>13582</v>
       </c>
-      <c r="G73" s="4" t="s">
+      <c r="G73" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20910,7 +20926,7 @@
       <c r="F74" s="5">
         <v>10166</v>
       </c>
-      <c r="G74" s="4" t="s">
+      <c r="G74" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20933,7 +20949,7 @@
       <c r="F75" s="5">
         <v>9747</v>
       </c>
-      <c r="G75" s="4" t="s">
+      <c r="G75" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -20953,10 +20969,10 @@
       <c r="E76">
         <v>180</v>
       </c>
-      <c r="F76" s="6">
+      <c r="F76" s="7">
         <v>4</v>
       </c>
-      <c r="G76" s="4" t="s">
+      <c r="G76" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -20979,7 +20995,7 @@
       <c r="F77" s="5">
         <v>19302</v>
       </c>
-      <c r="G77" s="4" t="s">
+      <c r="G77" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21002,7 +21018,7 @@
       <c r="F78" s="5">
         <v>936</v>
       </c>
-      <c r="G78" s="4" t="s">
+      <c r="G78" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21025,7 +21041,7 @@
       <c r="F79" s="5">
         <v>359</v>
       </c>
-      <c r="G79" s="4" t="s">
+      <c r="G79" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21071,7 +21087,7 @@
       <c r="F81" s="5">
         <v>319</v>
       </c>
-      <c r="G81" s="4" t="s">
+      <c r="G81" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21094,7 +21110,7 @@
       <c r="F82" s="5">
         <v>1764</v>
       </c>
-      <c r="G82" s="4" t="s">
+      <c r="G82" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21117,7 +21133,7 @@
       <c r="F83" s="5">
         <v>8199</v>
       </c>
-      <c r="G83" s="4" t="s">
+      <c r="G83" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21140,7 +21156,7 @@
       <c r="F84" s="5">
         <v>43303</v>
       </c>
-      <c r="G84" s="4" t="s">
+      <c r="G84" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21186,7 +21202,7 @@
       <c r="F86" s="5">
         <v>26114</v>
       </c>
-      <c r="G86" s="4" t="s">
+      <c r="G86" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21209,7 +21225,7 @@
       <c r="F87" s="5">
         <v>808</v>
       </c>
-      <c r="G87" s="4" t="s">
+      <c r="G87" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21232,7 +21248,7 @@
       <c r="F88" s="5">
         <v>8455</v>
       </c>
-      <c r="G88" s="4" t="s">
+      <c r="G88" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21255,7 +21271,7 @@
       <c r="F89" s="5">
         <v>7086</v>
       </c>
-      <c r="G89" s="4" t="s">
+      <c r="G89" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21278,7 +21294,7 @@
       <c r="F90" s="5">
         <v>18282</v>
       </c>
-      <c r="G90" s="4" t="s">
+      <c r="G90" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21301,7 +21317,7 @@
       <c r="F91" s="5">
         <v>12312</v>
       </c>
-      <c r="G91" s="4" t="s">
+      <c r="G91" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21321,10 +21337,10 @@
       <c r="E92">
         <v>144</v>
       </c>
-      <c r="F92" s="6">
+      <c r="F92" s="7">
         <v>4</v>
       </c>
-      <c r="G92" s="4" t="s">
+      <c r="G92" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -21347,7 +21363,7 @@
       <c r="F93" s="5">
         <v>14872</v>
       </c>
-      <c r="G93" s="4" t="s">
+      <c r="G93" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21367,10 +21383,10 @@
       <c r="E94">
         <v>144</v>
       </c>
-      <c r="F94" s="6">
+      <c r="F94" s="7">
         <v>3</v>
       </c>
-      <c r="G94" s="4" t="s">
+      <c r="G94" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -21416,7 +21432,7 @@
       <c r="F96" s="5">
         <v>33164</v>
       </c>
-      <c r="G96" s="4" t="s">
+      <c r="G96" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21432,13 +21448,12 @@
   <dimension ref="A1:G266"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -21480,10 +21495,10 @@
       <c r="E2">
         <v>50</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="7">
         <v>1</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -21506,7 +21521,7 @@
       <c r="F3" s="5">
         <v>46880</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21526,10 +21541,10 @@
       <c r="E4">
         <v>50</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="7">
         <v>2</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -21552,7 +21567,7 @@
       <c r="F5" s="5">
         <v>15008</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21575,7 +21590,7 @@
       <c r="F6" s="5">
         <v>18563</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21598,7 +21613,7 @@
       <c r="F7" s="5">
         <v>7989</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21618,10 +21633,10 @@
       <c r="E8">
         <v>50</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="7">
         <v>8</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -21644,7 +21659,7 @@
       <c r="F9" s="5">
         <v>3793</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21667,7 +21682,7 @@
       <c r="F10" s="5">
         <v>14254</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21690,7 +21705,7 @@
       <c r="F11" s="5">
         <v>5110</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21713,7 +21728,7 @@
       <c r="F12" s="5">
         <v>3159</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21736,7 +21751,7 @@
       <c r="F13" s="5">
         <v>4475</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21759,7 +21774,7 @@
       <c r="F14" s="5">
         <v>471</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21782,7 +21797,7 @@
       <c r="F15" s="5">
         <v>445</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21805,7 +21820,7 @@
       <c r="F16" s="5">
         <v>5267</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21828,7 +21843,7 @@
       <c r="F17" s="5">
         <v>8332</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21851,7 +21866,7 @@
       <c r="F18" s="5">
         <v>15919</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21874,7 +21889,7 @@
       <c r="F19" s="5">
         <v>2347</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21894,10 +21909,10 @@
       <c r="E20">
         <v>50</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="7">
         <v>6</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -21920,7 +21935,7 @@
       <c r="F21" s="5">
         <v>950</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21943,7 +21958,7 @@
       <c r="F22" s="5">
         <v>793</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21966,7 +21981,7 @@
       <c r="F23" s="5">
         <v>14</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -21989,7 +22004,7 @@
       <c r="F24" s="5">
         <v>49742</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22012,7 +22027,7 @@
       <c r="F25" s="5">
         <v>23061</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22035,7 +22050,7 @@
       <c r="F26" s="5">
         <v>8903</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22058,7 +22073,7 @@
       <c r="F27" s="5">
         <v>6190</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22081,7 +22096,7 @@
       <c r="F28" s="5">
         <v>23250</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22104,7 +22119,7 @@
       <c r="F29" s="5">
         <v>8719</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22127,7 +22142,7 @@
       <c r="F30" s="5">
         <v>9626</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G30" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22150,7 +22165,7 @@
       <c r="F31" s="5">
         <v>1199</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22173,7 +22188,7 @@
       <c r="F32" s="5">
         <v>5477</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="G32" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22196,7 +22211,7 @@
       <c r="F33" s="5">
         <v>23689</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="G33" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22219,7 +22234,7 @@
       <c r="F34" s="5">
         <v>8524</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="G34" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22242,7 +22257,7 @@
       <c r="F35" s="5">
         <v>18686</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G35" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22265,7 +22280,7 @@
       <c r="F36" s="5">
         <v>24483</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="G36" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22311,7 +22326,7 @@
       <c r="F38" s="5">
         <v>4621</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="G38" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22334,7 +22349,7 @@
       <c r="F39" s="5">
         <v>3223</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="G39" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22357,7 +22372,7 @@
       <c r="F40" s="5">
         <v>7031</v>
       </c>
-      <c r="G40" s="4" t="s">
+      <c r="G40" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22380,7 +22395,7 @@
       <c r="F41" s="5">
         <v>8844</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="G41" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22400,10 +22415,10 @@
       <c r="E42">
         <v>100</v>
       </c>
-      <c r="F42" s="6">
+      <c r="F42" s="7">
         <v>9</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="G42" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -22449,7 +22464,7 @@
       <c r="F44" s="5">
         <v>3439</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="G44" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22472,7 +22487,7 @@
       <c r="F45" s="5">
         <v>2776</v>
       </c>
-      <c r="G45" s="4" t="s">
+      <c r="G45" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22495,7 +22510,7 @@
       <c r="F46" s="5">
         <v>4764</v>
       </c>
-      <c r="G46" s="4" t="s">
+      <c r="G46" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22518,7 +22533,7 @@
       <c r="F47" s="5">
         <v>3213</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="G47" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22541,7 +22556,7 @@
       <c r="F48" s="5">
         <v>42</v>
       </c>
-      <c r="G48" s="4" t="s">
+      <c r="G48" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22564,7 +22579,7 @@
       <c r="F49" s="5">
         <v>1689</v>
       </c>
-      <c r="G49" s="4" t="s">
+      <c r="G49" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22587,7 +22602,7 @@
       <c r="F50" s="5">
         <v>2223</v>
       </c>
-      <c r="G50" s="4" t="s">
+      <c r="G50" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22610,7 +22625,7 @@
       <c r="F51" s="5">
         <v>1492</v>
       </c>
-      <c r="G51" s="4" t="s">
+      <c r="G51" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22633,7 +22648,7 @@
       <c r="F52" s="5">
         <v>1217</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="G52" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22656,7 +22671,7 @@
       <c r="F53" s="5">
         <v>1501</v>
       </c>
-      <c r="G53" s="4" t="s">
+      <c r="G53" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22679,7 +22694,7 @@
       <c r="F54" s="5">
         <v>751</v>
       </c>
-      <c r="G54" s="4" t="s">
+      <c r="G54" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22702,7 +22717,7 @@
       <c r="F55" s="5">
         <v>3204</v>
       </c>
-      <c r="G55" s="4" t="s">
+      <c r="G55" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22725,7 +22740,7 @@
       <c r="F56" s="5">
         <v>6582</v>
       </c>
-      <c r="G56" s="4" t="s">
+      <c r="G56" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22748,7 +22763,7 @@
       <c r="F57" s="5">
         <v>9360</v>
       </c>
-      <c r="G57" s="4" t="s">
+      <c r="G57" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22771,7 +22786,7 @@
       <c r="F58" s="5">
         <v>5186</v>
       </c>
-      <c r="G58" s="4" t="s">
+      <c r="G58" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22794,7 +22809,7 @@
       <c r="F59" s="5">
         <v>17008</v>
       </c>
-      <c r="G59" s="4" t="s">
+      <c r="G59" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22817,7 +22832,7 @@
       <c r="F60" s="5">
         <v>645</v>
       </c>
-      <c r="G60" s="4" t="s">
+      <c r="G60" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22840,7 +22855,7 @@
       <c r="F61" s="5">
         <v>3037</v>
       </c>
-      <c r="G61" s="4" t="s">
+      <c r="G61" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22863,7 +22878,7 @@
       <c r="F62" s="5">
         <v>2618</v>
       </c>
-      <c r="G62" s="4" t="s">
+      <c r="G62" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22886,7 +22901,7 @@
       <c r="F63" s="5">
         <v>1754</v>
       </c>
-      <c r="G63" s="4" t="s">
+      <c r="G63" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22909,7 +22924,7 @@
       <c r="F64" s="5">
         <v>253</v>
       </c>
-      <c r="G64" s="4" t="s">
+      <c r="G64" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22955,7 +22970,7 @@
       <c r="F66" s="5">
         <v>784</v>
       </c>
-      <c r="G66" s="4" t="s">
+      <c r="G66" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -22978,7 +22993,7 @@
       <c r="F67" s="5">
         <v>9167</v>
       </c>
-      <c r="G67" s="4" t="s">
+      <c r="G67" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23001,7 +23016,7 @@
       <c r="F68" s="5">
         <v>38116</v>
       </c>
-      <c r="G68" s="4" t="s">
+      <c r="G68" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23024,7 +23039,7 @@
       <c r="F69" s="5">
         <v>41458</v>
       </c>
-      <c r="G69" s="4" t="s">
+      <c r="G69" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23047,7 +23062,7 @@
       <c r="F70" s="5">
         <v>5567</v>
       </c>
-      <c r="G70" s="4" t="s">
+      <c r="G70" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23070,7 +23085,7 @@
       <c r="F71" s="5">
         <v>100</v>
       </c>
-      <c r="G71" s="4" t="s">
+      <c r="G71" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23093,7 +23108,7 @@
       <c r="F72" s="5">
         <v>30095</v>
       </c>
-      <c r="G72" s="4" t="s">
+      <c r="G72" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23116,7 +23131,7 @@
       <c r="F73" s="5">
         <v>16599</v>
       </c>
-      <c r="G73" s="4" t="s">
+      <c r="G73" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23139,7 +23154,7 @@
       <c r="F74" s="5">
         <v>47058</v>
       </c>
-      <c r="G74" s="4" t="s">
+      <c r="G74" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23162,7 +23177,7 @@
       <c r="F75" s="5">
         <v>23876</v>
       </c>
-      <c r="G75" s="4" t="s">
+      <c r="G75" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23185,7 +23200,7 @@
       <c r="F76" s="5">
         <v>2757</v>
       </c>
-      <c r="G76" s="4" t="s">
+      <c r="G76" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23208,7 +23223,7 @@
       <c r="F77" s="5">
         <v>43524</v>
       </c>
-      <c r="G77" s="4" t="s">
+      <c r="G77" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23231,7 +23246,7 @@
       <c r="F78" s="5">
         <v>43284</v>
       </c>
-      <c r="G78" s="4" t="s">
+      <c r="G78" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23254,7 +23269,7 @@
       <c r="F79" s="5">
         <v>39649</v>
       </c>
-      <c r="G79" s="4" t="s">
+      <c r="G79" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23277,7 +23292,7 @@
       <c r="F80" s="5">
         <v>16423</v>
       </c>
-      <c r="G80" s="4" t="s">
+      <c r="G80" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23300,7 +23315,7 @@
       <c r="F81" s="5">
         <v>10217</v>
       </c>
-      <c r="G81" s="4" t="s">
+      <c r="G81" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23320,10 +23335,10 @@
       <c r="E82">
         <v>100</v>
       </c>
-      <c r="F82" s="6">
+      <c r="F82" s="7">
         <v>9</v>
       </c>
-      <c r="G82" s="4" t="s">
+      <c r="G82" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -23346,7 +23361,7 @@
       <c r="F83" s="5">
         <v>13015</v>
       </c>
-      <c r="G83" s="4" t="s">
+      <c r="G83" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23369,7 +23384,7 @@
       <c r="F84" s="5">
         <v>3092</v>
       </c>
-      <c r="G84" s="4" t="s">
+      <c r="G84" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23392,7 +23407,7 @@
       <c r="F85" s="5">
         <v>13</v>
       </c>
-      <c r="G85" s="4" t="s">
+      <c r="G85" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23415,7 +23430,7 @@
       <c r="F86" s="5">
         <v>38853</v>
       </c>
-      <c r="G86" s="4" t="s">
+      <c r="G86" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23438,7 +23453,7 @@
       <c r="F87" s="5">
         <v>8930</v>
       </c>
-      <c r="G87" s="4" t="s">
+      <c r="G87" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23461,7 +23476,7 @@
       <c r="F88" s="5">
         <v>6513</v>
       </c>
-      <c r="G88" s="4" t="s">
+      <c r="G88" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23484,7 +23499,7 @@
       <c r="F89" s="5">
         <v>12755</v>
       </c>
-      <c r="G89" s="4" t="s">
+      <c r="G89" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23507,7 +23522,7 @@
       <c r="F90" s="5">
         <v>7711</v>
       </c>
-      <c r="G90" s="4" t="s">
+      <c r="G90" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23530,7 +23545,7 @@
       <c r="F91" s="5">
         <v>7789</v>
       </c>
-      <c r="G91" s="4" t="s">
+      <c r="G91" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23553,7 +23568,7 @@
       <c r="F92" s="5">
         <v>940</v>
       </c>
-      <c r="G92" s="4" t="s">
+      <c r="G92" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23576,7 +23591,7 @@
       <c r="F93" s="5">
         <v>11171</v>
       </c>
-      <c r="G93" s="4" t="s">
+      <c r="G93" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23599,7 +23614,7 @@
       <c r="F94" s="5">
         <v>2807</v>
       </c>
-      <c r="G94" s="4" t="s">
+      <c r="G94" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23622,7 +23637,7 @@
       <c r="F95" s="5">
         <v>6808</v>
       </c>
-      <c r="G95" s="4" t="s">
+      <c r="G95" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23645,7 +23660,7 @@
       <c r="F96" s="5">
         <v>15318</v>
       </c>
-      <c r="G96" s="4" t="s">
+      <c r="G96" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23668,7 +23683,7 @@
       <c r="F97" s="5">
         <v>2489</v>
       </c>
-      <c r="G97" s="4" t="s">
+      <c r="G97" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23691,7 +23706,7 @@
       <c r="F98" s="5">
         <v>26</v>
       </c>
-      <c r="G98" s="4" t="s">
+      <c r="G98" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23714,7 +23729,7 @@
       <c r="F99" s="5">
         <v>1687</v>
       </c>
-      <c r="G99" s="4" t="s">
+      <c r="G99" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23737,7 +23752,7 @@
       <c r="F100" s="5">
         <v>1441</v>
       </c>
-      <c r="G100" s="4" t="s">
+      <c r="G100" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23757,10 +23772,10 @@
       <c r="E101">
         <v>120</v>
       </c>
-      <c r="F101" s="6">
+      <c r="F101" s="7">
         <v>6</v>
       </c>
-      <c r="G101" s="4" t="s">
+      <c r="G101" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -23783,7 +23798,7 @@
       <c r="F102" s="5">
         <v>60</v>
       </c>
-      <c r="G102" s="4" t="s">
+      <c r="G102" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23806,7 +23821,7 @@
       <c r="F103" s="5">
         <v>335</v>
       </c>
-      <c r="G103" s="4" t="s">
+      <c r="G103" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23829,7 +23844,7 @@
       <c r="F104" s="5">
         <v>6286</v>
       </c>
-      <c r="G104" s="4" t="s">
+      <c r="G104" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23852,7 +23867,7 @@
       <c r="F105" s="5">
         <v>5774</v>
       </c>
-      <c r="G105" s="4" t="s">
+      <c r="G105" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23875,7 +23890,7 @@
       <c r="F106" s="5">
         <v>6024</v>
       </c>
-      <c r="G106" s="4" t="s">
+      <c r="G106" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23898,7 +23913,7 @@
       <c r="F107" s="5">
         <v>5045</v>
       </c>
-      <c r="G107" s="4" t="s">
+      <c r="G107" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23921,7 +23936,7 @@
       <c r="F108" s="5">
         <v>3138</v>
       </c>
-      <c r="G108" s="4" t="s">
+      <c r="G108" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23944,7 +23959,7 @@
       <c r="F109" s="5">
         <v>5148</v>
       </c>
-      <c r="G109" s="4" t="s">
+      <c r="G109" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23967,7 +23982,7 @@
       <c r="F110" s="5">
         <v>4818</v>
       </c>
-      <c r="G110" s="4" t="s">
+      <c r="G110" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -23987,10 +24002,10 @@
       <c r="E111">
         <v>120</v>
       </c>
-      <c r="F111" s="6">
+      <c r="F111" s="7">
         <v>8</v>
       </c>
-      <c r="G111" s="4" t="s">
+      <c r="G111" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -24013,7 +24028,7 @@
       <c r="F112" s="5">
         <v>2788</v>
       </c>
-      <c r="G112" s="4" t="s">
+      <c r="G112" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -24036,7 +24051,7 @@
       <c r="F113" s="5">
         <v>2880</v>
       </c>
-      <c r="G113" s="4" t="s">
+      <c r="G113" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -24059,7 +24074,7 @@
       <c r="F114" s="5">
         <v>137</v>
       </c>
-      <c r="G114" s="4" t="s">
+      <c r="G114" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -24102,10 +24117,10 @@
       <c r="E116">
         <v>24</v>
       </c>
-      <c r="F116" s="6">
+      <c r="F116" s="7">
         <v>3</v>
       </c>
-      <c r="G116" s="4" t="s">
+      <c r="G116" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -24125,10 +24140,10 @@
       <c r="E117">
         <v>24</v>
       </c>
-      <c r="F117" s="6">
+      <c r="F117" s="7">
         <v>1</v>
       </c>
-      <c r="G117" s="4" t="s">
+      <c r="G117" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -24151,7 +24166,7 @@
       <c r="F118" s="5">
         <v>2188</v>
       </c>
-      <c r="G118" s="4" t="s">
+      <c r="G118" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -24174,7 +24189,7 @@
       <c r="F119" s="5">
         <v>25356</v>
       </c>
-      <c r="G119" s="4" t="s">
+      <c r="G119" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -24197,7 +24212,7 @@
       <c r="F120" s="5">
         <v>28796</v>
       </c>
-      <c r="G120" s="4" t="s">
+      <c r="G120" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -24220,7 +24235,7 @@
       <c r="F121" s="5">
         <v>5028</v>
       </c>
-      <c r="G121" s="4" t="s">
+      <c r="G121" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -24243,7 +24258,7 @@
       <c r="F122" s="5">
         <v>3714</v>
       </c>
-      <c r="G122" s="4" t="s">
+      <c r="G122" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -24266,7 +24281,7 @@
       <c r="F123" s="5">
         <v>1463</v>
       </c>
-      <c r="G123" s="4" t="s">
+      <c r="G123" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -24289,7 +24304,7 @@
       <c r="F124" s="5">
         <v>8130</v>
       </c>
-      <c r="G124" s="4" t="s">
+      <c r="G124" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -24312,7 +24327,7 @@
       <c r="F125" s="5">
         <v>595</v>
       </c>
-      <c r="G125" s="4" t="s">
+      <c r="G125" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -24358,7 +24373,7 @@
       <c r="F127" s="5">
         <v>57</v>
       </c>
-      <c r="G127" s="4" t="s">
+      <c r="G127" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -24381,7 +24396,7 @@
       <c r="F128" s="5">
         <v>5434</v>
       </c>
-      <c r="G128" s="4" t="s">
+      <c r="G128" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -24404,7 +24419,7 @@
       <c r="F129" s="5">
         <v>8160</v>
       </c>
-      <c r="G129" s="4" t="s">
+      <c r="G129" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -24427,7 +24442,7 @@
       <c r="F130" s="5">
         <v>15659</v>
       </c>
-      <c r="G130" s="4" t="s">
+      <c r="G130" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -24450,7 +24465,7 @@
       <c r="F131" s="5">
         <v>9834</v>
       </c>
-      <c r="G131" s="4" t="s">
+      <c r="G131" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -24473,7 +24488,7 @@
       <c r="F132" s="5">
         <v>9665</v>
       </c>
-      <c r="G132" s="4" t="s">
+      <c r="G132" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -24519,7 +24534,7 @@
       <c r="F134" s="5">
         <v>5369</v>
       </c>
-      <c r="G134" s="4" t="s">
+      <c r="G134" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -24565,7 +24580,7 @@
       <c r="F136" s="5">
         <v>14101</v>
       </c>
-      <c r="G136" s="4" t="s">
+      <c r="G136" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -24634,7 +24649,7 @@
       <c r="F139" s="5">
         <v>49</v>
       </c>
-      <c r="G139" s="4" t="s">
+      <c r="G139" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -24657,7 +24672,7 @@
       <c r="F140" s="5">
         <v>297</v>
       </c>
-      <c r="G140" s="4" t="s">
+      <c r="G140" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -24680,7 +24695,7 @@
       <c r="F141" s="5">
         <v>180</v>
       </c>
-      <c r="G141" s="4" t="s">
+      <c r="G141" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -24723,10 +24738,10 @@
       <c r="E143">
         <v>24</v>
       </c>
-      <c r="F143" s="6">
+      <c r="F143" s="7">
         <v>3</v>
       </c>
-      <c r="G143" s="4" t="s">
+      <c r="G143" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -24772,7 +24787,7 @@
       <c r="F145" s="5">
         <v>538</v>
       </c>
-      <c r="G145" s="4" t="s">
+      <c r="G145" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -24792,10 +24807,10 @@
       <c r="E146">
         <v>24</v>
       </c>
-      <c r="F146" s="6">
+      <c r="F146" s="7">
         <v>5</v>
       </c>
-      <c r="G146" s="4" t="s">
+      <c r="G146" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -24815,10 +24830,10 @@
       <c r="E147">
         <v>24</v>
       </c>
-      <c r="F147" s="6">
+      <c r="F147" s="7">
         <v>4</v>
       </c>
-      <c r="G147" s="4" t="s">
+      <c r="G147" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -24841,7 +24856,7 @@
       <c r="F148" s="5">
         <v>172</v>
       </c>
-      <c r="G148" s="4" t="s">
+      <c r="G148" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -24864,7 +24879,7 @@
       <c r="F149" s="5">
         <v>616</v>
       </c>
-      <c r="G149" s="4" t="s">
+      <c r="G149" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -24887,7 +24902,7 @@
       <c r="F150" s="5">
         <v>557</v>
       </c>
-      <c r="G150" s="4" t="s">
+      <c r="G150" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -24910,7 +24925,7 @@
       <c r="F151" s="5">
         <v>459</v>
       </c>
-      <c r="G151" s="4" t="s">
+      <c r="G151" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -24933,7 +24948,7 @@
       <c r="F152" s="5">
         <v>303</v>
       </c>
-      <c r="G152" s="4" t="s">
+      <c r="G152" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -24956,7 +24971,7 @@
       <c r="F153" s="5">
         <v>159</v>
       </c>
-      <c r="G153" s="4" t="s">
+      <c r="G153" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -24979,7 +24994,7 @@
       <c r="F154" s="5">
         <v>283</v>
       </c>
-      <c r="G154" s="4" t="s">
+      <c r="G154" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -25002,7 +25017,7 @@
       <c r="F155" s="5">
         <v>1459</v>
       </c>
-      <c r="G155" s="4" t="s">
+      <c r="G155" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -25025,7 +25040,7 @@
       <c r="F156" s="5">
         <v>936</v>
       </c>
-      <c r="G156" s="4" t="s">
+      <c r="G156" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -25048,7 +25063,7 @@
       <c r="F157" s="5">
         <v>263</v>
       </c>
-      <c r="G157" s="4" t="s">
+      <c r="G157" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -25071,7 +25086,7 @@
       <c r="F158" s="5">
         <v>17</v>
       </c>
-      <c r="G158" s="4" t="s">
+      <c r="G158" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -25094,7 +25109,7 @@
       <c r="F159" s="5">
         <v>130</v>
       </c>
-      <c r="G159" s="4" t="s">
+      <c r="G159" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -25140,7 +25155,7 @@
       <c r="F161" s="5">
         <v>922</v>
       </c>
-      <c r="G161" s="4" t="s">
+      <c r="G161" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -25163,7 +25178,7 @@
       <c r="F162" s="5">
         <v>1843</v>
       </c>
-      <c r="G162" s="4" t="s">
+      <c r="G162" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -25186,7 +25201,7 @@
       <c r="F163" s="5">
         <v>586</v>
       </c>
-      <c r="G163" s="4" t="s">
+      <c r="G163" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -25209,7 +25224,7 @@
       <c r="F164" s="5">
         <v>996</v>
       </c>
-      <c r="G164" s="4" t="s">
+      <c r="G164" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -25232,7 +25247,7 @@
       <c r="F165" s="5">
         <v>1246</v>
       </c>
-      <c r="G165" s="4" t="s">
+      <c r="G165" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -25252,10 +25267,10 @@
       <c r="E166">
         <v>24</v>
       </c>
-      <c r="F166" s="6">
+      <c r="F166" s="7">
         <v>1</v>
       </c>
-      <c r="G166" s="4" t="s">
+      <c r="G166" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -25278,7 +25293,7 @@
       <c r="F167" s="5">
         <v>22562</v>
       </c>
-      <c r="G167" s="4" t="s">
+      <c r="G167" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -25301,7 +25316,7 @@
       <c r="F168" s="5">
         <v>4260</v>
       </c>
-      <c r="G168" s="4" t="s">
+      <c r="G168" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -25324,7 +25339,7 @@
       <c r="F169" s="5">
         <v>1404</v>
       </c>
-      <c r="G169" s="4" t="s">
+      <c r="G169" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -25344,10 +25359,10 @@
       <c r="E170">
         <v>36</v>
       </c>
-      <c r="F170" s="6">
+      <c r="F170" s="7">
         <v>3</v>
       </c>
-      <c r="G170" s="4" t="s">
+      <c r="G170" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -25416,7 +25431,7 @@
       <c r="F173" s="5">
         <v>1193</v>
       </c>
-      <c r="G173" s="4" t="s">
+      <c r="G173" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -25439,7 +25454,7 @@
       <c r="F174" s="5">
         <v>1492</v>
       </c>
-      <c r="G174" s="4" t="s">
+      <c r="G174" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -25485,7 +25500,7 @@
       <c r="F176" s="5">
         <v>48</v>
       </c>
-      <c r="G176" s="4" t="s">
+      <c r="G176" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -25508,7 +25523,7 @@
       <c r="F177" s="5">
         <v>193</v>
       </c>
-      <c r="G177" s="4" t="s">
+      <c r="G177" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -25531,7 +25546,7 @@
       <c r="F178" s="5">
         <v>520</v>
       </c>
-      <c r="G178" s="4" t="s">
+      <c r="G178" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -25554,7 +25569,7 @@
       <c r="F179" s="5">
         <v>218</v>
       </c>
-      <c r="G179" s="4" t="s">
+      <c r="G179" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -25623,7 +25638,7 @@
       <c r="F182" s="5">
         <v>922</v>
       </c>
-      <c r="G182" s="4" t="s">
+      <c r="G182" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -25646,7 +25661,7 @@
       <c r="F183" s="5">
         <v>4191</v>
       </c>
-      <c r="G183" s="4" t="s">
+      <c r="G183" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -25669,7 +25684,7 @@
       <c r="F184" s="5">
         <v>5005</v>
       </c>
-      <c r="G184" s="4" t="s">
+      <c r="G184" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -25692,7 +25707,7 @@
       <c r="F185" s="5">
         <v>1086</v>
       </c>
-      <c r="G185" s="4" t="s">
+      <c r="G185" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -25715,7 +25730,7 @@
       <c r="F186" s="5">
         <v>6027</v>
       </c>
-      <c r="G186" s="4" t="s">
+      <c r="G186" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -25738,7 +25753,7 @@
       <c r="F187" s="5">
         <v>5054</v>
       </c>
-      <c r="G187" s="4" t="s">
+      <c r="G187" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -25761,7 +25776,7 @@
       <c r="F188" s="5">
         <v>3358</v>
       </c>
-      <c r="G188" s="4" t="s">
+      <c r="G188" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -25784,7 +25799,7 @@
       <c r="F189" s="5">
         <v>1991</v>
       </c>
-      <c r="G189" s="4" t="s">
+      <c r="G189" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -25807,7 +25822,7 @@
       <c r="F190" s="5">
         <v>10090</v>
       </c>
-      <c r="G190" s="4" t="s">
+      <c r="G190" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -25876,7 +25891,7 @@
       <c r="F193" s="5">
         <v>8395</v>
       </c>
-      <c r="G193" s="4" t="s">
+      <c r="G193" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -25899,7 +25914,7 @@
       <c r="F194" s="5">
         <v>558</v>
       </c>
-      <c r="G194" s="4" t="s">
+      <c r="G194" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -25922,7 +25937,7 @@
       <c r="F195" s="5">
         <v>2132</v>
       </c>
-      <c r="G195" s="4" t="s">
+      <c r="G195" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -25991,7 +26006,7 @@
       <c r="F198" s="5">
         <v>216</v>
       </c>
-      <c r="G198" s="4" t="s">
+      <c r="G198" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26014,7 +26029,7 @@
       <c r="F199" s="5">
         <v>69</v>
       </c>
-      <c r="G199" s="4" t="s">
+      <c r="G199" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26037,7 +26052,7 @@
       <c r="F200" s="5">
         <v>1573</v>
       </c>
-      <c r="G200" s="4" t="s">
+      <c r="G200" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26060,7 +26075,7 @@
       <c r="F201" s="5">
         <v>1831</v>
       </c>
-      <c r="G201" s="4" t="s">
+      <c r="G201" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26083,7 +26098,7 @@
       <c r="F202" s="5">
         <v>2404</v>
       </c>
-      <c r="G202" s="4" t="s">
+      <c r="G202" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26106,7 +26121,7 @@
       <c r="F203" s="5">
         <v>2176</v>
       </c>
-      <c r="G203" s="4" t="s">
+      <c r="G203" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26129,7 +26144,7 @@
       <c r="F204" s="5">
         <v>4873</v>
       </c>
-      <c r="G204" s="4" t="s">
+      <c r="G204" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26152,7 +26167,7 @@
       <c r="F205" s="5">
         <v>745</v>
       </c>
-      <c r="G205" s="4" t="s">
+      <c r="G205" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26175,7 +26190,7 @@
       <c r="F206" s="5">
         <v>3896</v>
       </c>
-      <c r="G206" s="4" t="s">
+      <c r="G206" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26198,7 +26213,7 @@
       <c r="F207" s="5">
         <v>2774</v>
       </c>
-      <c r="G207" s="4" t="s">
+      <c r="G207" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26221,7 +26236,7 @@
       <c r="F208" s="5">
         <v>5462</v>
       </c>
-      <c r="G208" s="4" t="s">
+      <c r="G208" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26244,7 +26259,7 @@
       <c r="F209" s="5">
         <v>6036</v>
       </c>
-      <c r="G209" s="4" t="s">
+      <c r="G209" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26290,7 +26305,7 @@
       <c r="F211" s="5">
         <v>848</v>
       </c>
-      <c r="G211" s="4" t="s">
+      <c r="G211" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26313,7 +26328,7 @@
       <c r="F212" s="5">
         <v>4603</v>
       </c>
-      <c r="G212" s="4" t="s">
+      <c r="G212" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26336,7 +26351,7 @@
       <c r="F213" s="5">
         <v>369</v>
       </c>
-      <c r="G213" s="4" t="s">
+      <c r="G213" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26359,7 +26374,7 @@
       <c r="F214" s="5">
         <v>3947</v>
       </c>
-      <c r="G214" s="4" t="s">
+      <c r="G214" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26382,7 +26397,7 @@
       <c r="F215" s="5">
         <v>6239</v>
       </c>
-      <c r="G215" s="4" t="s">
+      <c r="G215" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26405,7 +26420,7 @@
       <c r="F216" s="5">
         <v>90</v>
       </c>
-      <c r="G216" s="4" t="s">
+      <c r="G216" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26428,7 +26443,7 @@
       <c r="F217" s="5">
         <v>395</v>
       </c>
-      <c r="G217" s="4" t="s">
+      <c r="G217" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26451,7 +26466,7 @@
       <c r="F218" s="5">
         <v>129</v>
       </c>
-      <c r="G218" s="4" t="s">
+      <c r="G218" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26471,10 +26486,10 @@
       <c r="E219">
         <v>5</v>
       </c>
-      <c r="F219" s="6">
+      <c r="F219" s="7">
         <v>1</v>
       </c>
-      <c r="G219" s="4" t="s">
+      <c r="G219" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -26520,7 +26535,7 @@
       <c r="F221" s="5">
         <v>3782</v>
       </c>
-      <c r="G221" s="4" t="s">
+      <c r="G221" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26543,7 +26558,7 @@
       <c r="F222" s="5">
         <v>1044</v>
       </c>
-      <c r="G222" s="4" t="s">
+      <c r="G222" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26566,7 +26581,7 @@
       <c r="F223" s="5">
         <v>2285</v>
       </c>
-      <c r="G223" s="4" t="s">
+      <c r="G223" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26589,7 +26604,7 @@
       <c r="F224" s="5">
         <v>1839</v>
       </c>
-      <c r="G224" s="4" t="s">
+      <c r="G224" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26612,7 +26627,7 @@
       <c r="F225" s="5">
         <v>451</v>
       </c>
-      <c r="G225" s="4" t="s">
+      <c r="G225" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26635,7 +26650,7 @@
       <c r="F226" s="5">
         <v>2246</v>
       </c>
-      <c r="G226" s="4" t="s">
+      <c r="G226" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26658,7 +26673,7 @@
       <c r="F227" s="5">
         <v>463</v>
       </c>
-      <c r="G227" s="4" t="s">
+      <c r="G227" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26704,7 +26719,7 @@
       <c r="F229" s="5">
         <v>444</v>
       </c>
-      <c r="G229" s="4" t="s">
+      <c r="G229" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26727,7 +26742,7 @@
       <c r="F230" s="5">
         <v>917</v>
       </c>
-      <c r="G230" s="4" t="s">
+      <c r="G230" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26773,7 +26788,7 @@
       <c r="F232" s="5">
         <v>262</v>
       </c>
-      <c r="G232" s="4" t="s">
+      <c r="G232" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26796,7 +26811,7 @@
       <c r="F233" s="5">
         <v>176</v>
       </c>
-      <c r="G233" s="4" t="s">
+      <c r="G233" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26819,7 +26834,7 @@
       <c r="F234" s="5">
         <v>72</v>
       </c>
-      <c r="G234" s="4" t="s">
+      <c r="G234" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26842,7 +26857,7 @@
       <c r="F235" s="5">
         <v>361</v>
       </c>
-      <c r="G235" s="4" t="s">
+      <c r="G235" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26865,7 +26880,7 @@
       <c r="F236" s="5">
         <v>257</v>
       </c>
-      <c r="G236" s="4" t="s">
+      <c r="G236" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26888,7 +26903,7 @@
       <c r="F237" s="5">
         <v>257</v>
       </c>
-      <c r="G237" s="4" t="s">
+      <c r="G237" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26911,7 +26926,7 @@
       <c r="F238" s="5">
         <v>231</v>
       </c>
-      <c r="G238" s="4" t="s">
+      <c r="G238" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26934,7 +26949,7 @@
       <c r="F239" s="5">
         <v>277</v>
       </c>
-      <c r="G239" s="4" t="s">
+      <c r="G239" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26957,7 +26972,7 @@
       <c r="F240" s="5">
         <v>117</v>
       </c>
-      <c r="G240" s="4" t="s">
+      <c r="G240" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -26980,7 +26995,7 @@
       <c r="F241" s="5">
         <v>1705</v>
       </c>
-      <c r="G241" s="4" t="s">
+      <c r="G241" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27000,10 +27015,10 @@
       <c r="E242">
         <v>5</v>
       </c>
-      <c r="F242" s="6">
+      <c r="F242" s="7">
         <v>1</v>
       </c>
-      <c r="G242" s="4" t="s">
+      <c r="G242" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -27026,7 +27041,7 @@
       <c r="F243" s="5">
         <v>275</v>
       </c>
-      <c r="G243" s="4" t="s">
+      <c r="G243" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27049,7 +27064,7 @@
       <c r="F244" s="5">
         <v>216</v>
       </c>
-      <c r="G244" s="4" t="s">
+      <c r="G244" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27095,7 +27110,7 @@
       <c r="F246" s="5">
         <v>236</v>
       </c>
-      <c r="G246" s="4" t="s">
+      <c r="G246" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27118,7 +27133,7 @@
       <c r="F247" s="5">
         <v>392</v>
       </c>
-      <c r="G247" s="4" t="s">
+      <c r="G247" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27141,7 +27156,7 @@
       <c r="F248" s="5">
         <v>167</v>
       </c>
-      <c r="G248" s="4" t="s">
+      <c r="G248" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27161,10 +27176,10 @@
       <c r="E249">
         <v>5</v>
       </c>
-      <c r="F249" s="6">
+      <c r="F249" s="7">
         <v>1</v>
       </c>
-      <c r="G249" s="4" t="s">
+      <c r="G249" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -27187,7 +27202,7 @@
       <c r="F250" s="5">
         <v>320</v>
       </c>
-      <c r="G250" s="4" t="s">
+      <c r="G250" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27210,7 +27225,7 @@
       <c r="F251" s="5">
         <v>4427</v>
       </c>
-      <c r="G251" s="4" t="s">
+      <c r="G251" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27279,7 +27294,7 @@
       <c r="F254" s="5">
         <v>143054</v>
       </c>
-      <c r="G254" s="4" t="s">
+      <c r="G254" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27302,7 +27317,7 @@
       <c r="F255" s="5">
         <v>211699</v>
       </c>
-      <c r="G255" s="4" t="s">
+      <c r="G255" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27325,7 +27340,7 @@
       <c r="F256" s="5">
         <v>90955</v>
       </c>
-      <c r="G256" s="4" t="s">
+      <c r="G256" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27348,7 +27363,7 @@
       <c r="F257" s="5">
         <v>620</v>
       </c>
-      <c r="G257" s="4" t="s">
+      <c r="G257" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27371,7 +27386,7 @@
       <c r="F258" s="5">
         <v>355</v>
       </c>
-      <c r="G258" s="4" t="s">
+      <c r="G258" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27394,7 +27409,7 @@
       <c r="F259" s="5">
         <v>89</v>
       </c>
-      <c r="G259" s="4" t="s">
+      <c r="G259" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27417,7 +27432,7 @@
       <c r="F260" s="5">
         <v>287</v>
       </c>
-      <c r="G260" s="4" t="s">
+      <c r="G260" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27440,7 +27455,7 @@
       <c r="F261" s="5">
         <v>72</v>
       </c>
-      <c r="G261" s="4" t="s">
+      <c r="G261" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27463,7 +27478,7 @@
       <c r="F262" s="5">
         <v>328</v>
       </c>
-      <c r="G262" s="4" t="s">
+      <c r="G262" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27486,7 +27501,7 @@
       <c r="F263" s="5">
         <v>238</v>
       </c>
-      <c r="G263" s="4" t="s">
+      <c r="G263" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27509,7 +27524,7 @@
       <c r="F264" s="5">
         <v>163</v>
       </c>
-      <c r="G264" s="4" t="s">
+      <c r="G264" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27532,7 +27547,7 @@
       <c r="F265" s="5">
         <v>27</v>
       </c>
-      <c r="G265" s="4" t="s">
+      <c r="G265" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27555,7 +27570,7 @@
       <c r="F266" s="5">
         <v>26</v>
       </c>
-      <c r="G266" s="4" t="s">
+      <c r="G266" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27571,13 +27586,12 @@
   <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -27622,7 +27636,7 @@
       <c r="F2" s="5">
         <v>3238</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27645,7 +27659,7 @@
       <c r="F3" s="5">
         <v>11065</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27668,7 +27682,7 @@
       <c r="F4" s="5">
         <v>4021</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27691,7 +27705,7 @@
       <c r="F5" s="5">
         <v>10493</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27714,7 +27728,7 @@
       <c r="F6" s="5">
         <v>207</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27737,7 +27751,7 @@
       <c r="F7" s="5">
         <v>7431</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27760,7 +27774,7 @@
       <c r="F8" s="5">
         <v>20598</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27783,7 +27797,7 @@
       <c r="F9" s="5">
         <v>40774</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27852,7 +27866,7 @@
       <c r="F12" s="5">
         <v>15306</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27872,10 +27886,10 @@
       <c r="E13">
         <v>500</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="7">
         <v>5</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -27898,7 +27912,7 @@
       <c r="F14" s="5">
         <v>1904</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27921,7 +27935,7 @@
       <c r="F15" s="5">
         <v>1063</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27944,7 +27958,7 @@
       <c r="F16" s="5">
         <v>2948</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27967,7 +27981,7 @@
       <c r="F17" s="5">
         <v>2798</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -27983,13 +27997,12 @@
   <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28034,7 +28047,7 @@
       <c r="F2" s="5">
         <v>1184</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28057,7 +28070,7 @@
       <c r="F3" s="5">
         <v>1329</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28080,7 +28093,7 @@
       <c r="F4" s="5">
         <v>925</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28103,7 +28116,7 @@
       <c r="F5" s="5">
         <v>874</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28126,7 +28139,7 @@
       <c r="F6" s="5">
         <v>722</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28149,7 +28162,7 @@
       <c r="F7" s="5">
         <v>433</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28172,7 +28185,7 @@
       <c r="F8" s="5">
         <v>645</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28195,7 +28208,7 @@
       <c r="F9" s="5">
         <v>468</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28218,7 +28231,7 @@
       <c r="F10" s="5">
         <v>2084</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28241,7 +28254,7 @@
       <c r="F11" s="5">
         <v>2119</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28264,7 +28277,7 @@
       <c r="F12" s="5">
         <v>2795</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28287,7 +28300,7 @@
       <c r="F13" s="5">
         <v>1630</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28310,7 +28323,7 @@
       <c r="F14" s="5">
         <v>486</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28333,7 +28346,7 @@
       <c r="F15" s="5">
         <v>692</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28356,7 +28369,7 @@
       <c r="F16" s="5">
         <v>1077</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28379,7 +28392,7 @@
       <c r="F17" s="5">
         <v>1164</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28402,7 +28415,7 @@
       <c r="F18" s="5">
         <v>243</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28425,7 +28438,7 @@
       <c r="F19" s="5">
         <v>61</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28448,7 +28461,7 @@
       <c r="F20" s="5">
         <v>1202</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28471,7 +28484,7 @@
       <c r="F21" s="5">
         <v>1344</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28494,7 +28507,7 @@
       <c r="F22" s="5">
         <v>1112</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28517,7 +28530,7 @@
       <c r="F23" s="5">
         <v>1048</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28540,7 +28553,7 @@
       <c r="F24" s="5">
         <v>616</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28563,7 +28576,7 @@
       <c r="F25" s="5">
         <v>430</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28586,7 +28599,7 @@
       <c r="F26" s="5">
         <v>202</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28609,7 +28622,7 @@
       <c r="F27" s="5">
         <v>198</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28632,7 +28645,7 @@
       <c r="F28" s="5">
         <v>497</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28655,7 +28668,7 @@
       <c r="F29" s="5">
         <v>477</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28678,7 +28691,7 @@
       <c r="F30" s="5">
         <v>663</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G30" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28701,7 +28714,7 @@
       <c r="F31" s="5">
         <v>613</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28721,10 +28734,10 @@
       <c r="E32">
         <v>48</v>
       </c>
-      <c r="F32" s="6">
+      <c r="F32" s="7">
         <v>2</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="G32" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -28740,13 +28753,12 @@
   <dimension ref="A1:G144"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -28791,7 +28803,7 @@
       <c r="F2" s="5">
         <v>74607</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28814,7 +28826,7 @@
       <c r="F3" s="5">
         <v>37794</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28837,7 +28849,7 @@
       <c r="F4" s="5">
         <v>27804</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28860,7 +28872,7 @@
       <c r="F5" s="5">
         <v>1038</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28883,7 +28895,7 @@
       <c r="F6" s="5">
         <v>2640</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28906,7 +28918,7 @@
       <c r="F7" s="5">
         <v>18827</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28929,7 +28941,7 @@
       <c r="F8" s="5">
         <v>6079</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28952,7 +28964,7 @@
       <c r="F9" s="5">
         <v>14929</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28975,7 +28987,7 @@
       <c r="F10" s="5">
         <v>9360</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -28998,7 +29010,7 @@
       <c r="F11" s="5">
         <v>6891</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29021,7 +29033,7 @@
       <c r="F12" s="5">
         <v>11851</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29044,7 +29056,7 @@
       <c r="F13" s="5">
         <v>4678</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29067,7 +29079,7 @@
       <c r="F14" s="5">
         <v>9351</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29090,7 +29102,7 @@
       <c r="F15" s="5">
         <v>7656</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29113,7 +29125,7 @@
       <c r="F16" s="5">
         <v>9675</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29136,7 +29148,7 @@
       <c r="F17" s="5">
         <v>14522</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29159,7 +29171,7 @@
       <c r="F18" s="5">
         <v>17198</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29182,7 +29194,7 @@
       <c r="F19" s="5">
         <v>9494</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29205,7 +29217,7 @@
       <c r="F20" s="5">
         <v>14861</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29228,7 +29240,7 @@
       <c r="F21" s="5">
         <v>9267</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29251,7 +29263,7 @@
       <c r="F22" s="5">
         <v>1033</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29271,10 +29283,10 @@
       <c r="E23">
         <v>192</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="7">
         <v>3</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -29297,7 +29309,7 @@
       <c r="F24" s="5">
         <v>3521</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29320,7 +29332,7 @@
       <c r="F25" s="5">
         <v>3794</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29343,7 +29355,7 @@
       <c r="F26" s="5">
         <v>13300</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29366,7 +29378,7 @@
       <c r="F27" s="5">
         <v>31026</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29389,7 +29401,7 @@
       <c r="F28" s="5">
         <v>122</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29412,7 +29424,7 @@
       <c r="F29" s="5">
         <v>13784</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29435,7 +29447,7 @@
       <c r="F30" s="5">
         <v>30886</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G30" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29458,7 +29470,7 @@
       <c r="F31" s="5">
         <v>11907</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29481,7 +29493,7 @@
       <c r="F32" s="5">
         <v>925</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="G32" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29504,7 +29516,7 @@
       <c r="F33" s="5">
         <v>1001</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="G33" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29524,10 +29536,10 @@
       <c r="E34">
         <v>72</v>
       </c>
-      <c r="F34" s="6">
+      <c r="F34" s="7">
         <v>6</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="G34" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -29550,7 +29562,7 @@
       <c r="F35" s="5">
         <v>258</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G35" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29573,7 +29585,7 @@
       <c r="F36" s="5">
         <v>42</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="G36" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29596,7 +29608,7 @@
       <c r="F37" s="5">
         <v>344</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="G37" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29619,7 +29631,7 @@
       <c r="F38" s="5">
         <v>235</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="G38" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29642,7 +29654,7 @@
       <c r="F39" s="5">
         <v>1014</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="G39" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29665,7 +29677,7 @@
       <c r="F40" s="5">
         <v>120</v>
       </c>
-      <c r="G40" s="4" t="s">
+      <c r="G40" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29688,7 +29700,7 @@
       <c r="F41" s="5">
         <v>454</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="G41" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29711,7 +29723,7 @@
       <c r="F42" s="5">
         <v>60</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="G42" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29734,7 +29746,7 @@
       <c r="F43" s="5">
         <v>400</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="G43" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29754,10 +29766,10 @@
       <c r="E44">
         <v>72</v>
       </c>
-      <c r="F44" s="6">
+      <c r="F44" s="7">
         <v>2</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="G44" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -29780,7 +29792,7 @@
       <c r="F45" s="5">
         <v>273</v>
       </c>
-      <c r="G45" s="4" t="s">
+      <c r="G45" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29803,7 +29815,7 @@
       <c r="F46" s="5">
         <v>842</v>
       </c>
-      <c r="G46" s="4" t="s">
+      <c r="G46" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29826,7 +29838,7 @@
       <c r="F47" s="5">
         <v>1400</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="G47" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29849,7 +29861,7 @@
       <c r="F48" s="5">
         <v>15932</v>
       </c>
-      <c r="G48" s="4" t="s">
+      <c r="G48" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29872,7 +29884,7 @@
       <c r="F49" s="5">
         <v>12651</v>
       </c>
-      <c r="G49" s="4" t="s">
+      <c r="G49" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29895,7 +29907,7 @@
       <c r="F50" s="5">
         <v>15140</v>
       </c>
-      <c r="G50" s="4" t="s">
+      <c r="G50" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29918,7 +29930,7 @@
       <c r="F51" s="5">
         <v>8998</v>
       </c>
-      <c r="G51" s="4" t="s">
+      <c r="G51" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29941,7 +29953,7 @@
       <c r="F52" s="5">
         <v>7073</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="G52" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29964,7 +29976,7 @@
       <c r="F53" s="5">
         <v>14694</v>
       </c>
-      <c r="G53" s="4" t="s">
+      <c r="G53" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -29987,7 +29999,7 @@
       <c r="F54" s="5">
         <v>7579</v>
       </c>
-      <c r="G54" s="4" t="s">
+      <c r="G54" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -30010,7 +30022,7 @@
       <c r="F55" s="5">
         <v>16418</v>
       </c>
-      <c r="G55" s="4" t="s">
+      <c r="G55" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -30033,7 +30045,7 @@
       <c r="F56" s="5">
         <v>25330</v>
       </c>
-      <c r="G56" s="4" t="s">
+      <c r="G56" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -30056,7 +30068,7 @@
       <c r="F57" s="5">
         <v>23706</v>
       </c>
-      <c r="G57" s="4" t="s">
+      <c r="G57" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -30079,7 +30091,7 @@
       <c r="F58" s="5">
         <v>4211</v>
       </c>
-      <c r="G58" s="4" t="s">
+      <c r="G58" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -30102,7 +30114,7 @@
       <c r="F59" s="5">
         <v>6675</v>
       </c>
-      <c r="G59" s="4" t="s">
+      <c r="G59" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -30125,7 +30137,7 @@
       <c r="F60" s="5">
         <v>7148</v>
       </c>
-      <c r="G60" s="4" t="s">
+      <c r="G60" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -30171,7 +30183,7 @@
       <c r="F62" s="5">
         <v>21418</v>
       </c>
-      <c r="G62" s="4" t="s">
+      <c r="G62" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -30194,7 +30206,7 @@
       <c r="F63" s="5">
         <v>15700</v>
       </c>
-      <c r="G63" s="4" t="s">
+      <c r="G63" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -30214,10 +30226,10 @@
       <c r="E64">
         <v>200</v>
       </c>
-      <c r="F64" s="6">
+      <c r="F64" s="7">
         <v>5</v>
       </c>
-      <c r="G64" s="4" t="s">
+      <c r="G64" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -30240,7 +30252,7 @@
       <c r="F65" s="5">
         <v>5330</v>
       </c>
-      <c r="G65" s="4" t="s">
+      <c r="G65" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -30263,7 +30275,7 @@
       <c r="F66" s="5">
         <v>7647</v>
       </c>
-      <c r="G66" s="4" t="s">
+      <c r="G66" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -30286,7 +30298,7 @@
       <c r="F67" s="5">
         <v>33838</v>
       </c>
-      <c r="G67" s="4" t="s">
+      <c r="G67" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -30309,7 +30321,7 @@
       <c r="F68" s="5">
         <v>44</v>
       </c>
-      <c r="G68" s="4" t="s">
+      <c r="G68" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -30332,7 +30344,7 @@
       <c r="F69" s="5">
         <v>25179</v>
       </c>
-      <c r="G69" s="4" t="s">
+      <c r="G69" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -30355,7 +30367,7 @@
       <c r="F70" s="5">
         <v>11081</v>
       </c>
-      <c r="G70" s="4" t="s">
+      <c r="G70" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -30378,7 +30390,7 @@
       <c r="F71" s="5">
         <v>1246</v>
       </c>
-      <c r="G71" s="4" t="s">
+      <c r="G71" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -30398,10 +30410,10 @@
       <c r="E72">
         <v>200</v>
       </c>
-      <c r="F72" s="6">
+      <c r="F72" s="7">
         <v>5</v>
       </c>
-      <c r="G72" s="4" t="s">
+      <c r="G72" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -30447,7 +30459,7 @@
       <c r="F74" s="5">
         <v>932</v>
       </c>
-      <c r="G74" s="4" t="s">
+      <c r="G74" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -30493,7 +30505,7 @@
       <c r="F76" s="5">
         <v>61218</v>
       </c>
-      <c r="G76" s="4" t="s">
+      <c r="G76" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -30562,7 +30574,7 @@
       <c r="F79" s="5">
         <v>1865</v>
       </c>
-      <c r="G79" s="4" t="s">
+      <c r="G79" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -30582,10 +30594,10 @@
       <c r="E80">
         <v>200</v>
       </c>
-      <c r="F80" s="6">
+      <c r="F80" s="7">
         <v>3</v>
       </c>
-      <c r="G80" s="4" t="s">
+      <c r="G80" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -30631,7 +30643,7 @@
       <c r="F82" s="5">
         <v>64226</v>
       </c>
-      <c r="G82" s="4" t="s">
+      <c r="G82" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -30654,7 +30666,7 @@
       <c r="F83" s="5">
         <v>227</v>
       </c>
-      <c r="G83" s="4" t="s">
+      <c r="G83" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -30674,10 +30686,10 @@
       <c r="E84">
         <v>1152</v>
       </c>
-      <c r="F84" s="6">
+      <c r="F84" s="7">
         <v>7</v>
       </c>
-      <c r="G84" s="4" t="s">
+      <c r="G84" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -30700,7 +30712,7 @@
       <c r="F85" s="5">
         <v>3385</v>
       </c>
-      <c r="G85" s="4" t="s">
+      <c r="G85" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -30723,7 +30735,7 @@
       <c r="F86" s="5">
         <v>20494</v>
       </c>
-      <c r="G86" s="4" t="s">
+      <c r="G86" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -30746,7 +30758,7 @@
       <c r="F87" s="5">
         <v>4143</v>
       </c>
-      <c r="G87" s="4" t="s">
+      <c r="G87" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -30769,7 +30781,7 @@
       <c r="F88" s="5">
         <v>5653</v>
       </c>
-      <c r="G88" s="4" t="s">
+      <c r="G88" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -30792,7 +30804,7 @@
       <c r="F89" s="5">
         <v>207</v>
       </c>
-      <c r="G89" s="4" t="s">
+      <c r="G89" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -30815,7 +30827,7 @@
       <c r="F90" s="5">
         <v>1132</v>
       </c>
-      <c r="G90" s="4" t="s">
+      <c r="G90" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -30835,10 +30847,10 @@
       <c r="E91">
         <v>576</v>
       </c>
-      <c r="F91" s="6">
+      <c r="F91" s="7">
         <v>3</v>
       </c>
-      <c r="G91" s="4" t="s">
+      <c r="G91" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -30861,7 +30873,7 @@
       <c r="F92" s="5">
         <v>5395</v>
       </c>
-      <c r="G92" s="4" t="s">
+      <c r="G92" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -30884,7 +30896,7 @@
       <c r="F93" s="5">
         <v>14255</v>
       </c>
-      <c r="G93" s="4" t="s">
+      <c r="G93" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -30904,10 +30916,10 @@
       <c r="E94">
         <v>576</v>
       </c>
-      <c r="F94" s="6">
+      <c r="F94" s="7">
         <v>4</v>
       </c>
-      <c r="G94" s="4" t="s">
+      <c r="G94" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -30953,7 +30965,7 @@
       <c r="F96" s="5">
         <v>189585</v>
       </c>
-      <c r="G96" s="4" t="s">
+      <c r="G96" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -30976,7 +30988,7 @@
       <c r="F97" s="5">
         <v>25960</v>
       </c>
-      <c r="G97" s="4" t="s">
+      <c r="G97" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -30999,7 +31011,7 @@
       <c r="F98" s="5">
         <v>233</v>
       </c>
-      <c r="G98" s="4" t="s">
+      <c r="G98" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31045,7 +31057,7 @@
       <c r="F100" s="5">
         <v>15999</v>
       </c>
-      <c r="G100" s="4" t="s">
+      <c r="G100" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31065,10 +31077,10 @@
       <c r="E101">
         <v>144</v>
       </c>
-      <c r="F101" s="6">
+      <c r="F101" s="7">
         <v>2</v>
       </c>
-      <c r="G101" s="4" t="s">
+      <c r="G101" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -31091,7 +31103,7 @@
       <c r="F102" s="5">
         <v>19642</v>
       </c>
-      <c r="G102" s="4" t="s">
+      <c r="G102" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31114,7 +31126,7 @@
       <c r="F103" s="5">
         <v>17836</v>
       </c>
-      <c r="G103" s="4" t="s">
+      <c r="G103" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31137,7 +31149,7 @@
       <c r="F104" s="5">
         <v>8023</v>
       </c>
-      <c r="G104" s="4" t="s">
+      <c r="G104" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31160,7 +31172,7 @@
       <c r="F105" s="5">
         <v>7186</v>
       </c>
-      <c r="G105" s="4" t="s">
+      <c r="G105" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31206,7 +31218,7 @@
       <c r="F107" s="5">
         <v>21533</v>
       </c>
-      <c r="G107" s="4" t="s">
+      <c r="G107" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31229,7 +31241,7 @@
       <c r="F108" s="5">
         <v>3610</v>
       </c>
-      <c r="G108" s="4" t="s">
+      <c r="G108" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31252,7 +31264,7 @@
       <c r="F109" s="5">
         <v>20645</v>
       </c>
-      <c r="G109" s="4" t="s">
+      <c r="G109" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31275,7 +31287,7 @@
       <c r="F110" s="5">
         <v>1359</v>
       </c>
-      <c r="G110" s="4" t="s">
+      <c r="G110" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31298,7 +31310,7 @@
       <c r="F111" s="5">
         <v>25522</v>
       </c>
-      <c r="G111" s="4" t="s">
+      <c r="G111" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31321,7 +31333,7 @@
       <c r="F112" s="5">
         <v>4391</v>
       </c>
-      <c r="G112" s="4" t="s">
+      <c r="G112" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31344,7 +31356,7 @@
       <c r="F113" s="5">
         <v>29516</v>
       </c>
-      <c r="G113" s="4" t="s">
+      <c r="G113" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31367,7 +31379,7 @@
       <c r="F114" s="5">
         <v>6541</v>
       </c>
-      <c r="G114" s="4" t="s">
+      <c r="G114" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31390,7 +31402,7 @@
       <c r="F115" s="5">
         <v>16122</v>
       </c>
-      <c r="G115" s="4" t="s">
+      <c r="G115" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31413,7 +31425,7 @@
       <c r="F116" s="5">
         <v>8627</v>
       </c>
-      <c r="G116" s="4" t="s">
+      <c r="G116" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31436,7 +31448,7 @@
       <c r="F117" s="5">
         <v>65</v>
       </c>
-      <c r="G117" s="4" t="s">
+      <c r="G117" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31459,7 +31471,7 @@
       <c r="F118" s="5">
         <v>4019</v>
       </c>
-      <c r="G118" s="4" t="s">
+      <c r="G118" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31505,7 +31517,7 @@
       <c r="F120" s="5">
         <v>788</v>
       </c>
-      <c r="G120" s="4" t="s">
+      <c r="G120" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31528,7 +31540,7 @@
       <c r="F121" s="5">
         <v>137</v>
       </c>
-      <c r="G121" s="4" t="s">
+      <c r="G121" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31551,7 +31563,7 @@
       <c r="F122" s="5">
         <v>2530</v>
       </c>
-      <c r="G122" s="4" t="s">
+      <c r="G122" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31574,7 +31586,7 @@
       <c r="F123" s="5">
         <v>23601</v>
       </c>
-      <c r="G123" s="4" t="s">
+      <c r="G123" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31597,7 +31609,7 @@
       <c r="F124" s="5">
         <v>5178</v>
       </c>
-      <c r="G124" s="4" t="s">
+      <c r="G124" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31620,7 +31632,7 @@
       <c r="F125" s="5">
         <v>6331</v>
       </c>
-      <c r="G125" s="4" t="s">
+      <c r="G125" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31643,7 +31655,7 @@
       <c r="F126" s="5">
         <v>3057</v>
       </c>
-      <c r="G126" s="4" t="s">
+      <c r="G126" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31666,7 +31678,7 @@
       <c r="F127" s="5">
         <v>10991</v>
       </c>
-      <c r="G127" s="4" t="s">
+      <c r="G127" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31689,7 +31701,7 @@
       <c r="F128" s="5">
         <v>8737</v>
       </c>
-      <c r="G128" s="4" t="s">
+      <c r="G128" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31712,7 +31724,7 @@
       <c r="F129" s="5">
         <v>3244</v>
       </c>
-      <c r="G129" s="4" t="s">
+      <c r="G129" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31735,7 +31747,7 @@
       <c r="F130" s="5">
         <v>43733</v>
       </c>
-      <c r="G130" s="4" t="s">
+      <c r="G130" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31758,7 +31770,7 @@
       <c r="F131" s="5">
         <v>287</v>
       </c>
-      <c r="G131" s="4" t="s">
+      <c r="G131" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31781,7 +31793,7 @@
       <c r="F132" s="5">
         <v>8436</v>
       </c>
-      <c r="G132" s="4" t="s">
+      <c r="G132" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31804,7 +31816,7 @@
       <c r="F133" s="5">
         <v>185</v>
       </c>
-      <c r="G133" s="4" t="s">
+      <c r="G133" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31827,7 +31839,7 @@
       <c r="F134" s="5">
         <v>6726</v>
       </c>
-      <c r="G134" s="4" t="s">
+      <c r="G134" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31850,7 +31862,7 @@
       <c r="F135" s="5">
         <v>12048</v>
       </c>
-      <c r="G135" s="4" t="s">
+      <c r="G135" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31873,7 +31885,7 @@
       <c r="F136" s="5">
         <v>2895</v>
       </c>
-      <c r="G136" s="4" t="s">
+      <c r="G136" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31896,7 +31908,7 @@
       <c r="F137" s="5">
         <v>108</v>
       </c>
-      <c r="G137" s="4" t="s">
+      <c r="G137" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31919,7 +31931,7 @@
       <c r="F138" s="5">
         <v>99</v>
       </c>
-      <c r="G138" s="4" t="s">
+      <c r="G138" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31942,7 +31954,7 @@
       <c r="F139" s="5">
         <v>125</v>
       </c>
-      <c r="G139" s="4" t="s">
+      <c r="G139" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31965,7 +31977,7 @@
       <c r="F140" s="5">
         <v>17</v>
       </c>
-      <c r="G140" s="4" t="s">
+      <c r="G140" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -31988,7 +32000,7 @@
       <c r="F141" s="5">
         <v>114</v>
       </c>
-      <c r="G141" s="4" t="s">
+      <c r="G141" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -32011,7 +32023,7 @@
       <c r="F142" s="5">
         <v>126</v>
       </c>
-      <c r="G142" s="4" t="s">
+      <c r="G142" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -32034,7 +32046,7 @@
       <c r="F143" s="5">
         <v>42</v>
       </c>
-      <c r="G143" s="4" t="s">
+      <c r="G143" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -32057,7 +32069,7 @@
       <c r="F144" s="5">
         <v>58</v>
       </c>
-      <c r="G144" s="4" t="s">
+      <c r="G144" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -32073,13 +32085,12 @@
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -32124,7 +32135,7 @@
       <c r="F2" s="5">
         <v>75321</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -32147,7 +32158,7 @@
       <c r="F3" s="5">
         <v>217243</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -32170,7 +32181,7 @@
       <c r="F4" s="5">
         <v>83362</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -32216,7 +32227,7 @@
       <c r="F6" s="5">
         <v>3927</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -32239,7 +32250,7 @@
       <c r="F7" s="5">
         <v>9975</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -32262,7 +32273,7 @@
       <c r="F8" s="5">
         <v>70240</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -32285,7 +32296,7 @@
       <c r="F9" s="5">
         <v>83953</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -32308,7 +32319,7 @@
       <c r="F10" s="5">
         <v>23800</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -32331,7 +32342,7 @@
       <c r="F11" s="5">
         <v>29904</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -32354,7 +32365,7 @@
       <c r="F12" s="5">
         <v>25578</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -32377,7 +32388,7 @@
       <c r="F13" s="5">
         <v>130113</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -32400,7 +32411,7 @@
       <c r="F14" s="5">
         <v>114396</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -32416,13 +32427,12 @@
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -32467,7 +32477,7 @@
       <c r="F2" s="5">
         <v>120536</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -32490,7 +32500,7 @@
       <c r="F3" s="5">
         <v>216410</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -32513,7 +32523,7 @@
       <c r="F4" s="5">
         <v>67049</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -32536,7 +32546,7 @@
       <c r="F5" s="5">
         <v>32978</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -32552,13 +32562,12 @@
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -32603,7 +32612,7 @@
       <c r="F2" s="5">
         <v>3022</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -32626,7 +32635,7 @@
       <c r="F3" s="5">
         <v>286</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -32649,7 +32658,7 @@
       <c r="F4" s="5">
         <v>157</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -32672,7 +32681,7 @@
       <c r="F5" s="5">
         <v>654</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -32692,10 +32701,10 @@
       <c r="E6">
         <v>18</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="7">
         <v>4</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -32718,7 +32727,7 @@
       <c r="F7" s="5">
         <v>1156</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -32741,7 +32750,7 @@
       <c r="F8" s="5">
         <v>1901</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -32764,7 +32773,7 @@
       <c r="F9" s="5">
         <v>1913</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="6" t="s">
         <v>29</v>
       </c>
     </row>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -32,7 +32,7 @@
     <t>Actualización:</t>
   </si>
   <si>
-    <t>7/3/2026, 10:24:36 p. m.</t>
+    <t>7/3/2026, 11:01:03 p. m.</t>
   </si>
   <si>
     <t>ACCESORIOS</t>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -32,7 +32,7 @@
     <t>Actualización:</t>
   </si>
   <si>
-    <t>07/03/2026, 19:46:36</t>
+    <t>07/03/2026, 21:09:26</t>
   </si>
   <si>
     <t>TOTAL GENERAL:</t>
@@ -53,7 +53,7 @@
     <t>ACCESORIOS</t>
   </si>
   <si>
-    <t>95 códigos, 984,026 unidades</t>
+    <t>95 códigos, 983,882 unidades</t>
   </si>
   <si>
     <t>ARCHIVO</t>
@@ -71,7 +71,7 @@
     <t>DIDACTICOS</t>
   </si>
   <si>
-    <t>31 códigos, 27,335 unidades</t>
+    <t>31 códigos, 27,311 unidades</t>
   </si>
   <si>
     <t>ESCRITURA</t>
@@ -83,7 +83,7 @@
     <t>FORROS</t>
   </si>
   <si>
-    <t>13 códigos, 867,812 unidades</t>
+    <t>13 códigos, 867,387 unidades</t>
   </si>
   <si>
     <t>MANUALIDADES</t>
@@ -119,7 +119,7 @@
     <t>PINTURA</t>
   </si>
   <si>
-    <t>76 códigos, 1,246,296 unidades</t>
+    <t>76 códigos, 1,246,008 unidades</t>
   </si>
   <si>
     <t>REPRESENTADAS</t>
@@ -9951,7 +9951,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2">
-        <v>8619761</v>
+        <v>8618880</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -16855,7 +16855,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="6">
-        <v>49384</v>
+        <v>49096</v>
       </c>
       <c r="G48" s="7" t="s">
         <v>48</v>
@@ -23036,7 +23036,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="6">
-        <v>7902</v>
+        <v>7758</v>
       </c>
       <c r="G41" s="7" t="s">
         <v>48</v>
@@ -30916,7 +30916,7 @@
         <v>12</v>
       </c>
       <c r="F2" s="6">
-        <v>1184</v>
+        <v>1172</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>48</v>
@@ -30985,7 +30985,7 @@
         <v>12</v>
       </c>
       <c r="F5" s="6">
-        <v>874</v>
+        <v>862</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>48</v>
@@ -35096,7 +35096,7 @@
         <v>25</v>
       </c>
       <c r="F6" s="6">
-        <v>3927</v>
+        <v>3627</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>48</v>
@@ -35234,7 +35234,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="6">
-        <v>25578</v>
+        <v>25453</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>48</v>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -32,7 +32,7 @@
     <t>Actualización:</t>
   </si>
   <si>
-    <t>07/03/2026, 21:09:26</t>
+    <t>07/03/2026, 22:20:47</t>
   </si>
   <si>
     <t>TOTAL GENERAL:</t>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -32,7 +32,7 @@
     <t>Actualización:</t>
   </si>
   <si>
-    <t>07/03/2026, 22:20:47</t>
+    <t>07/03/2026, 22:32:03</t>
   </si>
   <si>
     <t>TOTAL GENERAL:</t>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 07/03/2026, 23:56:18</t>
+    <t>Actualización: 08/03/2026, 24:11:38</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>
@@ -41,7 +41,7 @@
     <t>Unidades:</t>
   </si>
   <si>
-    <t>8,619,761</t>
+    <t>8,618,880</t>
   </si>
   <si>
     <t>Agotados:</t>
@@ -68,7 +68,7 @@
     <t>ACCESORIOS</t>
   </si>
   <si>
-    <t>984,026</t>
+    <t>983,882</t>
   </si>
   <si>
     <t>11.4%</t>
@@ -95,7 +95,7 @@
     <t>DIDACTICOS</t>
   </si>
   <si>
-    <t>27,335</t>
+    <t>27,311</t>
   </si>
   <si>
     <t>0.3%</t>
@@ -113,7 +113,7 @@
     <t>FORROS</t>
   </si>
   <si>
-    <t>867,812</t>
+    <t>867,387</t>
   </si>
   <si>
     <t>10.1%</t>
@@ -167,7 +167,7 @@
     <t>PINTURA</t>
   </si>
   <si>
-    <t>1,246,296</t>
+    <t>1,246,008</t>
   </si>
   <si>
     <t>14.5%</t>
@@ -17248,7 +17248,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="34">
-        <v>49384</v>
+        <v>49096</v>
       </c>
       <c r="G48" s="35" t="s">
         <v>69</v>
@@ -23429,7 +23429,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="34">
-        <v>7902</v>
+        <v>7758</v>
       </c>
       <c r="G41" s="35" t="s">
         <v>69</v>
@@ -31309,7 +31309,7 @@
         <v>12</v>
       </c>
       <c r="F2" s="34">
-        <v>1184</v>
+        <v>1172</v>
       </c>
       <c r="G2" s="35" t="s">
         <v>69</v>
@@ -31378,7 +31378,7 @@
         <v>12</v>
       </c>
       <c r="F5" s="34">
-        <v>874</v>
+        <v>862</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>69</v>
@@ -35489,7 +35489,7 @@
         <v>25</v>
       </c>
       <c r="F6" s="34">
-        <v>3927</v>
+        <v>3627</v>
       </c>
       <c r="G6" s="35" t="s">
         <v>69</v>
@@ -35627,7 +35627,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="34">
-        <v>25578</v>
+        <v>25453</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>69</v>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 08/03/2026, 24:11:38</t>
+    <t>Actualización: 08/03/2026, 07:40:55</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 08/03/2026, 07:40:55</t>
+    <t>Actualización: 08/03/2026, 08:37:30</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 08/03/2026, 08:37:30</t>
+    <t>Actualización: 08/03/2026, 09:21:49</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 08/03/2026, 09:21:49</t>
+    <t>Actualización: 08/03/2026, 10:20:29</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 08/03/2026, 13:29:05</t>
+    <t>Actualización: 08/03/2026, 14:20:52</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 08/03/2026, 14:20:52</t>
+    <t>Actualización: 08/03/2026, 15:21:56</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 08/03/2026, 15:21:56</t>
+    <t>Actualización: 08/03/2026, 16:19:58</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 08/03/2026, 18:20:06</t>
+    <t>Actualización: 08/03/2026, 21:37:02</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 09/03/2026, 09:29:49</t>
+    <t>Actualización: 09/03/2026, 09:51:53</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>
@@ -41,7 +41,7 @@
     <t>Unidades:</t>
   </si>
   <si>
-    <t>8,618,146</t>
+    <t>8,618,135</t>
   </si>
   <si>
     <t>Agotados:</t>
@@ -68,7 +68,7 @@
     <t>ACCESORIOS</t>
   </si>
   <si>
-    <t>983,740</t>
+    <t>983,739</t>
   </si>
   <si>
     <t>11.4%</t>
@@ -86,7 +86,7 @@
     <t>DIBUJO</t>
   </si>
   <si>
-    <t>121,826</t>
+    <t>121,824</t>
   </si>
   <si>
     <t>1.4%</t>
@@ -104,7 +104,7 @@
     <t>ESCRITURA</t>
   </si>
   <si>
-    <t>1,461,386</t>
+    <t>1,461,384</t>
   </si>
   <si>
     <t>17.0%</t>
@@ -149,7 +149,7 @@
     <t>PEGAMENTOS</t>
   </si>
   <si>
-    <t>634,544</t>
+    <t>634,542</t>
   </si>
   <si>
     <t>7.4%</t>
@@ -167,7 +167,7 @@
     <t>PINTURA</t>
   </si>
   <si>
-    <t>1,245,981</t>
+    <t>1,245,977</t>
   </si>
   <si>
     <t>14.5%</t>
@@ -10217,13 +10217,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="6">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11573,7 +11573,7 @@
         <v>48</v>
       </c>
       <c r="F16" s="34">
-        <v>16218</v>
+        <v>16216</v>
       </c>
       <c r="G16" s="35" t="s">
         <v>69</v>
@@ -13801,7 +13801,7 @@
         <v>60</v>
       </c>
       <c r="F90" s="34">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="G90" s="35" t="s">
         <v>69</v>
@@ -13824,7 +13824,7 @@
         <v>60</v>
       </c>
       <c r="F91" s="34">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="G91" s="35" t="s">
         <v>69</v>
@@ -13870,7 +13870,7 @@
         <v>60</v>
       </c>
       <c r="F93" s="34">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="G93" s="35" t="s">
         <v>69</v>
@@ -13893,7 +13893,7 @@
         <v>60</v>
       </c>
       <c r="F94" s="34">
-        <v>1390</v>
+        <v>1394</v>
       </c>
       <c r="G94" s="35" t="s">
         <v>69</v>
@@ -13915,11 +13915,11 @@
       <c r="E95">
         <v>60</v>
       </c>
-      <c r="F95" s="32">
-        <v>0</v>
-      </c>
-      <c r="G95" s="33" t="s">
-        <v>65</v>
+      <c r="F95" s="36">
+        <v>1</v>
+      </c>
+      <c r="G95" s="37" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -16328,7 +16328,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="34">
-        <v>15579</v>
+        <v>15578</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>
@@ -16558,7 +16558,7 @@
         <v>72</v>
       </c>
       <c r="F18" s="34">
-        <v>8012</v>
+        <v>8011</v>
       </c>
       <c r="G18" s="35" t="s">
         <v>69</v>
@@ -16673,7 +16673,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="34">
-        <v>13509</v>
+        <v>13508</v>
       </c>
       <c r="G23" s="35" t="s">
         <v>69</v>
@@ -17271,7 +17271,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="34">
-        <v>38451</v>
+        <v>38450</v>
       </c>
       <c r="G49" s="35" t="s">
         <v>69</v>
@@ -23429,7 +23429,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="34">
-        <v>7743</v>
+        <v>7742</v>
       </c>
       <c r="G41" s="35" t="s">
         <v>69</v>
@@ -31059,7 +31059,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="34">
-        <v>40774</v>
+        <v>40773</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>69</v>
@@ -31220,7 +31220,7 @@
         <v>200</v>
       </c>
       <c r="F16" s="34">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="G16" s="35" t="s">
         <v>69</v>
@@ -32088,7 +32088,7 @@
         <v>144</v>
       </c>
       <c r="F3" s="34">
-        <v>37794</v>
+        <v>37793</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -32571,7 +32571,7 @@
         <v>96</v>
       </c>
       <c r="F24" s="34">
-        <v>3512</v>
+        <v>3511</v>
       </c>
       <c r="G24" s="35" t="s">
         <v>69</v>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 09/03/2026, 13:53:44</t>
+    <t>Actualización: 09/03/2026, 14:40:44</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>
@@ -41,7 +41,7 @@
     <t>Unidades:</t>
   </si>
   <si>
-    <t>8,583,451</t>
+    <t>8,582,229</t>
   </si>
   <si>
     <t>Agotados:</t>
@@ -68,7 +68,7 @@
     <t>ACCESORIOS</t>
   </si>
   <si>
-    <t>976,033</t>
+    <t>975,601</t>
   </si>
   <si>
     <t>11.4%</t>
@@ -77,7 +77,7 @@
     <t>ARCHIVO</t>
   </si>
   <si>
-    <t>1,752,614</t>
+    <t>1,750,764</t>
   </si>
   <si>
     <t>20.4%</t>
@@ -86,7 +86,7 @@
     <t>DIBUJO</t>
   </si>
   <si>
-    <t>117,649</t>
+    <t>116,649</t>
   </si>
   <si>
     <t>1.4%</t>
@@ -104,10 +104,10 @@
     <t>ESCRITURA</t>
   </si>
   <si>
-    <t>1,453,492</t>
-  </si>
-  <si>
-    <t>16.9%</t>
+    <t>1,454,904</t>
+  </si>
+  <si>
+    <t>17.0%</t>
   </si>
   <si>
     <t>FORROS</t>
@@ -122,7 +122,7 @@
     <t>MANUALIDADES</t>
   </si>
   <si>
-    <t>435,893</t>
+    <t>435,701</t>
   </si>
   <si>
     <t>5.1%</t>
@@ -149,16 +149,16 @@
     <t>PEGAMENTOS</t>
   </si>
   <si>
-    <t>628,873</t>
-  </si>
-  <si>
-    <t>7.3%</t>
+    <t>630,873</t>
+  </si>
+  <si>
+    <t>7.4%</t>
   </si>
   <si>
     <t>PELOTAS</t>
   </si>
   <si>
-    <t>480,148</t>
+    <t>479,724</t>
   </si>
   <si>
     <t>5.6%</t>
@@ -167,7 +167,7 @@
     <t>PINTURA</t>
   </si>
   <si>
-    <t>1,243,751</t>
+    <t>1,243,015</t>
   </si>
   <si>
     <t>14.5%</t>
@@ -10217,13 +10217,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="6">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11665,7 +11665,7 @@
         <v>144</v>
       </c>
       <c r="F20" s="34">
-        <v>14675</v>
+        <v>16675</v>
       </c>
       <c r="G20" s="35" t="s">
         <v>69</v>
@@ -12605,7 +12605,7 @@
         <v>48</v>
       </c>
       <c r="F38" s="34">
-        <v>1483</v>
+        <v>1435</v>
       </c>
       <c r="G38" s="35" t="s">
         <v>69</v>
@@ -12674,7 +12674,7 @@
         <v>48</v>
       </c>
       <c r="F41" s="36">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G41" s="37" t="s">
         <v>109</v>
@@ -12743,7 +12743,7 @@
         <v>48</v>
       </c>
       <c r="F44" s="34">
-        <v>6499</v>
+        <v>6450</v>
       </c>
       <c r="G44" s="35" t="s">
         <v>69</v>
@@ -12812,7 +12812,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="34">
-        <v>11847</v>
+        <v>11798</v>
       </c>
       <c r="G47" s="35" t="s">
         <v>69</v>
@@ -12881,7 +12881,7 @@
         <v>48</v>
       </c>
       <c r="F50" s="34">
-        <v>5570</v>
+        <v>5474</v>
       </c>
       <c r="G50" s="35" t="s">
         <v>69</v>
@@ -12927,7 +12927,7 @@
         <v>48</v>
       </c>
       <c r="F52" s="36">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G52" s="37" t="s">
         <v>109</v>
@@ -12949,11 +12949,11 @@
       <c r="E53">
         <v>48</v>
       </c>
-      <c r="F53" s="36">
-        <v>5</v>
-      </c>
-      <c r="G53" s="37" t="s">
-        <v>109</v>
+      <c r="F53" s="34">
+        <v>294</v>
+      </c>
+      <c r="G53" s="35" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -12996,7 +12996,7 @@
         <v>36</v>
       </c>
       <c r="F55" s="34">
-        <v>2218</v>
+        <v>2182</v>
       </c>
       <c r="G55" s="35" t="s">
         <v>69</v>
@@ -13272,7 +13272,7 @@
         <v>60</v>
       </c>
       <c r="F67" s="34">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="G67" s="35" t="s">
         <v>69</v>
@@ -13433,7 +13433,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="34">
-        <v>1299</v>
+        <v>1269</v>
       </c>
       <c r="G74" s="35" t="s">
         <v>69</v>
@@ -13456,7 +13456,7 @@
         <v>60</v>
       </c>
       <c r="F75" s="34">
-        <v>4399</v>
+        <v>4369</v>
       </c>
       <c r="G75" s="35" t="s">
         <v>69</v>
@@ -13548,7 +13548,7 @@
         <v>60</v>
       </c>
       <c r="F79" s="34">
-        <v>5202</v>
+        <v>5172</v>
       </c>
       <c r="G79" s="35" t="s">
         <v>69</v>
@@ -13617,7 +13617,7 @@
         <v>60</v>
       </c>
       <c r="F82" s="34">
-        <v>1124</v>
+        <v>1094</v>
       </c>
       <c r="G82" s="35" t="s">
         <v>69</v>
@@ -13847,7 +13847,7 @@
         <v>60</v>
       </c>
       <c r="F92" s="34">
-        <v>1369</v>
+        <v>1349</v>
       </c>
       <c r="G92" s="35" t="s">
         <v>69</v>
@@ -13870,7 +13870,7 @@
         <v>60</v>
       </c>
       <c r="F93" s="34">
-        <v>1239</v>
+        <v>1219</v>
       </c>
       <c r="G93" s="35" t="s">
         <v>69</v>
@@ -13893,7 +13893,7 @@
         <v>60</v>
       </c>
       <c r="F94" s="34">
-        <v>1394</v>
+        <v>1374</v>
       </c>
       <c r="G94" s="35" t="s">
         <v>69</v>
@@ -13939,7 +13939,7 @@
         <v>60</v>
       </c>
       <c r="F96" s="34">
-        <v>2485</v>
+        <v>2455</v>
       </c>
       <c r="G96" s="35" t="s">
         <v>69</v>
@@ -13985,7 +13985,7 @@
         <v>60</v>
       </c>
       <c r="F98" s="34">
-        <v>3432</v>
+        <v>3401</v>
       </c>
       <c r="G98" s="35" t="s">
         <v>69</v>
@@ -14031,7 +14031,7 @@
         <v>60</v>
       </c>
       <c r="F100" s="34">
-        <v>1543</v>
+        <v>1513</v>
       </c>
       <c r="G100" s="35" t="s">
         <v>69</v>
@@ -14215,7 +14215,7 @@
         <v>60</v>
       </c>
       <c r="F108" s="34">
-        <v>2999</v>
+        <v>2969</v>
       </c>
       <c r="G108" s="35" t="s">
         <v>69</v>
@@ -14238,7 +14238,7 @@
         <v>60</v>
       </c>
       <c r="F109" s="34">
-        <v>1728</v>
+        <v>1668</v>
       </c>
       <c r="G109" s="35" t="s">
         <v>69</v>
@@ -14307,7 +14307,7 @@
         <v>60</v>
       </c>
       <c r="F112" s="34">
-        <v>7097</v>
+        <v>7067</v>
       </c>
       <c r="G112" s="35" t="s">
         <v>69</v>
@@ -14330,7 +14330,7 @@
         <v>60</v>
       </c>
       <c r="F113" s="34">
-        <v>6609</v>
+        <v>6549</v>
       </c>
       <c r="G113" s="35" t="s">
         <v>69</v>
@@ -14353,7 +14353,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="34">
-        <v>11106</v>
+        <v>11076</v>
       </c>
       <c r="G114" s="35" t="s">
         <v>69</v>
@@ -14950,11 +14950,11 @@
       <c r="E140">
         <v>120</v>
       </c>
-      <c r="F140" s="32">
-        <v>0</v>
-      </c>
-      <c r="G140" s="33" t="s">
-        <v>65</v>
+      <c r="F140" s="34">
+        <v>870</v>
+      </c>
+      <c r="G140" s="35" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -15089,7 +15089,7 @@
         <v>60</v>
       </c>
       <c r="F146" s="34">
-        <v>743</v>
+        <v>683</v>
       </c>
       <c r="G146" s="35" t="s">
         <v>69</v>
@@ -15640,11 +15640,11 @@
       <c r="E170">
         <v>120</v>
       </c>
-      <c r="F170" s="32">
-        <v>0</v>
-      </c>
-      <c r="G170" s="33" t="s">
-        <v>65</v>
+      <c r="F170" s="36">
+        <v>43</v>
+      </c>
+      <c r="G170" s="37" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -15986,7 +15986,7 @@
         <v>400</v>
       </c>
       <c r="F185" s="34">
-        <v>76950</v>
+        <v>76550</v>
       </c>
       <c r="G185" s="35" t="s">
         <v>69</v>
@@ -16009,7 +16009,7 @@
         <v>400</v>
       </c>
       <c r="F186" s="34">
-        <v>72165</v>
+        <v>71765</v>
       </c>
       <c r="G186" s="35" t="s">
         <v>69</v>
@@ -16328,7 +16328,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="34">
-        <v>15505</v>
+        <v>15289</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>
@@ -16397,7 +16397,7 @@
         <v>144</v>
       </c>
       <c r="F11" s="34">
-        <v>53217</v>
+        <v>52785</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>69</v>
@@ -16696,7 +16696,7 @@
         <v>48</v>
       </c>
       <c r="F24" s="34">
-        <v>12442</v>
+        <v>12202</v>
       </c>
       <c r="G24" s="35" t="s">
         <v>69</v>
@@ -17271,7 +17271,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="34">
-        <v>37693</v>
+        <v>37845</v>
       </c>
       <c r="G49" s="35" t="s">
         <v>69</v>
@@ -23429,7 +23429,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="34">
-        <v>7442</v>
+        <v>7394</v>
       </c>
       <c r="G41" s="35" t="s">
         <v>69</v>
@@ -23567,7 +23567,7 @@
         <v>144</v>
       </c>
       <c r="F47" s="34">
-        <v>4054</v>
+        <v>4006</v>
       </c>
       <c r="G47" s="35" t="s">
         <v>69</v>
@@ -23590,7 +23590,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="34">
-        <v>10180</v>
+        <v>10132</v>
       </c>
       <c r="G48" s="35" t="s">
         <v>69</v>
@@ -23613,7 +23613,7 @@
         <v>144</v>
       </c>
       <c r="F49" s="34">
-        <v>15509</v>
+        <v>15461</v>
       </c>
       <c r="G49" s="35" t="s">
         <v>69</v>
@@ -23636,7 +23636,7 @@
         <v>144</v>
       </c>
       <c r="F50" s="34">
-        <v>5656</v>
+        <v>5608</v>
       </c>
       <c r="G50" s="35" t="s">
         <v>69</v>
@@ -23659,7 +23659,7 @@
         <v>144</v>
       </c>
       <c r="F51" s="34">
-        <v>5151</v>
+        <v>5079</v>
       </c>
       <c r="G51" s="35" t="s">
         <v>69</v>
@@ -23682,7 +23682,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="34">
-        <v>6526</v>
+        <v>6454</v>
       </c>
       <c r="G52" s="35" t="s">
         <v>69</v>
@@ -23705,7 +23705,7 @@
         <v>144</v>
       </c>
       <c r="F53" s="34">
-        <v>6337</v>
+        <v>6289</v>
       </c>
       <c r="G53" s="35" t="s">
         <v>69</v>
@@ -24783,7 +24783,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="34">
-        <v>46870</v>
+        <v>46970</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -24852,7 +24852,7 @@
         <v>50</v>
       </c>
       <c r="F6" s="34">
-        <v>18563</v>
+        <v>17813</v>
       </c>
       <c r="G6" s="35" t="s">
         <v>69</v>
@@ -24921,7 +24921,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="34">
-        <v>3743</v>
+        <v>3643</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>69</v>
@@ -24967,7 +24967,7 @@
         <v>50</v>
       </c>
       <c r="F11" s="34">
-        <v>5110</v>
+        <v>5010</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>69</v>
@@ -24990,7 +24990,7 @@
         <v>50</v>
       </c>
       <c r="F12" s="34">
-        <v>3109</v>
+        <v>3009</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>69</v>
@@ -25013,7 +25013,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="34">
-        <v>4475</v>
+        <v>4375</v>
       </c>
       <c r="G13" s="35" t="s">
         <v>69</v>
@@ -25035,11 +25035,11 @@
       <c r="E14">
         <v>50</v>
       </c>
-      <c r="F14" s="34">
-        <v>271</v>
-      </c>
-      <c r="G14" s="35" t="s">
-        <v>69</v>
+      <c r="F14" s="36">
+        <v>171</v>
+      </c>
+      <c r="G14" s="37" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -25059,7 +25059,7 @@
         <v>50</v>
       </c>
       <c r="F15" s="34">
-        <v>395</v>
+        <v>295</v>
       </c>
       <c r="G15" s="35" t="s">
         <v>69</v>
@@ -25082,7 +25082,7 @@
         <v>50</v>
       </c>
       <c r="F16" s="34">
-        <v>5117</v>
+        <v>5017</v>
       </c>
       <c r="G16" s="35" t="s">
         <v>69</v>
@@ -25105,7 +25105,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="34">
-        <v>8232</v>
+        <v>8132</v>
       </c>
       <c r="G17" s="35" t="s">
         <v>69</v>
@@ -25128,7 +25128,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="34">
-        <v>15719</v>
+        <v>15619</v>
       </c>
       <c r="G18" s="35" t="s">
         <v>69</v>
@@ -25151,7 +25151,7 @@
         <v>50</v>
       </c>
       <c r="F19" s="34">
-        <v>2347</v>
+        <v>2247</v>
       </c>
       <c r="G19" s="35" t="s">
         <v>69</v>
@@ -25197,7 +25197,7 @@
         <v>50</v>
       </c>
       <c r="F21" s="34">
-        <v>750</v>
+        <v>650</v>
       </c>
       <c r="G21" s="35" t="s">
         <v>69</v>
@@ -25220,7 +25220,7 @@
         <v>50</v>
       </c>
       <c r="F22" s="34">
-        <v>743</v>
+        <v>643</v>
       </c>
       <c r="G22" s="35" t="s">
         <v>69</v>
@@ -30921,7 +30921,7 @@
         <v>500</v>
       </c>
       <c r="F3" s="34">
-        <v>11065</v>
+        <v>10065</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -34227,7 +34227,7 @@
         <v>144</v>
       </c>
       <c r="F96" s="34">
-        <v>189582</v>
+        <v>190794</v>
       </c>
       <c r="G96" s="35" t="s">
         <v>69</v>
@@ -35331,7 +35331,7 @@
         <v>192</v>
       </c>
       <c r="F144" s="36">
-        <v>58</v>
+        <v>258</v>
       </c>
       <c r="G144" s="37" t="s">
         <v>109</v>
@@ -35739,7 +35739,7 @@
         <v>72</v>
       </c>
       <c r="F2" s="34">
-        <v>120176</v>
+        <v>120032</v>
       </c>
       <c r="G2" s="35" t="s">
         <v>69</v>
@@ -35762,7 +35762,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="34">
-        <v>215690</v>
+        <v>215642</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 09/03/2026, 14:40:44</t>
+    <t>Actualización: 09/03/2026, 15:34:57</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>
@@ -41,7 +41,7 @@
     <t>Unidades:</t>
   </si>
   <si>
-    <t>8,582,229</t>
+    <t>8,491,684</t>
   </si>
   <si>
     <t>Agotados:</t>
@@ -68,34 +68,34 @@
     <t>ACCESORIOS</t>
   </si>
   <si>
-    <t>975,601</t>
-  </si>
-  <si>
-    <t>11.4%</t>
+    <t>956,635</t>
+  </si>
+  <si>
+    <t>11.3%</t>
   </si>
   <si>
     <t>ARCHIVO</t>
   </si>
   <si>
-    <t>1,750,764</t>
-  </si>
-  <si>
-    <t>20.4%</t>
+    <t>1,750,444</t>
+  </si>
+  <si>
+    <t>20.6%</t>
   </si>
   <si>
     <t>DIBUJO</t>
   </si>
   <si>
-    <t>116,649</t>
-  </si>
-  <si>
-    <t>1.4%</t>
+    <t>110,249</t>
+  </si>
+  <si>
+    <t>1.3%</t>
   </si>
   <si>
     <t>DIDACTICOS</t>
   </si>
   <si>
-    <t>27,293</t>
+    <t>26,309</t>
   </si>
   <si>
     <t>0.3%</t>
@@ -104,16 +104,16 @@
     <t>ESCRITURA</t>
   </si>
   <si>
-    <t>1,454,904</t>
-  </si>
-  <si>
-    <t>17.0%</t>
+    <t>1,451,689</t>
+  </si>
+  <si>
+    <t>17.1%</t>
   </si>
   <si>
     <t>FORROS</t>
   </si>
   <si>
-    <t>879,610</t>
+    <t>864,280</t>
   </si>
   <si>
     <t>10.2%</t>
@@ -122,7 +122,7 @@
     <t>MANUALIDADES</t>
   </si>
   <si>
-    <t>435,701</t>
+    <t>432,101</t>
   </si>
   <si>
     <t>5.1%</t>
@@ -140,7 +140,7 @@
     <t>METALICA</t>
   </si>
   <si>
-    <t>259,755</t>
+    <t>255,755</t>
   </si>
   <si>
     <t>3.0%</t>
@@ -149,16 +149,16 @@
     <t>PEGAMENTOS</t>
   </si>
   <si>
-    <t>630,873</t>
-  </si>
-  <si>
-    <t>7.4%</t>
+    <t>598,905</t>
+  </si>
+  <si>
+    <t>7.1%</t>
   </si>
   <si>
     <t>PELOTAS</t>
   </si>
   <si>
-    <t>479,724</t>
+    <t>479,722</t>
   </si>
   <si>
     <t>5.6%</t>
@@ -167,10 +167,10 @@
     <t>PINTURA</t>
   </si>
   <si>
-    <t>1,243,015</t>
-  </si>
-  <si>
-    <t>14.5%</t>
+    <t>1,237,255</t>
+  </si>
+  <si>
+    <t>14.6%</t>
   </si>
   <si>
     <t>REPRESENTADAS</t>
@@ -179,7 +179,7 @@
     <t>319,247</t>
   </si>
   <si>
-    <t>3.7%</t>
+    <t>3.8%</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -10217,13 +10217,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="6">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -10794,7 +10794,7 @@
         <v>400</v>
       </c>
       <c r="F14" s="34">
-        <v>15802</v>
+        <v>11802</v>
       </c>
       <c r="G14" s="35" t="s">
         <v>69</v>
@@ -11481,7 +11481,7 @@
         <v>192</v>
       </c>
       <c r="F12" s="34">
-        <v>37974</v>
+        <v>34134</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>69</v>
@@ -11504,7 +11504,7 @@
         <v>576</v>
       </c>
       <c r="F13" s="34">
-        <v>92896</v>
+        <v>91168</v>
       </c>
       <c r="G13" s="35" t="s">
         <v>69</v>
@@ -11527,7 +11527,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="34">
-        <v>91771</v>
+        <v>82171</v>
       </c>
       <c r="G14" s="35" t="s">
         <v>69</v>
@@ -11550,7 +11550,7 @@
         <v>24</v>
       </c>
       <c r="F15" s="34">
-        <v>11105</v>
+        <v>1505</v>
       </c>
       <c r="G15" s="35" t="s">
         <v>69</v>
@@ -11573,7 +11573,7 @@
         <v>48</v>
       </c>
       <c r="F16" s="34">
-        <v>15916</v>
+        <v>8716</v>
       </c>
       <c r="G16" s="35" t="s">
         <v>69</v>
@@ -12812,7 +12812,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="34">
-        <v>11798</v>
+        <v>11797</v>
       </c>
       <c r="G47" s="35" t="s">
         <v>69</v>
@@ -16032,7 +16032,7 @@
         <v>120</v>
       </c>
       <c r="F187" s="34">
-        <v>3608</v>
+        <v>3607</v>
       </c>
       <c r="G187" s="35" t="s">
         <v>69</v>
@@ -16328,7 +16328,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="34">
-        <v>15289</v>
+        <v>14569</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>
@@ -16535,7 +16535,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="34">
-        <v>98101</v>
+        <v>95941</v>
       </c>
       <c r="G17" s="35" t="s">
         <v>69</v>
@@ -16558,7 +16558,7 @@
         <v>72</v>
       </c>
       <c r="F18" s="34">
-        <v>8011</v>
+        <v>6571</v>
       </c>
       <c r="G18" s="35" t="s">
         <v>69</v>
@@ -16696,7 +16696,7 @@
         <v>48</v>
       </c>
       <c r="F24" s="34">
-        <v>12202</v>
+        <v>10762</v>
       </c>
       <c r="G24" s="35" t="s">
         <v>69</v>
@@ -22693,7 +22693,7 @@
         <v>72</v>
       </c>
       <c r="F9" s="34">
-        <v>8629</v>
+        <v>8557</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>69</v>
@@ -22716,7 +22716,7 @@
         <v>120</v>
       </c>
       <c r="F10" s="34">
-        <v>11508</v>
+        <v>11268</v>
       </c>
       <c r="G10" s="35" t="s">
         <v>69</v>
@@ -23199,7 +23199,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="34">
-        <v>153771</v>
+        <v>139371</v>
       </c>
       <c r="G31" s="35" t="s">
         <v>69</v>
@@ -23245,7 +23245,7 @@
         <v>120</v>
       </c>
       <c r="F33" s="34">
-        <v>39992</v>
+        <v>39392</v>
       </c>
       <c r="G33" s="35" t="s">
         <v>69</v>
@@ -23291,7 +23291,7 @@
         <v>120</v>
       </c>
       <c r="F35" s="36">
-        <v>568</v>
+        <v>88</v>
       </c>
       <c r="G35" s="37" t="s">
         <v>109</v>
@@ -23314,7 +23314,7 @@
         <v>120</v>
       </c>
       <c r="F36" s="34">
-        <v>27575</v>
+        <v>26375</v>
       </c>
       <c r="G36" s="35" t="s">
         <v>69</v>
@@ -23337,7 +23337,7 @@
         <v>120</v>
       </c>
       <c r="F37" s="34">
-        <v>10930</v>
+        <v>9730</v>
       </c>
       <c r="G37" s="35" t="s">
         <v>69</v>
@@ -23360,7 +23360,7 @@
         <v>120</v>
       </c>
       <c r="F38" s="34">
-        <v>101256</v>
+        <v>101016</v>
       </c>
       <c r="G38" s="35" t="s">
         <v>69</v>
@@ -23383,7 +23383,7 @@
         <v>120</v>
       </c>
       <c r="F39" s="34">
-        <v>16346</v>
+        <v>16226</v>
       </c>
       <c r="G39" s="35" t="s">
         <v>69</v>
@@ -23406,7 +23406,7 @@
         <v>120</v>
       </c>
       <c r="F40" s="34">
-        <v>2448</v>
+        <v>2088</v>
       </c>
       <c r="G40" s="35" t="s">
         <v>69</v>
@@ -23774,7 +23774,7 @@
         <v>144</v>
       </c>
       <c r="F56" s="36">
-        <v>19</v>
+        <v>265</v>
       </c>
       <c r="G56" s="37" t="s">
         <v>109</v>
@@ -24349,7 +24349,7 @@
         <v>144</v>
       </c>
       <c r="F81" s="36">
-        <v>319</v>
+        <v>19</v>
       </c>
       <c r="G81" s="37" t="s">
         <v>109</v>
@@ -29084,7 +29084,7 @@
         <v>64</v>
       </c>
       <c r="F190" s="34">
-        <v>10090</v>
+        <v>9770</v>
       </c>
       <c r="G190" s="35" t="s">
         <v>69</v>
@@ -31059,7 +31059,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="34">
-        <v>40773</v>
+        <v>34773</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>69</v>
@@ -31220,7 +31220,7 @@
         <v>200</v>
       </c>
       <c r="F16" s="34">
-        <v>2747</v>
+        <v>2347</v>
       </c>
       <c r="G16" s="35" t="s">
         <v>69</v>
@@ -31401,7 +31401,7 @@
         <v>24</v>
       </c>
       <c r="F6" s="34">
-        <v>721</v>
+        <v>553</v>
       </c>
       <c r="G6" s="35" t="s">
         <v>69</v>
@@ -31424,7 +31424,7 @@
         <v>24</v>
       </c>
       <c r="F7" s="34">
-        <v>433</v>
+        <v>313</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>69</v>
@@ -31585,7 +31585,7 @@
         <v>24</v>
       </c>
       <c r="F14" s="34">
-        <v>486</v>
+        <v>342</v>
       </c>
       <c r="G14" s="35" t="s">
         <v>69</v>
@@ -31608,7 +31608,7 @@
         <v>24</v>
       </c>
       <c r="F15" s="34">
-        <v>692</v>
+        <v>548</v>
       </c>
       <c r="G15" s="35" t="s">
         <v>69</v>
@@ -31677,7 +31677,7 @@
         <v>24</v>
       </c>
       <c r="F18" s="34">
-        <v>243</v>
+        <v>171</v>
       </c>
       <c r="G18" s="35" t="s">
         <v>69</v>
@@ -31815,7 +31815,7 @@
         <v>24</v>
       </c>
       <c r="F24" s="34">
-        <v>616</v>
+        <v>472</v>
       </c>
       <c r="G24" s="35" t="s">
         <v>69</v>
@@ -31838,7 +31838,7 @@
         <v>24</v>
       </c>
       <c r="F25" s="34">
-        <v>427</v>
+        <v>235</v>
       </c>
       <c r="G25" s="35" t="s">
         <v>69</v>
@@ -32065,7 +32065,7 @@
         <v>144</v>
       </c>
       <c r="F2" s="34">
-        <v>74607</v>
+        <v>73167</v>
       </c>
       <c r="G2" s="35" t="s">
         <v>69</v>
@@ -32088,7 +32088,7 @@
         <v>144</v>
       </c>
       <c r="F3" s="34">
-        <v>37793</v>
+        <v>37073</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -32524,11 +32524,11 @@
       <c r="E22">
         <v>192</v>
       </c>
-      <c r="F22" s="34">
-        <v>1030</v>
-      </c>
-      <c r="G22" s="35" t="s">
-        <v>69</v>
+      <c r="F22" s="36">
+        <v>646</v>
+      </c>
+      <c r="G22" s="37" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -32547,11 +32547,11 @@
       <c r="E23">
         <v>192</v>
       </c>
-      <c r="F23" s="32">
-        <v>0</v>
-      </c>
-      <c r="G23" s="33" t="s">
-        <v>65</v>
+      <c r="F23" s="36">
+        <v>1</v>
+      </c>
+      <c r="G23" s="37" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -32571,7 +32571,7 @@
         <v>96</v>
       </c>
       <c r="F24" s="34">
-        <v>3510</v>
+        <v>3318</v>
       </c>
       <c r="G24" s="35" t="s">
         <v>69</v>
@@ -32732,7 +32732,7 @@
         <v>96</v>
       </c>
       <c r="F31" s="34">
-        <v>11901</v>
+        <v>11709</v>
       </c>
       <c r="G31" s="35" t="s">
         <v>69</v>
@@ -34227,7 +34227,7 @@
         <v>144</v>
       </c>
       <c r="F96" s="34">
-        <v>190794</v>
+        <v>190506</v>
       </c>
       <c r="G96" s="35" t="s">
         <v>69</v>
@@ -35397,7 +35397,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="34">
-        <v>75638</v>
+        <v>73138</v>
       </c>
       <c r="G2" s="35" t="s">
         <v>69</v>
@@ -35420,7 +35420,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="34">
-        <v>235977</v>
+        <v>230977</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -35489,7 +35489,7 @@
         <v>25</v>
       </c>
       <c r="F6" s="34">
-        <v>1627</v>
+        <v>1127</v>
       </c>
       <c r="G6" s="35" t="s">
         <v>69</v>
@@ -35604,7 +35604,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="34">
-        <v>29604</v>
+        <v>28524</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>69</v>
@@ -35627,7 +35627,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="34">
-        <v>25453</v>
+        <v>24203</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>69</v>
@@ -35650,7 +35650,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="34">
-        <v>128213</v>
+        <v>123213</v>
       </c>
       <c r="G13" s="35" t="s">
         <v>69</v>
@@ -35762,7 +35762,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="34">
-        <v>215642</v>
+        <v>212042</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 09/03/2026, 15:34:57</t>
+    <t>Actualización: 09/03/2026, 16:32:46</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>
@@ -41,7 +41,7 @@
     <t>Unidades:</t>
   </si>
   <si>
-    <t>8,491,684</t>
+    <t>8,495,803</t>
   </si>
   <si>
     <t>Agotados:</t>
@@ -68,7 +68,7 @@
     <t>ACCESORIOS</t>
   </si>
   <si>
-    <t>956,635</t>
+    <t>956,624</t>
   </si>
   <si>
     <t>11.3%</t>
@@ -77,16 +77,16 @@
     <t>ARCHIVO</t>
   </si>
   <si>
-    <t>1,750,444</t>
-  </si>
-  <si>
-    <t>20.6%</t>
+    <t>1,758,625</t>
+  </si>
+  <si>
+    <t>20.7%</t>
   </si>
   <si>
     <t>DIBUJO</t>
   </si>
   <si>
-    <t>110,249</t>
+    <t>110,148</t>
   </si>
   <si>
     <t>1.3%</t>
@@ -95,7 +95,7 @@
     <t>DIDACTICOS</t>
   </si>
   <si>
-    <t>26,309</t>
+    <t>26,312</t>
   </si>
   <si>
     <t>0.3%</t>
@@ -104,7 +104,7 @@
     <t>ESCRITURA</t>
   </si>
   <si>
-    <t>1,451,689</t>
+    <t>1,451,472</t>
   </si>
   <si>
     <t>17.1%</t>
@@ -113,10 +113,10 @@
     <t>FORROS</t>
   </si>
   <si>
-    <t>864,280</t>
-  </si>
-  <si>
-    <t>10.2%</t>
+    <t>860,978</t>
+  </si>
+  <si>
+    <t>10.1%</t>
   </si>
   <si>
     <t>MANUALIDADES</t>
@@ -149,10 +149,10 @@
     <t>PEGAMENTOS</t>
   </si>
   <si>
-    <t>598,905</t>
-  </si>
-  <si>
-    <t>7.1%</t>
+    <t>598,603</t>
+  </si>
+  <si>
+    <t>7.0%</t>
   </si>
   <si>
     <t>PELOTAS</t>
@@ -167,7 +167,7 @@
     <t>PINTURA</t>
   </si>
   <si>
-    <t>1,237,255</t>
+    <t>1,237,237</t>
   </si>
   <si>
     <t>14.6%</t>
@@ -176,7 +176,7 @@
     <t>REPRESENTADAS</t>
   </si>
   <si>
-    <t>319,247</t>
+    <t>319,133</t>
   </si>
   <si>
     <t>3.8%</t>
@@ -10217,13 +10217,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="6">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11320,7 +11320,7 @@
         <v>288</v>
       </c>
       <c r="F5" s="34">
-        <v>65701</v>
+        <v>65501</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>69</v>
@@ -11527,7 +11527,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="34">
-        <v>82171</v>
+        <v>82069</v>
       </c>
       <c r="G14" s="35" t="s">
         <v>69</v>
@@ -16305,7 +16305,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="34">
-        <v>104051</v>
+        <v>104049</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>69</v>
@@ -16328,7 +16328,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="34">
-        <v>14569</v>
+        <v>14567</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>
@@ -16742,7 +16742,7 @@
         <v>60</v>
       </c>
       <c r="F26" s="34">
-        <v>32615</v>
+        <v>32613</v>
       </c>
       <c r="G26" s="35" t="s">
         <v>69</v>
@@ -16765,7 +16765,7 @@
         <v>60</v>
       </c>
       <c r="F27" s="34">
-        <v>71458</v>
+        <v>71446</v>
       </c>
       <c r="G27" s="35" t="s">
         <v>69</v>
@@ -18579,7 +18579,7 @@
         <v>120</v>
       </c>
       <c r="F28" s="34">
-        <v>9252</v>
+        <v>9192</v>
       </c>
       <c r="G28" s="35" t="s">
         <v>69</v>
@@ -19200,7 +19200,7 @@
         <v>120</v>
       </c>
       <c r="F55" s="36">
-        <v>208</v>
+        <v>178</v>
       </c>
       <c r="G55" s="37" t="s">
         <v>109</v>
@@ -19407,7 +19407,7 @@
         <v>60</v>
       </c>
       <c r="F64" s="34">
-        <v>513</v>
+        <v>489</v>
       </c>
       <c r="G64" s="35" t="s">
         <v>69</v>
@@ -23199,7 +23199,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="34">
-        <v>139371</v>
+        <v>139363</v>
       </c>
       <c r="G31" s="35" t="s">
         <v>69</v>
@@ -24349,7 +24349,7 @@
         <v>144</v>
       </c>
       <c r="F81" s="36">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G81" s="37" t="s">
         <v>109</v>
@@ -24829,7 +24829,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="34">
-        <v>11704</v>
+        <v>20254</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>69</v>
@@ -24875,7 +24875,7 @@
         <v>50</v>
       </c>
       <c r="F7" s="34">
-        <v>7539</v>
+        <v>7239</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>69</v>
@@ -24921,7 +24921,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="34">
-        <v>3643</v>
+        <v>3543</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>69</v>
@@ -25013,7 +25013,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="34">
-        <v>4375</v>
+        <v>4325</v>
       </c>
       <c r="G13" s="35" t="s">
         <v>69</v>
@@ -25105,7 +25105,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="34">
-        <v>8132</v>
+        <v>8032</v>
       </c>
       <c r="G17" s="35" t="s">
         <v>69</v>
@@ -25128,7 +25128,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="34">
-        <v>15619</v>
+        <v>15519</v>
       </c>
       <c r="G18" s="35" t="s">
         <v>69</v>
@@ -25588,7 +25588,7 @@
         <v>50</v>
       </c>
       <c r="F38" s="34">
-        <v>4321</v>
+        <v>4261</v>
       </c>
       <c r="G38" s="35" t="s">
         <v>69</v>
@@ -26324,7 +26324,7 @@
         <v>100</v>
       </c>
       <c r="F70" s="34">
-        <v>5067</v>
+        <v>3567</v>
       </c>
       <c r="G70" s="35" t="s">
         <v>69</v>
@@ -28025,11 +28025,11 @@
       <c r="E144">
         <v>24</v>
       </c>
-      <c r="F144" s="32">
-        <v>0</v>
-      </c>
-      <c r="G144" s="33" t="s">
-        <v>65</v>
+      <c r="F144" s="36">
+        <v>17</v>
+      </c>
+      <c r="G144" s="37" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -28164,7 +28164,7 @@
         <v>12</v>
       </c>
       <c r="F150" s="34">
-        <v>543</v>
+        <v>2559</v>
       </c>
       <c r="G150" s="35" t="s">
         <v>69</v>
@@ -28417,7 +28417,7 @@
         <v>24</v>
       </c>
       <c r="F161" s="34">
-        <v>922</v>
+        <v>898</v>
       </c>
       <c r="G161" s="35" t="s">
         <v>69</v>
@@ -28440,7 +28440,7 @@
         <v>24</v>
       </c>
       <c r="F162" s="34">
-        <v>1843</v>
+        <v>1747</v>
       </c>
       <c r="G162" s="35" t="s">
         <v>69</v>
@@ -28463,7 +28463,7 @@
         <v>24</v>
       </c>
       <c r="F163" s="34">
-        <v>586</v>
+        <v>562</v>
       </c>
       <c r="G163" s="35" t="s">
         <v>69</v>
@@ -28486,7 +28486,7 @@
         <v>24</v>
       </c>
       <c r="F164" s="34">
-        <v>996</v>
+        <v>948</v>
       </c>
       <c r="G164" s="35" t="s">
         <v>69</v>
@@ -30921,7 +30921,7 @@
         <v>500</v>
       </c>
       <c r="F3" s="34">
-        <v>10065</v>
+        <v>9965</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -31059,7 +31059,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="34">
-        <v>34773</v>
+        <v>34772</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>69</v>
@@ -31332,7 +31332,7 @@
         <v>12</v>
       </c>
       <c r="F3" s="34">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -31355,7 +31355,7 @@
         <v>12</v>
       </c>
       <c r="F4" s="34">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="G4" s="35" t="s">
         <v>69</v>
@@ -31401,7 +31401,7 @@
         <v>24</v>
       </c>
       <c r="F6" s="34">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="G6" s="35" t="s">
         <v>69</v>
@@ -32065,7 +32065,7 @@
         <v>144</v>
       </c>
       <c r="F2" s="34">
-        <v>73167</v>
+        <v>73166</v>
       </c>
       <c r="G2" s="35" t="s">
         <v>69</v>
@@ -33514,7 +33514,7 @@
         <v>200</v>
       </c>
       <c r="F65" s="34">
-        <v>4930</v>
+        <v>4906</v>
       </c>
       <c r="G65" s="35" t="s">
         <v>69</v>
@@ -33537,7 +33537,7 @@
         <v>200</v>
       </c>
       <c r="F66" s="34">
-        <v>7447</v>
+        <v>7347</v>
       </c>
       <c r="G66" s="35" t="s">
         <v>69</v>
@@ -33997,7 +33997,7 @@
         <v>576</v>
       </c>
       <c r="F86" s="34">
-        <v>19918</v>
+        <v>19868</v>
       </c>
       <c r="G86" s="35" t="s">
         <v>69</v>
@@ -34135,7 +34135,7 @@
         <v>576</v>
       </c>
       <c r="F92" s="34">
-        <v>4243</v>
+        <v>4231</v>
       </c>
       <c r="G92" s="35" t="s">
         <v>69</v>
@@ -34158,7 +34158,7 @@
         <v>576</v>
       </c>
       <c r="F93" s="34">
-        <v>14255</v>
+        <v>14231</v>
       </c>
       <c r="G93" s="35" t="s">
         <v>69</v>
@@ -34227,7 +34227,7 @@
         <v>144</v>
       </c>
       <c r="F96" s="34">
-        <v>190506</v>
+        <v>190504</v>
       </c>
       <c r="G96" s="35" t="s">
         <v>69</v>
@@ -34250,7 +34250,7 @@
         <v>288</v>
       </c>
       <c r="F97" s="34">
-        <v>25660</v>
+        <v>25656</v>
       </c>
       <c r="G97" s="35" t="s">
         <v>69</v>
@@ -35397,7 +35397,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="34">
-        <v>73138</v>
+        <v>72138</v>
       </c>
       <c r="G2" s="35" t="s">
         <v>69</v>
@@ -35420,7 +35420,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="34">
-        <v>230977</v>
+        <v>230477</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -35443,7 +35443,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="34">
-        <v>82862</v>
+        <v>82312</v>
       </c>
       <c r="G4" s="35" t="s">
         <v>69</v>
@@ -35489,7 +35489,7 @@
         <v>25</v>
       </c>
       <c r="F6" s="34">
-        <v>1127</v>
+        <v>752</v>
       </c>
       <c r="G6" s="35" t="s">
         <v>69</v>
@@ -35558,7 +35558,7 @@
         <v>48</v>
       </c>
       <c r="F9" s="34">
-        <v>83857</v>
+        <v>83713</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>69</v>
@@ -35604,7 +35604,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="34">
-        <v>28524</v>
+        <v>28416</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>69</v>
@@ -35627,7 +35627,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="34">
-        <v>24203</v>
+        <v>23578</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>69</v>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 09/03/2026, 16:32:46</t>
+    <t>Actualización: 09/03/2026, 17:28:57</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>
@@ -41,7 +41,7 @@
     <t>Unidades:</t>
   </si>
   <si>
-    <t>8,495,803</t>
+    <t>8,485,232</t>
   </si>
   <si>
     <t>Agotados:</t>
@@ -68,7 +68,7 @@
     <t>ACCESORIOS</t>
   </si>
   <si>
-    <t>956,624</t>
+    <t>955,064</t>
   </si>
   <si>
     <t>11.3%</t>
@@ -77,7 +77,7 @@
     <t>ARCHIVO</t>
   </si>
   <si>
-    <t>1,758,625</t>
+    <t>1,756,801</t>
   </si>
   <si>
     <t>20.7%</t>
@@ -86,7 +86,7 @@
     <t>DIBUJO</t>
   </si>
   <si>
-    <t>110,148</t>
+    <t>110,098</t>
   </si>
   <si>
     <t>1.3%</t>
@@ -104,7 +104,7 @@
     <t>ESCRITURA</t>
   </si>
   <si>
-    <t>1,451,472</t>
+    <t>1,451,064</t>
   </si>
   <si>
     <t>17.1%</t>
@@ -113,7 +113,7 @@
     <t>FORROS</t>
   </si>
   <si>
-    <t>860,978</t>
+    <t>857,244</t>
   </si>
   <si>
     <t>10.1%</t>
@@ -122,7 +122,7 @@
     <t>MANUALIDADES</t>
   </si>
   <si>
-    <t>432,101</t>
+    <t>432,077</t>
   </si>
   <si>
     <t>5.1%</t>
@@ -140,7 +140,7 @@
     <t>METALICA</t>
   </si>
   <si>
-    <t>255,755</t>
+    <t>254,655</t>
   </si>
   <si>
     <t>3.0%</t>
@@ -152,22 +152,22 @@
     <t>598,603</t>
   </si>
   <si>
-    <t>7.0%</t>
+    <t>7.1%</t>
   </si>
   <si>
     <t>PELOTAS</t>
   </si>
   <si>
-    <t>479,722</t>
-  </si>
-  <si>
-    <t>5.6%</t>
+    <t>479,721</t>
+  </si>
+  <si>
+    <t>5.7%</t>
   </si>
   <si>
     <t>PINTURA</t>
   </si>
   <si>
-    <t>1,237,237</t>
+    <t>1,236,277</t>
   </si>
   <si>
     <t>14.6%</t>
@@ -176,7 +176,7 @@
     <t>REPRESENTADAS</t>
   </si>
   <si>
-    <t>319,133</t>
+    <t>318,223</t>
   </si>
   <si>
     <t>3.8%</t>
@@ -10217,7 +10217,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>7</v>
@@ -10817,7 +10817,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="34">
-        <v>39569</v>
+        <v>39469</v>
       </c>
       <c r="G15" s="35" t="s">
         <v>69</v>
@@ -10955,7 +10955,7 @@
         <v>500</v>
       </c>
       <c r="F21" s="34">
-        <v>47755</v>
+        <v>47255</v>
       </c>
       <c r="G21" s="35" t="s">
         <v>69</v>
@@ -10978,7 +10978,7 @@
         <v>500</v>
       </c>
       <c r="F22" s="34">
-        <v>24084</v>
+        <v>23584</v>
       </c>
       <c r="G22" s="35" t="s">
         <v>69</v>
@@ -15710,7 +15710,7 @@
         <v>1</v>
       </c>
       <c r="F173" s="34">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G173" s="35" t="s">
         <v>69</v>
@@ -16259,7 +16259,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="34">
-        <v>2283</v>
+        <v>2259</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>69</v>
@@ -16305,7 +16305,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="34">
-        <v>104049</v>
+        <v>103185</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>69</v>
@@ -16328,7 +16328,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="34">
-        <v>14567</v>
+        <v>14495</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>
@@ -17981,7 +17981,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="34">
-        <v>6410</v>
+        <v>5900</v>
       </c>
       <c r="G2" s="35" t="s">
         <v>69</v>
@@ -18050,7 +18050,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="34">
-        <v>20489</v>
+        <v>20189</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>69</v>
@@ -18073,7 +18073,7 @@
         <v>200</v>
       </c>
       <c r="F6" s="34">
-        <v>36483</v>
+        <v>36463</v>
       </c>
       <c r="G6" s="35" t="s">
         <v>69</v>
@@ -20074,7 +20074,7 @@
         <v>2</v>
       </c>
       <c r="F93" s="34">
-        <v>283</v>
+        <v>203</v>
       </c>
       <c r="G93" s="35" t="s">
         <v>69</v>
@@ -23199,7 +23199,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="34">
-        <v>139363</v>
+        <v>138643</v>
       </c>
       <c r="G31" s="35" t="s">
         <v>69</v>
@@ -23268,7 +23268,7 @@
         <v>120</v>
       </c>
       <c r="F34" s="34">
-        <v>48824</v>
+        <v>48704</v>
       </c>
       <c r="G34" s="35" t="s">
         <v>69</v>
@@ -23314,7 +23314,7 @@
         <v>120</v>
       </c>
       <c r="F36" s="34">
-        <v>26375</v>
+        <v>26255</v>
       </c>
       <c r="G36" s="35" t="s">
         <v>69</v>
@@ -23337,7 +23337,7 @@
         <v>120</v>
       </c>
       <c r="F37" s="34">
-        <v>9730</v>
+        <v>9490</v>
       </c>
       <c r="G37" s="35" t="s">
         <v>69</v>
@@ -23544,7 +23544,7 @@
         <v>144</v>
       </c>
       <c r="F46" s="34">
-        <v>8923</v>
+        <v>8851</v>
       </c>
       <c r="G46" s="35" t="s">
         <v>69</v>
@@ -23843,7 +23843,7 @@
         <v>144</v>
       </c>
       <c r="F59" s="34">
-        <v>4550</v>
+        <v>4514</v>
       </c>
       <c r="G59" s="35" t="s">
         <v>69</v>
@@ -23866,7 +23866,7 @@
         <v>144</v>
       </c>
       <c r="F60" s="34">
-        <v>3902</v>
+        <v>3866</v>
       </c>
       <c r="G60" s="35" t="s">
         <v>69</v>
@@ -24372,7 +24372,7 @@
         <v>144</v>
       </c>
       <c r="F82" s="34">
-        <v>1764</v>
+        <v>1656</v>
       </c>
       <c r="G82" s="35" t="s">
         <v>69</v>
@@ -24533,7 +24533,7 @@
         <v>144</v>
       </c>
       <c r="F89" s="34">
-        <v>6626</v>
+        <v>6578</v>
       </c>
       <c r="G89" s="35" t="s">
         <v>69</v>
@@ -24556,7 +24556,7 @@
         <v>144</v>
       </c>
       <c r="F90" s="34">
-        <v>18282</v>
+        <v>18222</v>
       </c>
       <c r="G90" s="35" t="s">
         <v>69</v>
@@ -24875,7 +24875,7 @@
         <v>50</v>
       </c>
       <c r="F7" s="34">
-        <v>7239</v>
+        <v>7139</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>69</v>
@@ -24921,7 +24921,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="34">
-        <v>3543</v>
+        <v>3493</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>69</v>
@@ -24944,7 +24944,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="34">
-        <v>13854</v>
+        <v>13754</v>
       </c>
       <c r="G10" s="35" t="s">
         <v>69</v>
@@ -24967,7 +24967,7 @@
         <v>50</v>
       </c>
       <c r="F11" s="34">
-        <v>5010</v>
+        <v>4960</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>69</v>
@@ -25058,11 +25058,11 @@
       <c r="E15">
         <v>50</v>
       </c>
-      <c r="F15" s="34">
-        <v>295</v>
-      </c>
-      <c r="G15" s="35" t="s">
-        <v>69</v>
+      <c r="F15" s="32">
+        <v>0</v>
+      </c>
+      <c r="G15" s="33" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -25082,7 +25082,7 @@
         <v>50</v>
       </c>
       <c r="F16" s="34">
-        <v>5017</v>
+        <v>4892</v>
       </c>
       <c r="G16" s="35" t="s">
         <v>69</v>
@@ -25151,7 +25151,7 @@
         <v>50</v>
       </c>
       <c r="F19" s="34">
-        <v>2247</v>
+        <v>2197</v>
       </c>
       <c r="G19" s="35" t="s">
         <v>69</v>
@@ -25197,7 +25197,7 @@
         <v>50</v>
       </c>
       <c r="F21" s="34">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="G21" s="35" t="s">
         <v>69</v>
@@ -25220,7 +25220,7 @@
         <v>50</v>
       </c>
       <c r="F22" s="34">
-        <v>643</v>
+        <v>593</v>
       </c>
       <c r="G22" s="35" t="s">
         <v>69</v>
@@ -25404,7 +25404,7 @@
         <v>50</v>
       </c>
       <c r="F30" s="34">
-        <v>9626</v>
+        <v>9625</v>
       </c>
       <c r="G30" s="35" t="s">
         <v>69</v>
@@ -25611,7 +25611,7 @@
         <v>50</v>
       </c>
       <c r="F39" s="34">
-        <v>2723</v>
+        <v>2722</v>
       </c>
       <c r="G39" s="35" t="s">
         <v>69</v>
@@ -25634,7 +25634,7 @@
         <v>50</v>
       </c>
       <c r="F40" s="34">
-        <v>7031</v>
+        <v>6981</v>
       </c>
       <c r="G40" s="35" t="s">
         <v>69</v>
@@ -25726,7 +25726,7 @@
         <v>100</v>
       </c>
       <c r="F44" s="34">
-        <v>3139</v>
+        <v>3339</v>
       </c>
       <c r="G44" s="35" t="s">
         <v>69</v>
@@ -25772,7 +25772,7 @@
         <v>100</v>
       </c>
       <c r="F46" s="34">
-        <v>4764</v>
+        <v>4664</v>
       </c>
       <c r="G46" s="35" t="s">
         <v>69</v>
@@ -25795,7 +25795,7 @@
         <v>100</v>
       </c>
       <c r="F47" s="34">
-        <v>2713</v>
+        <v>2913</v>
       </c>
       <c r="G47" s="35" t="s">
         <v>69</v>
@@ -25841,7 +25841,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="34">
-        <v>1189</v>
+        <v>1389</v>
       </c>
       <c r="G49" s="35" t="s">
         <v>69</v>
@@ -25887,7 +25887,7 @@
         <v>100</v>
       </c>
       <c r="F51" s="34">
-        <v>1192</v>
+        <v>1492</v>
       </c>
       <c r="G51" s="35" t="s">
         <v>69</v>
@@ -25910,7 +25910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="34">
-        <v>817</v>
+        <v>1017</v>
       </c>
       <c r="G52" s="35" t="s">
         <v>69</v>
@@ -26324,7 +26324,7 @@
         <v>100</v>
       </c>
       <c r="F70" s="34">
-        <v>3567</v>
+        <v>1967</v>
       </c>
       <c r="G70" s="35" t="s">
         <v>69</v>
@@ -28302,7 +28302,7 @@
         <v>6</v>
       </c>
       <c r="F156" s="34">
-        <v>936</v>
+        <v>900</v>
       </c>
       <c r="G156" s="35" t="s">
         <v>69</v>
@@ -28555,7 +28555,7 @@
         <v>72</v>
       </c>
       <c r="F167" s="34">
-        <v>22562</v>
+        <v>22490</v>
       </c>
       <c r="G167" s="35" t="s">
         <v>69</v>
@@ -28578,7 +28578,7 @@
         <v>72</v>
       </c>
       <c r="F168" s="34">
-        <v>4260</v>
+        <v>4188</v>
       </c>
       <c r="G168" s="35" t="s">
         <v>69</v>
@@ -28601,7 +28601,7 @@
         <v>36</v>
       </c>
       <c r="F169" s="34">
-        <v>1404</v>
+        <v>1332</v>
       </c>
       <c r="G169" s="35" t="s">
         <v>69</v>
@@ -30990,7 +30990,7 @@
         <v>500</v>
       </c>
       <c r="F6" s="36">
-        <v>207</v>
+        <v>157</v>
       </c>
       <c r="G6" s="37" t="s">
         <v>109</v>
@@ -32065,7 +32065,7 @@
         <v>144</v>
       </c>
       <c r="F2" s="34">
-        <v>73166</v>
+        <v>73106</v>
       </c>
       <c r="G2" s="35" t="s">
         <v>69</v>
@@ -32456,7 +32456,7 @@
         <v>192</v>
       </c>
       <c r="F19" s="34">
-        <v>9494</v>
+        <v>9488</v>
       </c>
       <c r="G19" s="35" t="s">
         <v>69</v>
@@ -32479,7 +32479,7 @@
         <v>192</v>
       </c>
       <c r="F20" s="34">
-        <v>14861</v>
+        <v>14855</v>
       </c>
       <c r="G20" s="35" t="s">
         <v>69</v>
@@ -32594,7 +32594,7 @@
         <v>48</v>
       </c>
       <c r="F25" s="34">
-        <v>3794</v>
+        <v>3746</v>
       </c>
       <c r="G25" s="35" t="s">
         <v>69</v>
@@ -33215,7 +33215,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="34">
-        <v>7067</v>
+        <v>6779</v>
       </c>
       <c r="G52" s="35" t="s">
         <v>69</v>
@@ -35397,7 +35397,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="34">
-        <v>72138</v>
+        <v>71888</v>
       </c>
       <c r="G2" s="35" t="s">
         <v>69</v>
@@ -35420,7 +35420,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="34">
-        <v>230477</v>
+        <v>229877</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -35512,7 +35512,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="34">
-        <v>9975</v>
+        <v>7425</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>69</v>
@@ -35604,7 +35604,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="34">
-        <v>28416</v>
+        <v>28293</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>69</v>
@@ -35627,7 +35627,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="34">
-        <v>23578</v>
+        <v>23453</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>69</v>
@@ -35650,7 +35650,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="34">
-        <v>123213</v>
+        <v>123127</v>
       </c>
       <c r="G13" s="35" t="s">
         <v>69</v>
@@ -35808,7 +35808,7 @@
         <v>72</v>
       </c>
       <c r="F5" s="34">
-        <v>32978</v>
+        <v>32954</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>69</v>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 09/03/2026, 17:28:57</t>
+    <t>Actualización: 09/03/2026, 18:28:29</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>
@@ -41,7 +41,7 @@
     <t>Unidades:</t>
   </si>
   <si>
-    <t>8,485,232</t>
+    <t>8,477,923</t>
   </si>
   <si>
     <t>Agotados:</t>
@@ -68,7 +68,7 @@
     <t>ACCESORIOS</t>
   </si>
   <si>
-    <t>955,064</t>
+    <t>954,928</t>
   </si>
   <si>
     <t>11.3%</t>
@@ -77,7 +77,7 @@
     <t>ARCHIVO</t>
   </si>
   <si>
-    <t>1,756,801</t>
+    <t>1,752,151</t>
   </si>
   <si>
     <t>20.7%</t>
@@ -104,7 +104,7 @@
     <t>ESCRITURA</t>
   </si>
   <si>
-    <t>1,451,064</t>
+    <t>1,450,323</t>
   </si>
   <si>
     <t>17.1%</t>
@@ -113,7 +113,7 @@
     <t>FORROS</t>
   </si>
   <si>
-    <t>857,244</t>
+    <t>856,134</t>
   </si>
   <si>
     <t>10.1%</t>
@@ -167,7 +167,7 @@
     <t>PINTURA</t>
   </si>
   <si>
-    <t>1,236,277</t>
+    <t>1,235,605</t>
   </si>
   <si>
     <t>14.6%</t>
@@ -10217,13 +10217,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="6">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -16535,7 +16535,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="34">
-        <v>95941</v>
+        <v>95653</v>
       </c>
       <c r="G17" s="35" t="s">
         <v>69</v>
@@ -16558,7 +16558,7 @@
         <v>72</v>
       </c>
       <c r="F18" s="34">
-        <v>6571</v>
+        <v>6427</v>
       </c>
       <c r="G18" s="35" t="s">
         <v>69</v>
@@ -16673,7 +16673,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="34">
-        <v>13508</v>
+        <v>13268</v>
       </c>
       <c r="G23" s="35" t="s">
         <v>69</v>
@@ -22854,7 +22854,7 @@
         <v>24</v>
       </c>
       <c r="F16" s="36">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G16" s="37" t="s">
         <v>109</v>
@@ -22876,11 +22876,11 @@
       <c r="E17">
         <v>24</v>
       </c>
-      <c r="F17" s="32">
-        <v>0</v>
-      </c>
-      <c r="G17" s="33" t="s">
-        <v>65</v>
+      <c r="F17" s="36">
+        <v>1</v>
+      </c>
+      <c r="G17" s="37" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -22899,11 +22899,11 @@
       <c r="E18">
         <v>24</v>
       </c>
-      <c r="F18" s="32">
-        <v>0</v>
-      </c>
-      <c r="G18" s="33" t="s">
-        <v>65</v>
+      <c r="F18" s="36">
+        <v>1</v>
+      </c>
+      <c r="G18" s="37" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -23429,7 +23429,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="34">
-        <v>7394</v>
+        <v>7250</v>
       </c>
       <c r="G41" s="35" t="s">
         <v>69</v>
@@ -24783,7 +24783,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="34">
-        <v>46970</v>
+        <v>46720</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -24829,7 +24829,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="34">
-        <v>20254</v>
+        <v>18254</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>69</v>
@@ -27451,7 +27451,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="34">
-        <v>25116</v>
+        <v>22716</v>
       </c>
       <c r="G119" s="35" t="s">
         <v>69</v>
@@ -32134,7 +32134,7 @@
         <v>288</v>
       </c>
       <c r="F5" s="36">
-        <v>1038</v>
+        <v>750</v>
       </c>
       <c r="G5" s="37" t="s">
         <v>109</v>
@@ -32617,7 +32617,7 @@
         <v>24</v>
       </c>
       <c r="F26" s="34">
-        <v>13300</v>
+        <v>12943</v>
       </c>
       <c r="G26" s="35" t="s">
         <v>69</v>
@@ -33238,7 +33238,7 @@
         <v>96</v>
       </c>
       <c r="F53" s="34">
-        <v>14685</v>
+        <v>14589</v>
       </c>
       <c r="G53" s="35" t="s">
         <v>69</v>
@@ -35489,7 +35489,7 @@
         <v>25</v>
       </c>
       <c r="F6" s="34">
-        <v>752</v>
+        <v>502</v>
       </c>
       <c r="G6" s="35" t="s">
         <v>69</v>
@@ -35604,7 +35604,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="34">
-        <v>28293</v>
+        <v>27933</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>69</v>
@@ -35650,7 +35650,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="34">
-        <v>123127</v>
+        <v>122627</v>
       </c>
       <c r="G13" s="35" t="s">
         <v>69</v>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 09/03/2026, 20:59:53</t>
+    <t>Actualización: 10/03/2026, 07:24:43</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>
@@ -41,7 +41,7 @@
     <t>Unidades:</t>
   </si>
   <si>
-    <t>8,477,923</t>
+    <t>8,375,240</t>
   </si>
   <si>
     <t>Agotados:</t>
@@ -68,16 +68,16 @@
     <t>ACCESORIOS</t>
   </si>
   <si>
-    <t>954,928</t>
-  </si>
-  <si>
-    <t>11.3%</t>
+    <t>938,726</t>
+  </si>
+  <si>
+    <t>11.2%</t>
   </si>
   <si>
     <t>ARCHIVO</t>
   </si>
   <si>
-    <t>1,752,151</t>
+    <t>1,735,593</t>
   </si>
   <si>
     <t>20.7%</t>
@@ -86,16 +86,16 @@
     <t>DIBUJO</t>
   </si>
   <si>
-    <t>110,098</t>
-  </si>
-  <si>
-    <t>1.3%</t>
+    <t>103,298</t>
+  </si>
+  <si>
+    <t>1.2%</t>
   </si>
   <si>
     <t>DIDACTICOS</t>
   </si>
   <si>
-    <t>26,312</t>
+    <t>25,700</t>
   </si>
   <si>
     <t>0.3%</t>
@@ -104,25 +104,25 @@
     <t>ESCRITURA</t>
   </si>
   <si>
-    <t>1,450,323</t>
-  </si>
-  <si>
-    <t>17.1%</t>
+    <t>1,438,019</t>
+  </si>
+  <si>
+    <t>17.2%</t>
   </si>
   <si>
     <t>FORROS</t>
   </si>
   <si>
-    <t>856,134</t>
-  </si>
-  <si>
-    <t>10.1%</t>
+    <t>841,204</t>
+  </si>
+  <si>
+    <t>10.0%</t>
   </si>
   <si>
     <t>MANUALIDADES</t>
   </si>
   <si>
-    <t>432,077</t>
+    <t>426,357</t>
   </si>
   <si>
     <t>5.1%</t>
@@ -140,7 +140,7 @@
     <t>METALICA</t>
   </si>
   <si>
-    <t>254,655</t>
+    <t>248,477</t>
   </si>
   <si>
     <t>3.0%</t>
@@ -149,16 +149,16 @@
     <t>PEGAMENTOS</t>
   </si>
   <si>
-    <t>598,603</t>
-  </si>
-  <si>
-    <t>7.1%</t>
+    <t>584,779</t>
+  </si>
+  <si>
+    <t>7.0%</t>
   </si>
   <si>
     <t>PELOTAS</t>
   </si>
   <si>
-    <t>479,721</t>
+    <t>479,718</t>
   </si>
   <si>
     <t>5.7%</t>
@@ -167,7 +167,7 @@
     <t>PINTURA</t>
   </si>
   <si>
-    <t>1,235,605</t>
+    <t>1,226,053</t>
   </si>
   <si>
     <t>14.6%</t>
@@ -10217,13 +10217,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="6">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -10656,7 +10656,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="34">
-        <v>10052</v>
+        <v>9956</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>
@@ -10679,7 +10679,7 @@
         <v>48</v>
       </c>
       <c r="F9" s="34">
-        <v>2036</v>
+        <v>1940</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>69</v>
@@ -10817,7 +10817,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="34">
-        <v>39469</v>
+        <v>38969</v>
       </c>
       <c r="G15" s="35" t="s">
         <v>69</v>
@@ -10840,7 +10840,7 @@
         <v>72</v>
       </c>
       <c r="F16" s="34">
-        <v>2310</v>
+        <v>2094</v>
       </c>
       <c r="G16" s="35" t="s">
         <v>69</v>
@@ -10863,7 +10863,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="34">
-        <v>14034</v>
+        <v>13746</v>
       </c>
       <c r="G17" s="35" t="s">
         <v>69</v>
@@ -10885,11 +10885,11 @@
       <c r="E18">
         <v>288</v>
       </c>
-      <c r="F18" s="36">
-        <v>542</v>
-      </c>
-      <c r="G18" s="37" t="s">
-        <v>109</v>
+      <c r="F18" s="32">
+        <v>0</v>
+      </c>
+      <c r="G18" s="33" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -10955,7 +10955,7 @@
         <v>500</v>
       </c>
       <c r="F21" s="34">
-        <v>47255</v>
+        <v>45255</v>
       </c>
       <c r="G21" s="35" t="s">
         <v>69</v>
@@ -10978,7 +10978,7 @@
         <v>500</v>
       </c>
       <c r="F22" s="34">
-        <v>23584</v>
+        <v>22084</v>
       </c>
       <c r="G22" s="35" t="s">
         <v>69</v>
@@ -11000,11 +11000,11 @@
       <c r="E23">
         <v>300</v>
       </c>
-      <c r="F23" s="34">
-        <v>1775</v>
-      </c>
-      <c r="G23" s="35" t="s">
-        <v>69</v>
+      <c r="F23" s="36">
+        <v>1175</v>
+      </c>
+      <c r="G23" s="37" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -11070,7 +11070,7 @@
         <v>120</v>
       </c>
       <c r="F26" s="34">
-        <v>3104</v>
+        <v>2864</v>
       </c>
       <c r="G26" s="35" t="s">
         <v>69</v>
@@ -11185,7 +11185,7 @@
         <v>100</v>
       </c>
       <c r="F31" s="34">
-        <v>1351</v>
+        <v>1251</v>
       </c>
       <c r="G31" s="35" t="s">
         <v>69</v>
@@ -11320,7 +11320,7 @@
         <v>288</v>
       </c>
       <c r="F5" s="34">
-        <v>65501</v>
+        <v>62141</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>69</v>
@@ -11343,7 +11343,7 @@
         <v>384</v>
       </c>
       <c r="F6" s="34">
-        <v>94120</v>
+        <v>92200</v>
       </c>
       <c r="G6" s="35" t="s">
         <v>69</v>
@@ -11366,7 +11366,7 @@
         <v>384</v>
       </c>
       <c r="F7" s="34">
-        <v>57680</v>
+        <v>56528</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>69</v>
@@ -11481,7 +11481,7 @@
         <v>192</v>
       </c>
       <c r="F12" s="34">
-        <v>34134</v>
+        <v>30294</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>69</v>
@@ -11504,7 +11504,7 @@
         <v>576</v>
       </c>
       <c r="F13" s="34">
-        <v>91168</v>
+        <v>90016</v>
       </c>
       <c r="G13" s="35" t="s">
         <v>69</v>
@@ -11527,7 +11527,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="34">
-        <v>82069</v>
+        <v>79669</v>
       </c>
       <c r="G14" s="35" t="s">
         <v>69</v>
@@ -12743,7 +12743,7 @@
         <v>48</v>
       </c>
       <c r="F44" s="34">
-        <v>6450</v>
+        <v>6447</v>
       </c>
       <c r="G44" s="35" t="s">
         <v>69</v>
@@ -16190,7 +16190,7 @@
         <v>288</v>
       </c>
       <c r="F2" s="34">
-        <v>25237</v>
+        <v>24949</v>
       </c>
       <c r="G2" s="35" t="s">
         <v>69</v>
@@ -16420,7 +16420,7 @@
         <v>144</v>
       </c>
       <c r="F12" s="34">
-        <v>15523</v>
+        <v>14383</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>69</v>
@@ -16466,7 +16466,7 @@
         <v>144</v>
       </c>
       <c r="F14" s="34">
-        <v>10060</v>
+        <v>9628</v>
       </c>
       <c r="G14" s="35" t="s">
         <v>69</v>
@@ -16581,7 +16581,7 @@
         <v>36</v>
       </c>
       <c r="F19" s="34">
-        <v>5063</v>
+        <v>4991</v>
       </c>
       <c r="G19" s="35" t="s">
         <v>69</v>
@@ -16673,7 +16673,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="34">
-        <v>13268</v>
+        <v>12968</v>
       </c>
       <c r="G23" s="35" t="s">
         <v>69</v>
@@ -16696,7 +16696,7 @@
         <v>48</v>
       </c>
       <c r="F24" s="34">
-        <v>10762</v>
+        <v>9802</v>
       </c>
       <c r="G24" s="35" t="s">
         <v>69</v>
@@ -16742,7 +16742,7 @@
         <v>60</v>
       </c>
       <c r="F26" s="34">
-        <v>32613</v>
+        <v>32313</v>
       </c>
       <c r="G26" s="35" t="s">
         <v>69</v>
@@ -16765,7 +16765,7 @@
         <v>60</v>
       </c>
       <c r="F27" s="34">
-        <v>71446</v>
+        <v>71146</v>
       </c>
       <c r="G27" s="35" t="s">
         <v>69</v>
@@ -17248,7 +17248,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="34">
-        <v>49096</v>
+        <v>46936</v>
       </c>
       <c r="G48" s="35" t="s">
         <v>69</v>
@@ -17317,7 +17317,7 @@
         <v>360</v>
       </c>
       <c r="F51" s="34">
-        <v>27538</v>
+        <v>23938</v>
       </c>
       <c r="G51" s="35" t="s">
         <v>69</v>
@@ -22578,7 +22578,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="34">
-        <v>11431</v>
+        <v>11181</v>
       </c>
       <c r="G4" s="35" t="s">
         <v>69</v>
@@ -23084,7 +23084,7 @@
         <v>36</v>
       </c>
       <c r="F26" s="34">
-        <v>5385</v>
+        <v>5313</v>
       </c>
       <c r="G26" s="35" t="s">
         <v>69</v>
@@ -23130,7 +23130,7 @@
         <v>36</v>
       </c>
       <c r="F28" s="34">
-        <v>3655</v>
+        <v>3583</v>
       </c>
       <c r="G28" s="35" t="s">
         <v>69</v>
@@ -23153,7 +23153,7 @@
         <v>36</v>
       </c>
       <c r="F29" s="34">
-        <v>5310</v>
+        <v>5166</v>
       </c>
       <c r="G29" s="35" t="s">
         <v>69</v>
@@ -23245,7 +23245,7 @@
         <v>120</v>
       </c>
       <c r="F33" s="34">
-        <v>39392</v>
+        <v>38192</v>
       </c>
       <c r="G33" s="35" t="s">
         <v>69</v>
@@ -23268,7 +23268,7 @@
         <v>120</v>
       </c>
       <c r="F34" s="34">
-        <v>48704</v>
+        <v>47264</v>
       </c>
       <c r="G34" s="35" t="s">
         <v>69</v>
@@ -23290,11 +23290,11 @@
       <c r="E35">
         <v>120</v>
       </c>
-      <c r="F35" s="36">
-        <v>88</v>
-      </c>
-      <c r="G35" s="37" t="s">
-        <v>109</v>
+      <c r="F35" s="32">
+        <v>0</v>
+      </c>
+      <c r="G35" s="33" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -23337,7 +23337,7 @@
         <v>120</v>
       </c>
       <c r="F37" s="34">
-        <v>9490</v>
+        <v>7090</v>
       </c>
       <c r="G37" s="35" t="s">
         <v>69</v>
@@ -23360,7 +23360,7 @@
         <v>120</v>
       </c>
       <c r="F38" s="34">
-        <v>101016</v>
+        <v>100416</v>
       </c>
       <c r="G38" s="35" t="s">
         <v>69</v>
@@ -23383,7 +23383,7 @@
         <v>120</v>
       </c>
       <c r="F39" s="34">
-        <v>16226</v>
+        <v>15746</v>
       </c>
       <c r="G39" s="35" t="s">
         <v>69</v>
@@ -23406,7 +23406,7 @@
         <v>120</v>
       </c>
       <c r="F40" s="34">
-        <v>2088</v>
+        <v>888</v>
       </c>
       <c r="G40" s="35" t="s">
         <v>69</v>
@@ -23429,7 +23429,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="34">
-        <v>7250</v>
+        <v>6242</v>
       </c>
       <c r="G41" s="35" t="s">
         <v>69</v>
@@ -23452,7 +23452,7 @@
         <v>144</v>
       </c>
       <c r="F42" s="34">
-        <v>11077</v>
+        <v>10645</v>
       </c>
       <c r="G42" s="35" t="s">
         <v>69</v>
@@ -23475,7 +23475,7 @@
         <v>144</v>
       </c>
       <c r="F43" s="34">
-        <v>9827</v>
+        <v>9539</v>
       </c>
       <c r="G43" s="35" t="s">
         <v>69</v>
@@ -23498,7 +23498,7 @@
         <v>144</v>
       </c>
       <c r="F44" s="34">
-        <v>10489</v>
+        <v>10201</v>
       </c>
       <c r="G44" s="35" t="s">
         <v>69</v>
@@ -23521,7 +23521,7 @@
         <v>144</v>
       </c>
       <c r="F45" s="34">
-        <v>10890</v>
+        <v>10602</v>
       </c>
       <c r="G45" s="35" t="s">
         <v>69</v>
@@ -23544,7 +23544,7 @@
         <v>144</v>
       </c>
       <c r="F46" s="34">
-        <v>8851</v>
+        <v>8563</v>
       </c>
       <c r="G46" s="35" t="s">
         <v>69</v>
@@ -23567,7 +23567,7 @@
         <v>144</v>
       </c>
       <c r="F47" s="34">
-        <v>4006</v>
+        <v>3286</v>
       </c>
       <c r="G47" s="35" t="s">
         <v>69</v>
@@ -23590,7 +23590,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="34">
-        <v>10132</v>
+        <v>9412</v>
       </c>
       <c r="G48" s="35" t="s">
         <v>69</v>
@@ -23613,7 +23613,7 @@
         <v>144</v>
       </c>
       <c r="F49" s="34">
-        <v>15461</v>
+        <v>15029</v>
       </c>
       <c r="G49" s="35" t="s">
         <v>69</v>
@@ -23636,7 +23636,7 @@
         <v>144</v>
       </c>
       <c r="F50" s="34">
-        <v>5608</v>
+        <v>5176</v>
       </c>
       <c r="G50" s="35" t="s">
         <v>69</v>
@@ -23659,7 +23659,7 @@
         <v>144</v>
       </c>
       <c r="F51" s="34">
-        <v>5079</v>
+        <v>4215</v>
       </c>
       <c r="G51" s="35" t="s">
         <v>69</v>
@@ -23682,7 +23682,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="34">
-        <v>6454</v>
+        <v>5734</v>
       </c>
       <c r="G52" s="35" t="s">
         <v>69</v>
@@ -23705,7 +23705,7 @@
         <v>144</v>
       </c>
       <c r="F53" s="34">
-        <v>6289</v>
+        <v>6001</v>
       </c>
       <c r="G53" s="35" t="s">
         <v>69</v>
@@ -23727,11 +23727,11 @@
       <c r="E54">
         <v>144</v>
       </c>
-      <c r="F54" s="36">
-        <v>432</v>
-      </c>
-      <c r="G54" s="37" t="s">
-        <v>109</v>
+      <c r="F54" s="32">
+        <v>0</v>
+      </c>
+      <c r="G54" s="33" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -23774,7 +23774,7 @@
         <v>144</v>
       </c>
       <c r="F56" s="36">
-        <v>265</v>
+        <v>121</v>
       </c>
       <c r="G56" s="37" t="s">
         <v>109</v>
@@ -23889,7 +23889,7 @@
         <v>96</v>
       </c>
       <c r="F61" s="34">
-        <v>3245</v>
+        <v>3053</v>
       </c>
       <c r="G61" s="35" t="s">
         <v>69</v>
@@ -23935,7 +23935,7 @@
         <v>120</v>
       </c>
       <c r="F63" s="34">
-        <v>9041</v>
+        <v>8681</v>
       </c>
       <c r="G63" s="35" t="s">
         <v>69</v>
@@ -23958,7 +23958,7 @@
         <v>120</v>
       </c>
       <c r="F64" s="34">
-        <v>7340</v>
+        <v>6980</v>
       </c>
       <c r="G64" s="35" t="s">
         <v>69</v>
@@ -24829,7 +24829,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="34">
-        <v>18254</v>
+        <v>15754</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>69</v>
@@ -24875,7 +24875,7 @@
         <v>50</v>
       </c>
       <c r="F7" s="34">
-        <v>7139</v>
+        <v>6939</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>69</v>
@@ -24944,7 +24944,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="34">
-        <v>13754</v>
+        <v>13654</v>
       </c>
       <c r="G10" s="35" t="s">
         <v>69</v>
@@ -24990,7 +24990,7 @@
         <v>50</v>
       </c>
       <c r="F12" s="34">
-        <v>3009</v>
+        <v>2859</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>69</v>
@@ -25036,7 +25036,7 @@
         <v>50</v>
       </c>
       <c r="F14" s="36">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="G14" s="37" t="s">
         <v>109</v>
@@ -25105,7 +25105,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="34">
-        <v>8032</v>
+        <v>7882</v>
       </c>
       <c r="G17" s="35" t="s">
         <v>69</v>
@@ -25128,7 +25128,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="34">
-        <v>15519</v>
+        <v>15119</v>
       </c>
       <c r="G18" s="35" t="s">
         <v>69</v>
@@ -25151,7 +25151,7 @@
         <v>50</v>
       </c>
       <c r="F19" s="34">
-        <v>2197</v>
+        <v>1897</v>
       </c>
       <c r="G19" s="35" t="s">
         <v>69</v>
@@ -25196,11 +25196,11 @@
       <c r="E21">
         <v>50</v>
       </c>
-      <c r="F21" s="34">
-        <v>550</v>
-      </c>
-      <c r="G21" s="35" t="s">
-        <v>69</v>
+      <c r="F21" s="36">
+        <v>100</v>
+      </c>
+      <c r="G21" s="37" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -25220,7 +25220,7 @@
         <v>50</v>
       </c>
       <c r="F22" s="34">
-        <v>593</v>
+        <v>493</v>
       </c>
       <c r="G22" s="35" t="s">
         <v>69</v>
@@ -25726,7 +25726,7 @@
         <v>100</v>
       </c>
       <c r="F44" s="34">
-        <v>3339</v>
+        <v>3289</v>
       </c>
       <c r="G44" s="35" t="s">
         <v>69</v>
@@ -25749,7 +25749,7 @@
         <v>100</v>
       </c>
       <c r="F45" s="34">
-        <v>2776</v>
+        <v>2726</v>
       </c>
       <c r="G45" s="35" t="s">
         <v>69</v>
@@ -25795,7 +25795,7 @@
         <v>100</v>
       </c>
       <c r="F47" s="34">
-        <v>2913</v>
+        <v>2813</v>
       </c>
       <c r="G47" s="35" t="s">
         <v>69</v>
@@ -25841,7 +25841,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="34">
-        <v>1389</v>
+        <v>1339</v>
       </c>
       <c r="G49" s="35" t="s">
         <v>69</v>
@@ -25864,7 +25864,7 @@
         <v>100</v>
       </c>
       <c r="F50" s="34">
-        <v>2223</v>
+        <v>2173</v>
       </c>
       <c r="G50" s="35" t="s">
         <v>69</v>
@@ -25910,7 +25910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="34">
-        <v>1017</v>
+        <v>917</v>
       </c>
       <c r="G52" s="35" t="s">
         <v>69</v>
@@ -26485,7 +26485,7 @@
         <v>100</v>
       </c>
       <c r="F77" s="34">
-        <v>43324</v>
+        <v>42324</v>
       </c>
       <c r="G77" s="35" t="s">
         <v>69</v>
@@ -26554,7 +26554,7 @@
         <v>100</v>
       </c>
       <c r="F80" s="34">
-        <v>16423</v>
+        <v>15923</v>
       </c>
       <c r="G80" s="35" t="s">
         <v>69</v>
@@ -26577,7 +26577,7 @@
         <v>100</v>
       </c>
       <c r="F81" s="34">
-        <v>10217</v>
+        <v>9717</v>
       </c>
       <c r="G81" s="35" t="s">
         <v>69</v>
@@ -26646,7 +26646,7 @@
         <v>100</v>
       </c>
       <c r="F84" s="34">
-        <v>3092</v>
+        <v>2592</v>
       </c>
       <c r="G84" s="35" t="s">
         <v>69</v>
@@ -26945,7 +26945,7 @@
         <v>120</v>
       </c>
       <c r="F97" s="34">
-        <v>2487</v>
+        <v>2247</v>
       </c>
       <c r="G97" s="35" t="s">
         <v>69</v>
@@ -27014,7 +27014,7 @@
         <v>120</v>
       </c>
       <c r="F100" s="34">
-        <v>1340</v>
+        <v>1100</v>
       </c>
       <c r="G100" s="35" t="s">
         <v>69</v>
@@ -27520,7 +27520,7 @@
         <v>24</v>
       </c>
       <c r="F122" s="34">
-        <v>3713</v>
+        <v>3593</v>
       </c>
       <c r="G122" s="35" t="s">
         <v>69</v>
@@ -27589,7 +27589,7 @@
         <v>24</v>
       </c>
       <c r="F125" s="34">
-        <v>595</v>
+        <v>475</v>
       </c>
       <c r="G125" s="35" t="s">
         <v>69</v>
@@ -27727,7 +27727,7 @@
         <v>24</v>
       </c>
       <c r="F131" s="34">
-        <v>9834</v>
+        <v>9762</v>
       </c>
       <c r="G131" s="35" t="s">
         <v>69</v>
@@ -28370,11 +28370,11 @@
       <c r="E159">
         <v>24</v>
       </c>
-      <c r="F159" s="34">
-        <v>130</v>
-      </c>
-      <c r="G159" s="35" t="s">
-        <v>69</v>
+      <c r="F159" s="36">
+        <v>34</v>
+      </c>
+      <c r="G159" s="37" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -28417,7 +28417,7 @@
         <v>24</v>
       </c>
       <c r="F161" s="34">
-        <v>898</v>
+        <v>778</v>
       </c>
       <c r="G161" s="35" t="s">
         <v>69</v>
@@ -28463,7 +28463,7 @@
         <v>24</v>
       </c>
       <c r="F163" s="34">
-        <v>562</v>
+        <v>490</v>
       </c>
       <c r="G163" s="35" t="s">
         <v>69</v>
@@ -28509,7 +28509,7 @@
         <v>24</v>
       </c>
       <c r="F165" s="34">
-        <v>1246</v>
+        <v>1126</v>
       </c>
       <c r="G165" s="35" t="s">
         <v>69</v>
@@ -28693,7 +28693,7 @@
         <v>72</v>
       </c>
       <c r="F173" s="34">
-        <v>1193</v>
+        <v>1121</v>
       </c>
       <c r="G173" s="35" t="s">
         <v>69</v>
@@ -28785,7 +28785,7 @@
         <v>48</v>
       </c>
       <c r="F177" s="36">
-        <v>193</v>
+        <v>97</v>
       </c>
       <c r="G177" s="37" t="s">
         <v>109</v>
@@ -28808,7 +28808,7 @@
         <v>48</v>
       </c>
       <c r="F178" s="34">
-        <v>520</v>
+        <v>424</v>
       </c>
       <c r="G178" s="35" t="s">
         <v>69</v>
@@ -28830,11 +28830,11 @@
       <c r="E179">
         <v>36</v>
       </c>
-      <c r="F179" s="34">
-        <v>218</v>
-      </c>
-      <c r="G179" s="35" t="s">
-        <v>69</v>
+      <c r="F179" s="36">
+        <v>146</v>
+      </c>
+      <c r="G179" s="37" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -28900,7 +28900,7 @@
         <v>36</v>
       </c>
       <c r="F182" s="34">
-        <v>922</v>
+        <v>850</v>
       </c>
       <c r="G182" s="35" t="s">
         <v>69</v>
@@ -29084,7 +29084,7 @@
         <v>64</v>
       </c>
       <c r="F190" s="34">
-        <v>9770</v>
+        <v>9450</v>
       </c>
       <c r="G190" s="35" t="s">
         <v>69</v>
@@ -30257,7 +30257,7 @@
         <v>5</v>
       </c>
       <c r="F241" s="34">
-        <v>1705</v>
+        <v>1695</v>
       </c>
       <c r="G241" s="35" t="s">
         <v>69</v>
@@ -30303,7 +30303,7 @@
         <v>5</v>
       </c>
       <c r="F243" s="34">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="G243" s="35" t="s">
         <v>69</v>
@@ -30395,7 +30395,7 @@
         <v>5</v>
       </c>
       <c r="F247" s="34">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="G247" s="35" t="s">
         <v>69</v>
@@ -30487,7 +30487,7 @@
         <v>40</v>
       </c>
       <c r="F251" s="34">
-        <v>4427</v>
+        <v>3227</v>
       </c>
       <c r="G251" s="35" t="s">
         <v>69</v>
@@ -30556,7 +30556,7 @@
         <v>40</v>
       </c>
       <c r="F254" s="34">
-        <v>141054</v>
+        <v>135054</v>
       </c>
       <c r="G254" s="35" t="s">
         <v>69</v>
@@ -30921,7 +30921,7 @@
         <v>500</v>
       </c>
       <c r="F3" s="34">
-        <v>9965</v>
+        <v>6965</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -31036,7 +31036,7 @@
         <v>400</v>
       </c>
       <c r="F8" s="34">
-        <v>16723</v>
+        <v>16323</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>
@@ -31059,7 +31059,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="34">
-        <v>34772</v>
+        <v>33772</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>69</v>
@@ -31174,7 +31174,7 @@
         <v>200</v>
       </c>
       <c r="F14" s="34">
-        <v>1904</v>
+        <v>1504</v>
       </c>
       <c r="G14" s="35" t="s">
         <v>69</v>
@@ -31219,11 +31219,11 @@
       <c r="E16">
         <v>200</v>
       </c>
-      <c r="F16" s="34">
-        <v>2347</v>
-      </c>
-      <c r="G16" s="35" t="s">
-        <v>69</v>
+      <c r="F16" s="36">
+        <v>347</v>
+      </c>
+      <c r="G16" s="37" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -31309,7 +31309,7 @@
         <v>12</v>
       </c>
       <c r="F2" s="34">
-        <v>1170</v>
+        <v>1146</v>
       </c>
       <c r="G2" s="35" t="s">
         <v>69</v>
@@ -31332,7 +31332,7 @@
         <v>12</v>
       </c>
       <c r="F3" s="34">
-        <v>1329</v>
+        <v>1305</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -31378,7 +31378,7 @@
         <v>12</v>
       </c>
       <c r="F5" s="34">
-        <v>857</v>
+        <v>737</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>69</v>
@@ -31493,7 +31493,7 @@
         <v>48</v>
       </c>
       <c r="F10" s="34">
-        <v>2084</v>
+        <v>2036</v>
       </c>
       <c r="G10" s="35" t="s">
         <v>69</v>
@@ -31516,7 +31516,7 @@
         <v>48</v>
       </c>
       <c r="F11" s="34">
-        <v>2119</v>
+        <v>2071</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>69</v>
@@ -31539,7 +31539,7 @@
         <v>48</v>
       </c>
       <c r="F12" s="34">
-        <v>2795</v>
+        <v>2747</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>69</v>
@@ -31562,7 +31562,7 @@
         <v>48</v>
       </c>
       <c r="F13" s="34">
-        <v>1630</v>
+        <v>1582</v>
       </c>
       <c r="G13" s="35" t="s">
         <v>69</v>
@@ -31723,7 +31723,7 @@
         <v>24</v>
       </c>
       <c r="F20" s="34">
-        <v>1202</v>
+        <v>1154</v>
       </c>
       <c r="G20" s="35" t="s">
         <v>69</v>
@@ -31746,7 +31746,7 @@
         <v>24</v>
       </c>
       <c r="F21" s="34">
-        <v>1344</v>
+        <v>1296</v>
       </c>
       <c r="G21" s="35" t="s">
         <v>69</v>
@@ -31769,7 +31769,7 @@
         <v>24</v>
       </c>
       <c r="F22" s="34">
-        <v>1112</v>
+        <v>1064</v>
       </c>
       <c r="G22" s="35" t="s">
         <v>69</v>
@@ -31792,7 +31792,7 @@
         <v>24</v>
       </c>
       <c r="F23" s="34">
-        <v>1048</v>
+        <v>1000</v>
       </c>
       <c r="G23" s="35" t="s">
         <v>69</v>
@@ -31976,7 +31976,7 @@
         <v>12</v>
       </c>
       <c r="F31" s="34">
-        <v>613</v>
+        <v>553</v>
       </c>
       <c r="G31" s="35" t="s">
         <v>69</v>
@@ -32249,7 +32249,7 @@
         <v>288</v>
       </c>
       <c r="F10" s="34">
-        <v>9360</v>
+        <v>9072</v>
       </c>
       <c r="G10" s="35" t="s">
         <v>69</v>
@@ -32341,7 +32341,7 @@
         <v>96</v>
       </c>
       <c r="F14" s="34">
-        <v>9345</v>
+        <v>9249</v>
       </c>
       <c r="G14" s="35" t="s">
         <v>69</v>
@@ -32364,7 +32364,7 @@
         <v>96</v>
       </c>
       <c r="F15" s="34">
-        <v>7647</v>
+        <v>7551</v>
       </c>
       <c r="G15" s="35" t="s">
         <v>69</v>
@@ -32525,7 +32525,7 @@
         <v>192</v>
       </c>
       <c r="F22" s="36">
-        <v>646</v>
+        <v>454</v>
       </c>
       <c r="G22" s="37" t="s">
         <v>109</v>
@@ -32571,7 +32571,7 @@
         <v>96</v>
       </c>
       <c r="F24" s="34">
-        <v>3318</v>
+        <v>3222</v>
       </c>
       <c r="G24" s="35" t="s">
         <v>69</v>
@@ -33169,7 +33169,7 @@
         <v>144</v>
       </c>
       <c r="F50" s="34">
-        <v>15140</v>
+        <v>14996</v>
       </c>
       <c r="G50" s="35" t="s">
         <v>69</v>
@@ -33238,7 +33238,7 @@
         <v>96</v>
       </c>
       <c r="F53" s="34">
-        <v>14589</v>
+        <v>14109</v>
       </c>
       <c r="G53" s="35" t="s">
         <v>69</v>
@@ -33629,7 +33629,7 @@
         <v>200</v>
       </c>
       <c r="F70" s="34">
-        <v>9581</v>
+        <v>8581</v>
       </c>
       <c r="G70" s="35" t="s">
         <v>69</v>
@@ -33767,7 +33767,7 @@
         <v>200</v>
       </c>
       <c r="F76" s="34">
-        <v>60988</v>
+        <v>57988</v>
       </c>
       <c r="G76" s="35" t="s">
         <v>69</v>
@@ -33905,7 +33905,7 @@
         <v>1152</v>
       </c>
       <c r="F82" s="34">
-        <v>61922</v>
+        <v>56162</v>
       </c>
       <c r="G82" s="35" t="s">
         <v>69</v>
@@ -34020,7 +34020,7 @@
         <v>576</v>
       </c>
       <c r="F87" s="34">
-        <v>4143</v>
+        <v>2991</v>
       </c>
       <c r="G87" s="35" t="s">
         <v>69</v>
@@ -35443,7 +35443,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="34">
-        <v>82312</v>
+        <v>80312</v>
       </c>
       <c r="G4" s="35" t="s">
         <v>69</v>
@@ -35512,7 +35512,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="34">
-        <v>7425</v>
+        <v>6425</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>69</v>
@@ -35535,7 +35535,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="34">
-        <v>69708</v>
+        <v>68748</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>
@@ -35604,7 +35604,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="34">
-        <v>27933</v>
+        <v>27213</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>69</v>
@@ -35627,7 +35627,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="34">
-        <v>23453</v>
+        <v>18203</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>69</v>
@@ -35650,7 +35650,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="34">
-        <v>122627</v>
+        <v>117627</v>
       </c>
       <c r="G13" s="35" t="s">
         <v>69</v>
@@ -35739,7 +35739,7 @@
         <v>72</v>
       </c>
       <c r="F2" s="34">
-        <v>120032</v>
+        <v>119312</v>
       </c>
       <c r="G2" s="35" t="s">
         <v>69</v>
@@ -35762,7 +35762,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="34">
-        <v>212042</v>
+        <v>207042</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 10/03/2026, 07:24:43</t>
+    <t>Actualización: 10/03/2026, 07:29:35</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 10/03/2026, 07:29:35</t>
+    <t>Actualización: 10/03/2026, 07:39:58</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 10/03/2026, 07:39:58</t>
+    <t>Actualización: 10/03/2026, 08:00:35</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 10/03/2026, 08:22:27</t>
+    <t>Actualización: 10/03/2026, 09:48:45</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>
@@ -41,7 +41,7 @@
     <t>Unidades:</t>
   </si>
   <si>
-    <t>8,375,240</t>
+    <t>8,372,807</t>
   </si>
   <si>
     <t>Agotados:</t>
@@ -68,7 +68,7 @@
     <t>ACCESORIOS</t>
   </si>
   <si>
-    <t>938,726</t>
+    <t>938,432</t>
   </si>
   <si>
     <t>11.2%</t>
@@ -77,7 +77,7 @@
     <t>ARCHIVO</t>
   </si>
   <si>
-    <t>1,735,593</t>
+    <t>1,734,532</t>
   </si>
   <si>
     <t>20.7%</t>
@@ -86,16 +86,16 @@
     <t>DIBUJO</t>
   </si>
   <si>
-    <t>103,298</t>
-  </si>
-  <si>
-    <t>1.2%</t>
+    <t>104,898</t>
+  </si>
+  <si>
+    <t>1.3%</t>
   </si>
   <si>
     <t>DIDACTICOS</t>
   </si>
   <si>
-    <t>25,700</t>
+    <t>25,676</t>
   </si>
   <si>
     <t>0.3%</t>
@@ -104,7 +104,7 @@
     <t>ESCRITURA</t>
   </si>
   <si>
-    <t>1,438,019</t>
+    <t>1,437,983</t>
   </si>
   <si>
     <t>17.2%</t>
@@ -113,7 +113,7 @@
     <t>FORROS</t>
   </si>
   <si>
-    <t>841,204</t>
+    <t>840,186</t>
   </si>
   <si>
     <t>10.0%</t>
@@ -140,7 +140,7 @@
     <t>METALICA</t>
   </si>
   <si>
-    <t>248,477</t>
+    <t>247,453</t>
   </si>
   <si>
     <t>3.0%</t>
@@ -149,7 +149,7 @@
     <t>PEGAMENTOS</t>
   </si>
   <si>
-    <t>584,779</t>
+    <t>584,659</t>
   </si>
   <si>
     <t>7.0%</t>
@@ -167,7 +167,7 @@
     <t>PINTURA</t>
   </si>
   <si>
-    <t>1,226,053</t>
+    <t>1,225,897</t>
   </si>
   <si>
     <t>14.6%</t>
@@ -176,7 +176,7 @@
     <t>REPRESENTADAS</t>
   </si>
   <si>
-    <t>318,223</t>
+    <t>317,923</t>
   </si>
   <si>
     <t>3.8%</t>
@@ -10217,13 +10217,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="6">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="7">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -10978,7 +10978,7 @@
         <v>500</v>
       </c>
       <c r="F22" s="34">
-        <v>22084</v>
+        <v>21084</v>
       </c>
       <c r="G22" s="35" t="s">
         <v>69</v>
@@ -11070,7 +11070,7 @@
         <v>120</v>
       </c>
       <c r="F26" s="34">
-        <v>2864</v>
+        <v>2840</v>
       </c>
       <c r="G26" s="35" t="s">
         <v>69</v>
@@ -11527,7 +11527,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="34">
-        <v>79669</v>
+        <v>79549</v>
       </c>
       <c r="G14" s="35" t="s">
         <v>69</v>
@@ -16535,7 +16535,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="34">
-        <v>95653</v>
+        <v>95509</v>
       </c>
       <c r="G17" s="35" t="s">
         <v>69</v>
@@ -16742,7 +16742,7 @@
         <v>60</v>
       </c>
       <c r="F26" s="34">
-        <v>32313</v>
+        <v>32301</v>
       </c>
       <c r="G26" s="35" t="s">
         <v>69</v>
@@ -17981,7 +17981,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="34">
-        <v>5900</v>
+        <v>5600</v>
       </c>
       <c r="G2" s="35" t="s">
         <v>69</v>
@@ -22762,7 +22762,7 @@
         <v>36</v>
       </c>
       <c r="F12" s="34">
-        <v>3709</v>
+        <v>3703</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>69</v>
@@ -23268,7 +23268,7 @@
         <v>120</v>
       </c>
       <c r="F34" s="34">
-        <v>47264</v>
+        <v>47204</v>
       </c>
       <c r="G34" s="35" t="s">
         <v>69</v>
@@ -23314,7 +23314,7 @@
         <v>120</v>
       </c>
       <c r="F36" s="34">
-        <v>26255</v>
+        <v>26195</v>
       </c>
       <c r="G36" s="35" t="s">
         <v>69</v>
@@ -23337,7 +23337,7 @@
         <v>120</v>
       </c>
       <c r="F37" s="34">
-        <v>7090</v>
+        <v>7030</v>
       </c>
       <c r="G37" s="35" t="s">
         <v>69</v>
@@ -23429,7 +23429,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="34">
-        <v>6242</v>
+        <v>6170</v>
       </c>
       <c r="G41" s="35" t="s">
         <v>69</v>
@@ -23866,7 +23866,7 @@
         <v>144</v>
       </c>
       <c r="F60" s="34">
-        <v>3866</v>
+        <v>3830</v>
       </c>
       <c r="G60" s="35" t="s">
         <v>69</v>
@@ -24829,7 +24829,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="34">
-        <v>15754</v>
+        <v>15604</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>69</v>
@@ -24875,7 +24875,7 @@
         <v>50</v>
       </c>
       <c r="F7" s="34">
-        <v>6939</v>
+        <v>6914</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>69</v>
@@ -24921,7 +24921,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="34">
-        <v>3493</v>
+        <v>3468</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>69</v>
@@ -24944,7 +24944,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="34">
-        <v>13654</v>
+        <v>13629</v>
       </c>
       <c r="G10" s="35" t="s">
         <v>69</v>
@@ -24967,7 +24967,7 @@
         <v>50</v>
       </c>
       <c r="F11" s="34">
-        <v>4960</v>
+        <v>4935</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>69</v>
@@ -24990,7 +24990,7 @@
         <v>50</v>
       </c>
       <c r="F12" s="34">
-        <v>2859</v>
+        <v>2834</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>69</v>
@@ -25013,7 +25013,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="34">
-        <v>4325</v>
+        <v>4300</v>
       </c>
       <c r="G13" s="35" t="s">
         <v>69</v>
@@ -25035,11 +25035,11 @@
       <c r="E14">
         <v>50</v>
       </c>
-      <c r="F14" s="36">
-        <v>21</v>
-      </c>
-      <c r="G14" s="37" t="s">
-        <v>109</v>
+      <c r="F14" s="32">
+        <v>0</v>
+      </c>
+      <c r="G14" s="33" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -25082,7 +25082,7 @@
         <v>50</v>
       </c>
       <c r="F16" s="34">
-        <v>4892</v>
+        <v>4867</v>
       </c>
       <c r="G16" s="35" t="s">
         <v>69</v>
@@ -25105,7 +25105,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="34">
-        <v>7882</v>
+        <v>7857</v>
       </c>
       <c r="G17" s="35" t="s">
         <v>69</v>
@@ -25128,7 +25128,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="34">
-        <v>15119</v>
+        <v>15094</v>
       </c>
       <c r="G18" s="35" t="s">
         <v>69</v>
@@ -25151,7 +25151,7 @@
         <v>50</v>
       </c>
       <c r="F19" s="34">
-        <v>1897</v>
+        <v>1872</v>
       </c>
       <c r="G19" s="35" t="s">
         <v>69</v>
@@ -25197,7 +25197,7 @@
         <v>50</v>
       </c>
       <c r="F21" s="36">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="G21" s="37" t="s">
         <v>109</v>
@@ -25220,7 +25220,7 @@
         <v>50</v>
       </c>
       <c r="F22" s="34">
-        <v>493</v>
+        <v>468</v>
       </c>
       <c r="G22" s="35" t="s">
         <v>69</v>
@@ -26301,7 +26301,7 @@
         <v>100</v>
       </c>
       <c r="F69" s="34">
-        <v>41458</v>
+        <v>41408</v>
       </c>
       <c r="G69" s="35" t="s">
         <v>69</v>
@@ -26485,7 +26485,7 @@
         <v>100</v>
       </c>
       <c r="F77" s="34">
-        <v>42324</v>
+        <v>42274</v>
       </c>
       <c r="G77" s="35" t="s">
         <v>69</v>
@@ -26508,7 +26508,7 @@
         <v>100</v>
       </c>
       <c r="F78" s="34">
-        <v>43284</v>
+        <v>43234</v>
       </c>
       <c r="G78" s="35" t="s">
         <v>69</v>
@@ -27451,7 +27451,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="34">
-        <v>22716</v>
+        <v>22476</v>
       </c>
       <c r="G119" s="35" t="s">
         <v>69</v>
@@ -30579,7 +30579,7 @@
         <v>100</v>
       </c>
       <c r="F255" s="34">
-        <v>211687</v>
+        <v>211487</v>
       </c>
       <c r="G255" s="35" t="s">
         <v>69</v>
@@ -30898,7 +30898,7 @@
         <v>1000</v>
       </c>
       <c r="F2" s="36">
-        <v>3238</v>
+        <v>3088</v>
       </c>
       <c r="G2" s="37" t="s">
         <v>109</v>
@@ -30921,7 +30921,7 @@
         <v>500</v>
       </c>
       <c r="F3" s="34">
-        <v>6965</v>
+        <v>8815</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -31036,7 +31036,7 @@
         <v>400</v>
       </c>
       <c r="F8" s="34">
-        <v>16323</v>
+        <v>16273</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>
@@ -31059,7 +31059,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="34">
-        <v>33772</v>
+        <v>33722</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>69</v>
@@ -31838,7 +31838,7 @@
         <v>24</v>
       </c>
       <c r="F25" s="34">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="G25" s="35" t="s">
         <v>69</v>
@@ -33997,7 +33997,7 @@
         <v>576</v>
       </c>
       <c r="F86" s="34">
-        <v>19868</v>
+        <v>19832</v>
       </c>
       <c r="G86" s="35" t="s">
         <v>69</v>
@@ -35397,7 +35397,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="34">
-        <v>71888</v>
+        <v>71588</v>
       </c>
       <c r="G2" s="35" t="s">
         <v>69</v>
@@ -35420,7 +35420,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="34">
-        <v>229877</v>
+        <v>229477</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -35535,7 +35535,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="34">
-        <v>68748</v>
+        <v>68700</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>
@@ -35558,7 +35558,7 @@
         <v>48</v>
       </c>
       <c r="F9" s="34">
-        <v>83713</v>
+        <v>83665</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>69</v>
@@ -35604,7 +35604,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="34">
-        <v>27213</v>
+        <v>27141</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>69</v>
@@ -35627,7 +35627,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="34">
-        <v>18203</v>
+        <v>18153</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>69</v>
@@ -35650,7 +35650,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="34">
-        <v>117627</v>
+        <v>117527</v>
       </c>
       <c r="G13" s="35" t="s">
         <v>69</v>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 10/03/2026, 09:48:45</t>
+    <t>Actualización: 10/03/2026, 11:00:03</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>
@@ -41,7 +41,7 @@
     <t>Unidades:</t>
   </si>
   <si>
-    <t>8,372,807</t>
+    <t>8,351,314</t>
   </si>
   <si>
     <t>Agotados:</t>
@@ -68,7 +68,7 @@
     <t>ACCESORIOS</t>
   </si>
   <si>
-    <t>938,432</t>
+    <t>937,116</t>
   </si>
   <si>
     <t>11.2%</t>
@@ -77,7 +77,7 @@
     <t>ARCHIVO</t>
   </si>
   <si>
-    <t>1,734,532</t>
+    <t>1,729,152</t>
   </si>
   <si>
     <t>20.7%</t>
@@ -104,16 +104,16 @@
     <t>ESCRITURA</t>
   </si>
   <si>
-    <t>1,437,983</t>
-  </si>
-  <si>
-    <t>17.2%</t>
+    <t>1,429,994</t>
+  </si>
+  <si>
+    <t>17.1%</t>
   </si>
   <si>
     <t>FORROS</t>
   </si>
   <si>
-    <t>840,186</t>
+    <t>834,561</t>
   </si>
   <si>
     <t>10.0%</t>
@@ -122,7 +122,7 @@
     <t>MANUALIDADES</t>
   </si>
   <si>
-    <t>426,357</t>
+    <t>425,997</t>
   </si>
   <si>
     <t>5.1%</t>
@@ -149,7 +149,7 @@
     <t>PEGAMENTOS</t>
   </si>
   <si>
-    <t>584,659</t>
+    <t>583,891</t>
   </si>
   <si>
     <t>7.0%</t>
@@ -167,16 +167,16 @@
     <t>PINTURA</t>
   </si>
   <si>
-    <t>1,225,897</t>
-  </si>
-  <si>
-    <t>14.6%</t>
+    <t>1,225,245</t>
+  </si>
+  <si>
+    <t>14.7%</t>
   </si>
   <si>
     <t>REPRESENTADAS</t>
   </si>
   <si>
-    <t>317,923</t>
+    <t>318,520</t>
   </si>
   <si>
     <t>3.8%</t>
@@ -10217,13 +10217,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="6">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="7">
-        <v>252</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11274,7 +11274,7 @@
         <v>384</v>
       </c>
       <c r="F3" s="34">
-        <v>34348</v>
+        <v>33580</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -16328,7 +16328,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="34">
-        <v>14495</v>
+        <v>14493</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>
@@ -16535,7 +16535,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="34">
-        <v>95509</v>
+        <v>95221</v>
       </c>
       <c r="G17" s="35" t="s">
         <v>69</v>
@@ -16581,7 +16581,7 @@
         <v>36</v>
       </c>
       <c r="F19" s="34">
-        <v>4991</v>
+        <v>4989</v>
       </c>
       <c r="G19" s="35" t="s">
         <v>69</v>
@@ -16719,7 +16719,7 @@
         <v>120</v>
       </c>
       <c r="F25" s="34">
-        <v>18308</v>
+        <v>17948</v>
       </c>
       <c r="G25" s="35" t="s">
         <v>69</v>
@@ -17981,7 +17981,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="34">
-        <v>5600</v>
+        <v>5780</v>
       </c>
       <c r="G2" s="35" t="s">
         <v>69</v>
@@ -18050,7 +18050,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="34">
-        <v>20189</v>
+        <v>20389</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>69</v>
@@ -18441,7 +18441,7 @@
         <v>120</v>
       </c>
       <c r="F22" s="34">
-        <v>2053</v>
+        <v>2103</v>
       </c>
       <c r="G22" s="35" t="s">
         <v>69</v>
@@ -18579,7 +18579,7 @@
         <v>120</v>
       </c>
       <c r="F28" s="34">
-        <v>9192</v>
+        <v>9244</v>
       </c>
       <c r="G28" s="35" t="s">
         <v>69</v>
@@ -18648,7 +18648,7 @@
         <v>120</v>
       </c>
       <c r="F31" s="34">
-        <v>3120</v>
+        <v>3420</v>
       </c>
       <c r="G31" s="35" t="s">
         <v>69</v>
@@ -19637,7 +19637,7 @@
         <v>240</v>
       </c>
       <c r="F74" s="34">
-        <v>1529</v>
+        <v>1624</v>
       </c>
       <c r="G74" s="35" t="s">
         <v>69</v>
@@ -19752,7 +19752,7 @@
         <v>120</v>
       </c>
       <c r="F79" s="36">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="G79" s="37" t="s">
         <v>109</v>
@@ -19958,11 +19958,11 @@
       <c r="E88">
         <v>20</v>
       </c>
-      <c r="F88" s="32">
-        <v>0</v>
-      </c>
-      <c r="G88" s="33" t="s">
-        <v>65</v>
+      <c r="F88" s="36">
+        <v>10</v>
+      </c>
+      <c r="G88" s="37" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -20188,11 +20188,11 @@
       <c r="E98">
         <v>5</v>
       </c>
-      <c r="F98" s="32">
-        <v>0</v>
-      </c>
-      <c r="G98" s="33" t="s">
-        <v>65</v>
+      <c r="F98" s="36">
+        <v>20</v>
+      </c>
+      <c r="G98" s="37" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -20464,11 +20464,11 @@
       <c r="E110">
         <v>54</v>
       </c>
-      <c r="F110" s="34">
-        <v>1093</v>
-      </c>
-      <c r="G110" s="35" t="s">
-        <v>69</v>
+      <c r="F110" s="36">
+        <v>93</v>
+      </c>
+      <c r="G110" s="37" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -22328,7 +22328,7 @@
         <v>50</v>
       </c>
       <c r="F191" s="34">
-        <v>1873</v>
+        <v>2173</v>
       </c>
       <c r="G191" s="35" t="s">
         <v>69</v>
@@ -22351,7 +22351,7 @@
         <v>50</v>
       </c>
       <c r="F192" s="34">
-        <v>1210</v>
+        <v>1510</v>
       </c>
       <c r="G192" s="35" t="s">
         <v>69</v>
@@ -22578,7 +22578,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="34">
-        <v>11181</v>
+        <v>11081</v>
       </c>
       <c r="G4" s="35" t="s">
         <v>69</v>
@@ -23038,7 +23038,7 @@
         <v>60</v>
       </c>
       <c r="F24" s="34">
-        <v>3513</v>
+        <v>3453</v>
       </c>
       <c r="G24" s="35" t="s">
         <v>69</v>
@@ -23475,7 +23475,7 @@
         <v>144</v>
       </c>
       <c r="F43" s="34">
-        <v>9539</v>
+        <v>9251</v>
       </c>
       <c r="G43" s="35" t="s">
         <v>69</v>
@@ -23498,7 +23498,7 @@
         <v>144</v>
       </c>
       <c r="F44" s="34">
-        <v>10201</v>
+        <v>9913</v>
       </c>
       <c r="G44" s="35" t="s">
         <v>69</v>
@@ -23521,7 +23521,7 @@
         <v>144</v>
       </c>
       <c r="F45" s="34">
-        <v>10602</v>
+        <v>10314</v>
       </c>
       <c r="G45" s="35" t="s">
         <v>69</v>
@@ -23544,7 +23544,7 @@
         <v>144</v>
       </c>
       <c r="F46" s="34">
-        <v>8563</v>
+        <v>8274</v>
       </c>
       <c r="G46" s="35" t="s">
         <v>69</v>
@@ -23567,7 +23567,7 @@
         <v>144</v>
       </c>
       <c r="F47" s="34">
-        <v>3286</v>
+        <v>3285</v>
       </c>
       <c r="G47" s="35" t="s">
         <v>69</v>
@@ -24648,7 +24648,7 @@
         <v>144</v>
       </c>
       <c r="F94" s="36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G94" s="37" t="s">
         <v>109</v>
@@ -24921,7 +24921,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="34">
-        <v>3468</v>
+        <v>3168</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>69</v>
@@ -25058,11 +25058,11 @@
       <c r="E15">
         <v>50</v>
       </c>
-      <c r="F15" s="32">
-        <v>0</v>
-      </c>
-      <c r="G15" s="33" t="s">
-        <v>65</v>
+      <c r="F15" s="36">
+        <v>5</v>
+      </c>
+      <c r="G15" s="37" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -27451,7 +27451,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="34">
-        <v>22476</v>
+        <v>17391</v>
       </c>
       <c r="G119" s="35" t="s">
         <v>69</v>
@@ -32295,7 +32295,7 @@
         <v>144</v>
       </c>
       <c r="F12" s="34">
-        <v>11851</v>
+        <v>11850</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>69</v>
@@ -33215,7 +33215,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="34">
-        <v>6779</v>
+        <v>6491</v>
       </c>
       <c r="G52" s="35" t="s">
         <v>69</v>
@@ -33514,7 +33514,7 @@
         <v>200</v>
       </c>
       <c r="F65" s="34">
-        <v>4906</v>
+        <v>3046</v>
       </c>
       <c r="G65" s="35" t="s">
         <v>69</v>
@@ -33537,7 +33537,7 @@
         <v>200</v>
       </c>
       <c r="F66" s="34">
-        <v>7347</v>
+        <v>5657</v>
       </c>
       <c r="G66" s="35" t="s">
         <v>69</v>
@@ -33560,7 +33560,7 @@
         <v>200</v>
       </c>
       <c r="F67" s="34">
-        <v>33638</v>
+        <v>32678</v>
       </c>
       <c r="G67" s="35" t="s">
         <v>69</v>
@@ -33629,7 +33629,7 @@
         <v>200</v>
       </c>
       <c r="F70" s="34">
-        <v>8581</v>
+        <v>7171</v>
       </c>
       <c r="G70" s="35" t="s">
         <v>69</v>
@@ -33651,11 +33651,11 @@
       <c r="E71">
         <v>200</v>
       </c>
-      <c r="F71" s="34">
-        <v>1246</v>
-      </c>
-      <c r="G71" s="35" t="s">
-        <v>69</v>
+      <c r="F71" s="36">
+        <v>966</v>
+      </c>
+      <c r="G71" s="37" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -34134,11 +34134,11 @@
       <c r="E92">
         <v>576</v>
       </c>
-      <c r="F92" s="34">
-        <v>4231</v>
-      </c>
-      <c r="G92" s="35" t="s">
-        <v>69</v>
+      <c r="F92" s="36">
+        <v>2731</v>
+      </c>
+      <c r="G92" s="37" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -35420,7 +35420,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="34">
-        <v>229477</v>
+        <v>226977</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -35512,7 +35512,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="34">
-        <v>6425</v>
+        <v>5675</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>69</v>
@@ -35627,7 +35627,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="34">
-        <v>18153</v>
+        <v>15778</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>69</v>
@@ -35762,7 +35762,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="34">
-        <v>207042</v>
+        <v>206682</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 10/03/2026, 11:00:03</t>
+    <t>Actualización: 10/03/2026, 12:03:30</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>
@@ -41,7 +41,7 @@
     <t>Unidades:</t>
   </si>
   <si>
-    <t>8,351,314</t>
+    <t>8,331,389</t>
   </si>
   <si>
     <t>Agotados:</t>
@@ -68,7 +68,7 @@
     <t>ACCESORIOS</t>
   </si>
   <si>
-    <t>937,116</t>
+    <t>935,445</t>
   </si>
   <si>
     <t>11.2%</t>
@@ -77,7 +77,7 @@
     <t>ARCHIVO</t>
   </si>
   <si>
-    <t>1,729,152</t>
+    <t>1,727,625</t>
   </si>
   <si>
     <t>20.7%</t>
@@ -86,7 +86,7 @@
     <t>DIBUJO</t>
   </si>
   <si>
-    <t>104,898</t>
+    <t>104,698</t>
   </si>
   <si>
     <t>1.3%</t>
@@ -104,7 +104,7 @@
     <t>ESCRITURA</t>
   </si>
   <si>
-    <t>1,429,994</t>
+    <t>1,423,835</t>
   </si>
   <si>
     <t>17.1%</t>
@@ -113,7 +113,7 @@
     <t>FORROS</t>
   </si>
   <si>
-    <t>834,561</t>
+    <t>834,465</t>
   </si>
   <si>
     <t>10.0%</t>
@@ -131,7 +131,7 @@
     <t>MASCOTAS</t>
   </si>
   <si>
-    <t>9,093</t>
+    <t>8,985</t>
   </si>
   <si>
     <t>0.1%</t>
@@ -140,16 +140,16 @@
     <t>METALICA</t>
   </si>
   <si>
-    <t>247,453</t>
-  </si>
-  <si>
-    <t>3.0%</t>
+    <t>244,953</t>
+  </si>
+  <si>
+    <t>2.9%</t>
   </si>
   <si>
     <t>PEGAMENTOS</t>
   </si>
   <si>
-    <t>583,891</t>
+    <t>583,651</t>
   </si>
   <si>
     <t>7.0%</t>
@@ -158,7 +158,7 @@
     <t>PELOTAS</t>
   </si>
   <si>
-    <t>479,718</t>
+    <t>477,389</t>
   </si>
   <si>
     <t>5.7%</t>
@@ -167,7 +167,7 @@
     <t>PINTURA</t>
   </si>
   <si>
-    <t>1,225,245</t>
+    <t>1,224,674</t>
   </si>
   <si>
     <t>14.7%</t>
@@ -176,7 +176,7 @@
     <t>REPRESENTADAS</t>
   </si>
   <si>
-    <t>318,520</t>
+    <t>313,996</t>
   </si>
   <si>
     <t>3.8%</t>
@@ -10217,13 +10217,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="6">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="7">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -10978,7 +10978,7 @@
         <v>500</v>
       </c>
       <c r="F22" s="34">
-        <v>21084</v>
+        <v>18584</v>
       </c>
       <c r="G22" s="35" t="s">
         <v>69</v>
@@ -11527,7 +11527,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="34">
-        <v>79549</v>
+        <v>79309</v>
       </c>
       <c r="G14" s="35" t="s">
         <v>69</v>
@@ -12743,7 +12743,7 @@
         <v>48</v>
       </c>
       <c r="F44" s="34">
-        <v>6447</v>
+        <v>6183</v>
       </c>
       <c r="G44" s="35" t="s">
         <v>69</v>
@@ -13019,7 +13019,7 @@
         <v>36</v>
       </c>
       <c r="F56" s="36">
-        <v>159</v>
+        <v>65</v>
       </c>
       <c r="G56" s="37" t="s">
         <v>109</v>
@@ -13111,7 +13111,7 @@
         <v>36</v>
       </c>
       <c r="F60" s="34">
-        <v>1375</v>
+        <v>1351</v>
       </c>
       <c r="G60" s="35" t="s">
         <v>69</v>
@@ -13570,11 +13570,11 @@
       <c r="E80">
         <v>60</v>
       </c>
-      <c r="F80" s="36">
-        <v>11</v>
-      </c>
-      <c r="G80" s="37" t="s">
-        <v>109</v>
+      <c r="F80" s="32">
+        <v>0</v>
+      </c>
+      <c r="G80" s="33" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -13617,7 +13617,7 @@
         <v>60</v>
       </c>
       <c r="F82" s="34">
-        <v>1094</v>
+        <v>938</v>
       </c>
       <c r="G82" s="35" t="s">
         <v>69</v>
@@ -13824,7 +13824,7 @@
         <v>60</v>
       </c>
       <c r="F91" s="34">
-        <v>1517</v>
+        <v>1433</v>
       </c>
       <c r="G91" s="35" t="s">
         <v>69</v>
@@ -14169,7 +14169,7 @@
         <v>60</v>
       </c>
       <c r="F106" s="34">
-        <v>1458</v>
+        <v>1386</v>
       </c>
       <c r="G106" s="35" t="s">
         <v>69</v>
@@ -14238,7 +14238,7 @@
         <v>60</v>
       </c>
       <c r="F109" s="34">
-        <v>1668</v>
+        <v>1644</v>
       </c>
       <c r="G109" s="35" t="s">
         <v>69</v>
@@ -15986,7 +15986,7 @@
         <v>400</v>
       </c>
       <c r="F185" s="34">
-        <v>76550</v>
+        <v>75750</v>
       </c>
       <c r="G185" s="35" t="s">
         <v>69</v>
@@ -16009,7 +16009,7 @@
         <v>400</v>
       </c>
       <c r="F186" s="34">
-        <v>71765</v>
+        <v>70965</v>
       </c>
       <c r="G186" s="35" t="s">
         <v>69</v>
@@ -16397,7 +16397,7 @@
         <v>144</v>
       </c>
       <c r="F11" s="34">
-        <v>52785</v>
+        <v>52784</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>69</v>
@@ -16535,7 +16535,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="34">
-        <v>95221</v>
+        <v>94973</v>
       </c>
       <c r="G17" s="35" t="s">
         <v>69</v>
@@ -16673,7 +16673,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="34">
-        <v>12968</v>
+        <v>12967</v>
       </c>
       <c r="G23" s="35" t="s">
         <v>69</v>
@@ -16811,7 +16811,7 @@
         <v>576</v>
       </c>
       <c r="F29" s="34">
-        <v>51222</v>
+        <v>51102</v>
       </c>
       <c r="G29" s="35" t="s">
         <v>69</v>
@@ -17225,7 +17225,7 @@
         <v>288</v>
       </c>
       <c r="F47" s="34">
-        <v>8672</v>
+        <v>8472</v>
       </c>
       <c r="G47" s="35" t="s">
         <v>69</v>
@@ -17593,7 +17593,7 @@
         <v>12</v>
       </c>
       <c r="F63" s="36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G63" s="37" t="s">
         <v>109</v>
@@ -18050,7 +18050,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="34">
-        <v>20389</v>
+        <v>20189</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>69</v>
@@ -18441,7 +18441,7 @@
         <v>120</v>
       </c>
       <c r="F22" s="34">
-        <v>2103</v>
+        <v>1803</v>
       </c>
       <c r="G22" s="35" t="s">
         <v>69</v>
@@ -18579,7 +18579,7 @@
         <v>120</v>
       </c>
       <c r="F28" s="34">
-        <v>9244</v>
+        <v>8444</v>
       </c>
       <c r="G28" s="35" t="s">
         <v>69</v>
@@ -18648,7 +18648,7 @@
         <v>120</v>
       </c>
       <c r="F31" s="34">
-        <v>3420</v>
+        <v>2820</v>
       </c>
       <c r="G31" s="35" t="s">
         <v>69</v>
@@ -19637,7 +19637,7 @@
         <v>240</v>
       </c>
       <c r="F74" s="34">
-        <v>1624</v>
+        <v>1356</v>
       </c>
       <c r="G74" s="35" t="s">
         <v>69</v>
@@ -19752,7 +19752,7 @@
         <v>120</v>
       </c>
       <c r="F79" s="36">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="G79" s="37" t="s">
         <v>109</v>
@@ -19821,7 +19821,7 @@
         <v>40</v>
       </c>
       <c r="F82" s="34">
-        <v>2596</v>
+        <v>1896</v>
       </c>
       <c r="G82" s="35" t="s">
         <v>69</v>
@@ -20188,11 +20188,11 @@
       <c r="E98">
         <v>5</v>
       </c>
-      <c r="F98" s="36">
-        <v>20</v>
-      </c>
-      <c r="G98" s="37" t="s">
-        <v>109</v>
+      <c r="F98" s="32">
+        <v>0</v>
+      </c>
+      <c r="G98" s="33" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -22328,7 +22328,7 @@
         <v>50</v>
       </c>
       <c r="F191" s="34">
-        <v>2173</v>
+        <v>1373</v>
       </c>
       <c r="G191" s="35" t="s">
         <v>69</v>
@@ -22351,7 +22351,7 @@
         <v>50</v>
       </c>
       <c r="F192" s="34">
-        <v>1510</v>
+        <v>710</v>
       </c>
       <c r="G192" s="35" t="s">
         <v>69</v>
@@ -22946,7 +22946,7 @@
         <v>36</v>
       </c>
       <c r="F20" s="34">
-        <v>5384</v>
+        <v>5348</v>
       </c>
       <c r="G20" s="35" t="s">
         <v>69</v>
@@ -22992,7 +22992,7 @@
         <v>36</v>
       </c>
       <c r="F22" s="34">
-        <v>15898</v>
+        <v>15798</v>
       </c>
       <c r="G22" s="35" t="s">
         <v>69</v>
@@ -23199,7 +23199,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="34">
-        <v>138643</v>
+        <v>137620</v>
       </c>
       <c r="G31" s="35" t="s">
         <v>69</v>
@@ -23360,7 +23360,7 @@
         <v>120</v>
       </c>
       <c r="F38" s="34">
-        <v>100416</v>
+        <v>99906</v>
       </c>
       <c r="G38" s="35" t="s">
         <v>69</v>
@@ -23498,7 +23498,7 @@
         <v>144</v>
       </c>
       <c r="F44" s="34">
-        <v>9913</v>
+        <v>9912</v>
       </c>
       <c r="G44" s="35" t="s">
         <v>69</v>
@@ -24372,7 +24372,7 @@
         <v>144</v>
       </c>
       <c r="F82" s="34">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="G82" s="35" t="s">
         <v>69</v>
@@ -24875,7 +24875,7 @@
         <v>50</v>
       </c>
       <c r="F7" s="34">
-        <v>6914</v>
+        <v>6864</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>69</v>
@@ -24921,7 +24921,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="34">
-        <v>3168</v>
+        <v>3118</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>69</v>
@@ -24944,7 +24944,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="34">
-        <v>13629</v>
+        <v>13579</v>
       </c>
       <c r="G10" s="35" t="s">
         <v>69</v>
@@ -25105,7 +25105,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="34">
-        <v>7857</v>
+        <v>7807</v>
       </c>
       <c r="G17" s="35" t="s">
         <v>69</v>
@@ -25220,7 +25220,7 @@
         <v>50</v>
       </c>
       <c r="F22" s="34">
-        <v>468</v>
+        <v>418</v>
       </c>
       <c r="G22" s="35" t="s">
         <v>69</v>
@@ -26278,7 +26278,7 @@
         <v>100</v>
       </c>
       <c r="F68" s="34">
-        <v>38116</v>
+        <v>37916</v>
       </c>
       <c r="G68" s="35" t="s">
         <v>69</v>
@@ -26301,7 +26301,7 @@
         <v>100</v>
       </c>
       <c r="F69" s="34">
-        <v>41408</v>
+        <v>41208</v>
       </c>
       <c r="G69" s="35" t="s">
         <v>69</v>
@@ -26346,11 +26346,11 @@
       <c r="E71">
         <v>100</v>
       </c>
-      <c r="F71" s="36">
-        <v>100</v>
-      </c>
-      <c r="G71" s="37" t="s">
-        <v>109</v>
+      <c r="F71" s="32">
+        <v>0</v>
+      </c>
+      <c r="G71" s="33" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -27658,7 +27658,7 @@
         <v>24</v>
       </c>
       <c r="F128" s="34">
-        <v>5534</v>
+        <v>5486</v>
       </c>
       <c r="G128" s="35" t="s">
         <v>69</v>
@@ -27681,7 +27681,7 @@
         <v>24</v>
       </c>
       <c r="F129" s="34">
-        <v>8160</v>
+        <v>8112</v>
       </c>
       <c r="G129" s="35" t="s">
         <v>69</v>
@@ -27704,7 +27704,7 @@
         <v>24</v>
       </c>
       <c r="F130" s="34">
-        <v>15659</v>
+        <v>15611</v>
       </c>
       <c r="G130" s="35" t="s">
         <v>69</v>
@@ -27727,7 +27727,7 @@
         <v>24</v>
       </c>
       <c r="F131" s="34">
-        <v>9762</v>
+        <v>9714</v>
       </c>
       <c r="G131" s="35" t="s">
         <v>69</v>
@@ -30004,7 +30004,7 @@
         <v>5</v>
       </c>
       <c r="F230" s="34">
-        <v>917</v>
+        <v>857</v>
       </c>
       <c r="G230" s="35" t="s">
         <v>69</v>
@@ -30050,7 +30050,7 @@
         <v>5</v>
       </c>
       <c r="F232" s="34">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="G232" s="35" t="s">
         <v>69</v>
@@ -30095,11 +30095,11 @@
       <c r="E234">
         <v>5</v>
       </c>
-      <c r="F234" s="34">
-        <v>72</v>
-      </c>
-      <c r="G234" s="35" t="s">
-        <v>69</v>
+      <c r="F234" s="36">
+        <v>22</v>
+      </c>
+      <c r="G234" s="37" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
@@ -30119,7 +30119,7 @@
         <v>5</v>
       </c>
       <c r="F235" s="34">
-        <v>361</v>
+        <v>336</v>
       </c>
       <c r="G235" s="35" t="s">
         <v>69</v>
@@ -30142,7 +30142,7 @@
         <v>5</v>
       </c>
       <c r="F236" s="34">
-        <v>257</v>
+        <v>217</v>
       </c>
       <c r="G236" s="35" t="s">
         <v>69</v>
@@ -30165,7 +30165,7 @@
         <v>5</v>
       </c>
       <c r="F237" s="34">
-        <v>257</v>
+        <v>212</v>
       </c>
       <c r="G237" s="35" t="s">
         <v>69</v>
@@ -30188,7 +30188,7 @@
         <v>5</v>
       </c>
       <c r="F238" s="34">
-        <v>231</v>
+        <v>181</v>
       </c>
       <c r="G238" s="35" t="s">
         <v>69</v>
@@ -30211,7 +30211,7 @@
         <v>5</v>
       </c>
       <c r="F239" s="34">
-        <v>277</v>
+        <v>247</v>
       </c>
       <c r="G239" s="35" t="s">
         <v>69</v>
@@ -30257,7 +30257,7 @@
         <v>5</v>
       </c>
       <c r="F241" s="34">
-        <v>1695</v>
+        <v>1515</v>
       </c>
       <c r="G241" s="35" t="s">
         <v>69</v>
@@ -30372,7 +30372,7 @@
         <v>5</v>
       </c>
       <c r="F246" s="34">
-        <v>236</v>
+        <v>191</v>
       </c>
       <c r="G246" s="35" t="s">
         <v>69</v>
@@ -30395,7 +30395,7 @@
         <v>5</v>
       </c>
       <c r="F247" s="34">
-        <v>382</v>
+        <v>352</v>
       </c>
       <c r="G247" s="35" t="s">
         <v>69</v>
@@ -31059,7 +31059,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="34">
-        <v>33722</v>
+        <v>33522</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>69</v>
@@ -32387,7 +32387,7 @@
         <v>96</v>
       </c>
       <c r="F16" s="34">
-        <v>9579</v>
+        <v>9479</v>
       </c>
       <c r="G16" s="35" t="s">
         <v>69</v>
@@ -32410,7 +32410,7 @@
         <v>192</v>
       </c>
       <c r="F17" s="34">
-        <v>14522</v>
+        <v>14322</v>
       </c>
       <c r="G17" s="35" t="s">
         <v>69</v>
@@ -32502,7 +32502,7 @@
         <v>192</v>
       </c>
       <c r="F21" s="34">
-        <v>9266</v>
+        <v>9265</v>
       </c>
       <c r="G21" s="35" t="s">
         <v>69</v>
@@ -32594,7 +32594,7 @@
         <v>48</v>
       </c>
       <c r="F25" s="34">
-        <v>3746</v>
+        <v>3650</v>
       </c>
       <c r="G25" s="35" t="s">
         <v>69</v>
@@ -32686,7 +32686,7 @@
         <v>192</v>
       </c>
       <c r="F29" s="34">
-        <v>13781</v>
+        <v>13681</v>
       </c>
       <c r="G29" s="35" t="s">
         <v>69</v>
@@ -32709,7 +32709,7 @@
         <v>192</v>
       </c>
       <c r="F30" s="34">
-        <v>30886</v>
+        <v>30786</v>
       </c>
       <c r="G30" s="35" t="s">
         <v>69</v>
@@ -33238,7 +33238,7 @@
         <v>96</v>
       </c>
       <c r="F53" s="34">
-        <v>14109</v>
+        <v>14009</v>
       </c>
       <c r="G53" s="35" t="s">
         <v>69</v>
@@ -33905,7 +33905,7 @@
         <v>1152</v>
       </c>
       <c r="F82" s="34">
-        <v>56162</v>
+        <v>55802</v>
       </c>
       <c r="G82" s="35" t="s">
         <v>69</v>
@@ -33997,7 +33997,7 @@
         <v>576</v>
       </c>
       <c r="F86" s="34">
-        <v>19832</v>
+        <v>19831</v>
       </c>
       <c r="G86" s="35" t="s">
         <v>69</v>
@@ -34135,7 +34135,7 @@
         <v>576</v>
       </c>
       <c r="F92" s="36">
-        <v>2731</v>
+        <v>1231</v>
       </c>
       <c r="G92" s="37" t="s">
         <v>109</v>
@@ -34227,7 +34227,7 @@
         <v>144</v>
       </c>
       <c r="F96" s="34">
-        <v>190504</v>
+        <v>186903</v>
       </c>
       <c r="G96" s="35" t="s">
         <v>69</v>
@@ -35535,7 +35535,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="34">
-        <v>68700</v>
+        <v>68604</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>
@@ -35897,7 +35897,7 @@
         <v>12</v>
       </c>
       <c r="F3" s="34">
-        <v>286</v>
+        <v>214</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -36012,7 +36012,7 @@
         <v>18</v>
       </c>
       <c r="F8" s="34">
-        <v>1901</v>
+        <v>1865</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 10/03/2026, 12:03:30</t>
+    <t>Actualización: 10/03/2026, 13:47:22</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>
@@ -41,7 +41,7 @@
     <t>Unidades:</t>
   </si>
   <si>
-    <t>8,331,389</t>
+    <t>8,328,981</t>
   </si>
   <si>
     <t>Agotados:</t>
@@ -68,7 +68,7 @@
     <t>ACCESORIOS</t>
   </si>
   <si>
-    <t>935,445</t>
+    <t>934,276</t>
   </si>
   <si>
     <t>11.2%</t>
@@ -77,7 +77,7 @@
     <t>ARCHIVO</t>
   </si>
   <si>
-    <t>1,727,625</t>
+    <t>1,727,577</t>
   </si>
   <si>
     <t>20.7%</t>
@@ -95,7 +95,7 @@
     <t>DIDACTICOS</t>
   </si>
   <si>
-    <t>25,676</t>
+    <t>25,675</t>
   </si>
   <si>
     <t>0.3%</t>
@@ -104,7 +104,7 @@
     <t>ESCRITURA</t>
   </si>
   <si>
-    <t>1,423,835</t>
+    <t>1,423,789</t>
   </si>
   <si>
     <t>17.1%</t>
@@ -113,7 +113,7 @@
     <t>FORROS</t>
   </si>
   <si>
-    <t>834,465</t>
+    <t>833,915</t>
   </si>
   <si>
     <t>10.0%</t>
@@ -122,7 +122,7 @@
     <t>MANUALIDADES</t>
   </si>
   <si>
-    <t>425,997</t>
+    <t>425,994</t>
   </si>
   <si>
     <t>5.1%</t>
@@ -140,7 +140,7 @@
     <t>METALICA</t>
   </si>
   <si>
-    <t>244,953</t>
+    <t>244,952</t>
   </si>
   <si>
     <t>2.9%</t>
@@ -158,7 +158,7 @@
     <t>PELOTAS</t>
   </si>
   <si>
-    <t>477,389</t>
+    <t>476,866</t>
   </si>
   <si>
     <t>5.7%</t>
@@ -167,7 +167,7 @@
     <t>PINTURA</t>
   </si>
   <si>
-    <t>1,224,674</t>
+    <t>1,224,661</t>
   </si>
   <si>
     <t>14.7%</t>
@@ -176,7 +176,7 @@
     <t>REPRESENTADAS</t>
   </si>
   <si>
-    <t>313,996</t>
+    <t>313,942</t>
   </si>
   <si>
     <t>3.8%</t>
@@ -10217,13 +10217,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="6">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -10955,7 +10955,7 @@
         <v>500</v>
       </c>
       <c r="F21" s="34">
-        <v>45255</v>
+        <v>45254</v>
       </c>
       <c r="G21" s="35" t="s">
         <v>69</v>
@@ -11389,7 +11389,7 @@
         <v>144</v>
       </c>
       <c r="F8" s="34">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>
@@ -11435,7 +11435,7 @@
         <v>36</v>
       </c>
       <c r="F10" s="36">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G10" s="37" t="s">
         <v>109</v>
@@ -11800,7 +11800,7 @@
         <v>24</v>
       </c>
       <c r="F3" s="34">
-        <v>2050</v>
+        <v>2044</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -11915,7 +11915,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="34">
-        <v>5341</v>
+        <v>5335</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>
@@ -12467,7 +12467,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="34">
-        <v>3505</v>
+        <v>3504</v>
       </c>
       <c r="G32" s="35" t="s">
         <v>69</v>
@@ -12490,7 +12490,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="34">
-        <v>2922</v>
+        <v>2916</v>
       </c>
       <c r="G33" s="35" t="s">
         <v>69</v>
@@ -12605,7 +12605,7 @@
         <v>48</v>
       </c>
       <c r="F38" s="34">
-        <v>1435</v>
+        <v>1387</v>
       </c>
       <c r="G38" s="35" t="s">
         <v>69</v>
@@ -12812,7 +12812,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="34">
-        <v>11797</v>
+        <v>11773</v>
       </c>
       <c r="G47" s="35" t="s">
         <v>69</v>
@@ -12927,7 +12927,7 @@
         <v>48</v>
       </c>
       <c r="F52" s="36">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="G52" s="37" t="s">
         <v>109</v>
@@ -13410,7 +13410,7 @@
         <v>60</v>
       </c>
       <c r="F73" s="34">
-        <v>3194</v>
+        <v>3182</v>
       </c>
       <c r="G73" s="35" t="s">
         <v>69</v>
@@ -13433,7 +13433,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="34">
-        <v>1269</v>
+        <v>1245</v>
       </c>
       <c r="G74" s="35" t="s">
         <v>69</v>
@@ -13479,7 +13479,7 @@
         <v>60</v>
       </c>
       <c r="F76" s="34">
-        <v>8593</v>
+        <v>8545</v>
       </c>
       <c r="G76" s="35" t="s">
         <v>69</v>
@@ -13570,11 +13570,11 @@
       <c r="E80">
         <v>60</v>
       </c>
-      <c r="F80" s="32">
-        <v>0</v>
-      </c>
-      <c r="G80" s="33" t="s">
-        <v>65</v>
+      <c r="F80" s="36">
+        <v>72</v>
+      </c>
+      <c r="G80" s="37" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -14008,7 +14008,7 @@
         <v>60</v>
       </c>
       <c r="F99" s="34">
-        <v>3914</v>
+        <v>3854</v>
       </c>
       <c r="G99" s="35" t="s">
         <v>69</v>
@@ -14192,7 +14192,7 @@
         <v>60</v>
       </c>
       <c r="F107" s="34">
-        <v>5577</v>
+        <v>5517</v>
       </c>
       <c r="G107" s="35" t="s">
         <v>69</v>
@@ -14353,7 +14353,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="34">
-        <v>11076</v>
+        <v>11016</v>
       </c>
       <c r="G114" s="35" t="s">
         <v>69</v>
@@ -14675,7 +14675,7 @@
         <v>120</v>
       </c>
       <c r="F128" s="36">
-        <v>519</v>
+        <v>483</v>
       </c>
       <c r="G128" s="37" t="s">
         <v>109</v>
@@ -14974,7 +14974,7 @@
         <v>120</v>
       </c>
       <c r="F141" s="34">
-        <v>4217</v>
+        <v>4133</v>
       </c>
       <c r="G141" s="35" t="s">
         <v>69</v>
@@ -15457,7 +15457,7 @@
         <v>120</v>
       </c>
       <c r="F162" s="34">
-        <v>4672</v>
+        <v>4660</v>
       </c>
       <c r="G162" s="35" t="s">
         <v>69</v>
@@ -15664,7 +15664,7 @@
         <v>120</v>
       </c>
       <c r="F171" s="34">
-        <v>7702</v>
+        <v>7678</v>
       </c>
       <c r="G171" s="35" t="s">
         <v>69</v>
@@ -15687,7 +15687,7 @@
         <v>120</v>
       </c>
       <c r="F172" s="34">
-        <v>2089</v>
+        <v>2065</v>
       </c>
       <c r="G172" s="35" t="s">
         <v>69</v>
@@ -16259,7 +16259,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="34">
-        <v>2259</v>
+        <v>2307</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>69</v>
@@ -16282,7 +16282,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="34">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G6" s="35" t="s">
         <v>69</v>
@@ -16305,7 +16305,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="34">
-        <v>103185</v>
+        <v>103184</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>69</v>
@@ -16397,7 +16397,7 @@
         <v>144</v>
       </c>
       <c r="F11" s="34">
-        <v>52784</v>
+        <v>52782</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>69</v>
@@ -16535,7 +16535,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="34">
-        <v>94973</v>
+        <v>94919</v>
       </c>
       <c r="G17" s="35" t="s">
         <v>69</v>
@@ -16765,7 +16765,7 @@
         <v>60</v>
       </c>
       <c r="F27" s="34">
-        <v>71146</v>
+        <v>71144</v>
       </c>
       <c r="G27" s="35" t="s">
         <v>69</v>
@@ -17248,7 +17248,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="34">
-        <v>46936</v>
+        <v>46934</v>
       </c>
       <c r="G48" s="35" t="s">
         <v>69</v>
@@ -17271,7 +17271,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="34">
-        <v>37845</v>
+        <v>37843</v>
       </c>
       <c r="G49" s="35" t="s">
         <v>69</v>
@@ -17616,7 +17616,7 @@
         <v>12</v>
       </c>
       <c r="F64" s="36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G64" s="37" t="s">
         <v>109</v>
@@ -19752,7 +19752,7 @@
         <v>120</v>
       </c>
       <c r="F79" s="36">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="G79" s="37" t="s">
         <v>109</v>
@@ -22670,7 +22670,7 @@
         <v>144</v>
       </c>
       <c r="F8" s="34">
-        <v>17891</v>
+        <v>17890</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>
@@ -23245,7 +23245,7 @@
         <v>120</v>
       </c>
       <c r="F33" s="34">
-        <v>38192</v>
+        <v>38191</v>
       </c>
       <c r="G33" s="35" t="s">
         <v>69</v>
@@ -23268,7 +23268,7 @@
         <v>120</v>
       </c>
       <c r="F34" s="34">
-        <v>47204</v>
+        <v>46104</v>
       </c>
       <c r="G34" s="35" t="s">
         <v>69</v>
@@ -23360,7 +23360,7 @@
         <v>120</v>
       </c>
       <c r="F38" s="34">
-        <v>99906</v>
+        <v>99816</v>
       </c>
       <c r="G38" s="35" t="s">
         <v>69</v>
@@ -23636,7 +23636,7 @@
         <v>144</v>
       </c>
       <c r="F50" s="34">
-        <v>5176</v>
+        <v>5174</v>
       </c>
       <c r="G50" s="35" t="s">
         <v>69</v>
@@ -23774,7 +23774,7 @@
         <v>144</v>
       </c>
       <c r="F56" s="36">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="G56" s="37" t="s">
         <v>109</v>
@@ -23935,7 +23935,7 @@
         <v>120</v>
       </c>
       <c r="F63" s="34">
-        <v>8681</v>
+        <v>8680</v>
       </c>
       <c r="G63" s="35" t="s">
         <v>69</v>
@@ -23958,7 +23958,7 @@
         <v>120</v>
       </c>
       <c r="F64" s="34">
-        <v>6980</v>
+        <v>6979</v>
       </c>
       <c r="G64" s="35" t="s">
         <v>69</v>
@@ -24349,7 +24349,7 @@
         <v>144</v>
       </c>
       <c r="F81" s="36">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G81" s="37" t="s">
         <v>109</v>
@@ -24648,7 +24648,7 @@
         <v>144</v>
       </c>
       <c r="F94" s="36">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G94" s="37" t="s">
         <v>109</v>
@@ -25289,7 +25289,7 @@
         <v>50</v>
       </c>
       <c r="F25" s="34">
-        <v>23011</v>
+        <v>22981</v>
       </c>
       <c r="G25" s="35" t="s">
         <v>69</v>
@@ -28440,7 +28440,7 @@
         <v>24</v>
       </c>
       <c r="F162" s="34">
-        <v>1747</v>
+        <v>1735</v>
       </c>
       <c r="G162" s="35" t="s">
         <v>69</v>
@@ -28486,7 +28486,7 @@
         <v>24</v>
       </c>
       <c r="F164" s="34">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="G164" s="35" t="s">
         <v>69</v>
@@ -31723,7 +31723,7 @@
         <v>24</v>
       </c>
       <c r="F20" s="34">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="G20" s="35" t="s">
         <v>69</v>
@@ -32065,7 +32065,7 @@
         <v>144</v>
       </c>
       <c r="F2" s="34">
-        <v>73106</v>
+        <v>73105</v>
       </c>
       <c r="G2" s="35" t="s">
         <v>69</v>
@@ -32157,7 +32157,7 @@
         <v>144</v>
       </c>
       <c r="F6" s="34">
-        <v>2640</v>
+        <v>2638</v>
       </c>
       <c r="G6" s="35" t="s">
         <v>69</v>
@@ -32341,7 +32341,7 @@
         <v>96</v>
       </c>
       <c r="F14" s="34">
-        <v>9249</v>
+        <v>9248</v>
       </c>
       <c r="G14" s="35" t="s">
         <v>69</v>
@@ -32364,7 +32364,7 @@
         <v>96</v>
       </c>
       <c r="F15" s="34">
-        <v>7551</v>
+        <v>7550</v>
       </c>
       <c r="G15" s="35" t="s">
         <v>69</v>
@@ -32594,7 +32594,7 @@
         <v>48</v>
       </c>
       <c r="F25" s="34">
-        <v>3650</v>
+        <v>3647</v>
       </c>
       <c r="G25" s="35" t="s">
         <v>69</v>
@@ -33146,7 +33146,7 @@
         <v>96</v>
       </c>
       <c r="F49" s="34">
-        <v>12651</v>
+        <v>12650</v>
       </c>
       <c r="G49" s="35" t="s">
         <v>69</v>
@@ -33215,7 +33215,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="34">
-        <v>6491</v>
+        <v>6455</v>
       </c>
       <c r="G52" s="35" t="s">
         <v>69</v>
@@ -33238,7 +33238,7 @@
         <v>96</v>
       </c>
       <c r="F53" s="34">
-        <v>14009</v>
+        <v>14008</v>
       </c>
       <c r="G53" s="35" t="s">
         <v>69</v>
@@ -33261,7 +33261,7 @@
         <v>96</v>
       </c>
       <c r="F54" s="34">
-        <v>7483</v>
+        <v>7482</v>
       </c>
       <c r="G54" s="35" t="s">
         <v>69</v>
@@ -34203,11 +34203,11 @@
       <c r="E95">
         <v>120</v>
       </c>
-      <c r="F95" s="32">
-        <v>0</v>
-      </c>
-      <c r="G95" s="33" t="s">
-        <v>65</v>
+      <c r="F95" s="36">
+        <v>3</v>
+      </c>
+      <c r="G95" s="37" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -34250,7 +34250,7 @@
         <v>288</v>
       </c>
       <c r="F97" s="34">
-        <v>25656</v>
+        <v>25654</v>
       </c>
       <c r="G97" s="35" t="s">
         <v>69</v>
@@ -35397,7 +35397,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="34">
-        <v>71588</v>
+        <v>71338</v>
       </c>
       <c r="G2" s="35" t="s">
         <v>69</v>
@@ -35420,7 +35420,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="34">
-        <v>226977</v>
+        <v>226677</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -35739,7 +35739,7 @@
         <v>72</v>
       </c>
       <c r="F2" s="34">
-        <v>119312</v>
+        <v>119309</v>
       </c>
       <c r="G2" s="35" t="s">
         <v>69</v>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 10/03/2026, 13:47:22</t>
+    <t>Actualización: 10/03/2026, 14:38:06</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 10/03/2026, 14:38:06</t>
+    <t>Actualización: 10/03/2026, 15:34:38</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>
@@ -41,7 +41,7 @@
     <t>Unidades:</t>
   </si>
   <si>
-    <t>8,328,981</t>
+    <t>8,330,991</t>
   </si>
   <si>
     <t>Agotados:</t>
@@ -77,16 +77,16 @@
     <t>ARCHIVO</t>
   </si>
   <si>
-    <t>1,727,577</t>
-  </si>
-  <si>
-    <t>20.7%</t>
+    <t>1,732,787</t>
+  </si>
+  <si>
+    <t>20.8%</t>
   </si>
   <si>
     <t>DIBUJO</t>
   </si>
   <si>
-    <t>104,698</t>
+    <t>104,448</t>
   </si>
   <si>
     <t>1.3%</t>
@@ -104,7 +104,7 @@
     <t>ESCRITURA</t>
   </si>
   <si>
-    <t>1,423,789</t>
+    <t>1,423,045</t>
   </si>
   <si>
     <t>17.1%</t>
@@ -113,7 +113,7 @@
     <t>FORROS</t>
   </si>
   <si>
-    <t>833,915</t>
+    <t>833,110</t>
   </si>
   <si>
     <t>10.0%</t>
@@ -149,7 +149,7 @@
     <t>PEGAMENTOS</t>
   </si>
   <si>
-    <t>583,651</t>
+    <t>582,928</t>
   </si>
   <si>
     <t>7.0%</t>
@@ -158,7 +158,7 @@
     <t>PELOTAS</t>
   </si>
   <si>
-    <t>476,866</t>
+    <t>476,718</t>
   </si>
   <si>
     <t>5.7%</t>
@@ -167,7 +167,7 @@
     <t>PINTURA</t>
   </si>
   <si>
-    <t>1,224,661</t>
+    <t>1,224,131</t>
   </si>
   <si>
     <t>14.7%</t>
@@ -10217,13 +10217,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="6">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11481,7 +11481,7 @@
         <v>192</v>
       </c>
       <c r="F12" s="34">
-        <v>30294</v>
+        <v>30102</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>69</v>
@@ -11527,7 +11527,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="34">
-        <v>79309</v>
+        <v>78778</v>
       </c>
       <c r="G14" s="35" t="s">
         <v>69</v>
@@ -11800,7 +11800,7 @@
         <v>24</v>
       </c>
       <c r="F3" s="34">
-        <v>2044</v>
+        <v>2038</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -11915,7 +11915,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="34">
-        <v>5335</v>
+        <v>5329</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>
@@ -12282,11 +12282,11 @@
       <c r="E24">
         <v>48</v>
       </c>
-      <c r="F24" s="32">
-        <v>0</v>
-      </c>
-      <c r="G24" s="33" t="s">
-        <v>65</v>
+      <c r="F24" s="36">
+        <v>1</v>
+      </c>
+      <c r="G24" s="37" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -12305,11 +12305,11 @@
       <c r="E25">
         <v>48</v>
       </c>
-      <c r="F25" s="32">
-        <v>0</v>
-      </c>
-      <c r="G25" s="33" t="s">
-        <v>65</v>
+      <c r="F25" s="36">
+        <v>1</v>
+      </c>
+      <c r="G25" s="37" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -12490,7 +12490,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="34">
-        <v>2916</v>
+        <v>2910</v>
       </c>
       <c r="G33" s="35" t="s">
         <v>69</v>
@@ -12605,7 +12605,7 @@
         <v>48</v>
       </c>
       <c r="F38" s="34">
-        <v>1387</v>
+        <v>1375</v>
       </c>
       <c r="G38" s="35" t="s">
         <v>69</v>
@@ -12812,7 +12812,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="34">
-        <v>11773</v>
+        <v>11761</v>
       </c>
       <c r="G47" s="35" t="s">
         <v>69</v>
@@ -12927,7 +12927,7 @@
         <v>48</v>
       </c>
       <c r="F52" s="36">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G52" s="37" t="s">
         <v>109</v>
@@ -13479,7 +13479,7 @@
         <v>60</v>
       </c>
       <c r="F76" s="34">
-        <v>8545</v>
+        <v>8533</v>
       </c>
       <c r="G76" s="35" t="s">
         <v>69</v>
@@ -13571,7 +13571,7 @@
         <v>60</v>
       </c>
       <c r="F80" s="36">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="G80" s="37" t="s">
         <v>109</v>
@@ -14008,7 +14008,7 @@
         <v>60</v>
       </c>
       <c r="F99" s="34">
-        <v>3854</v>
+        <v>3842</v>
       </c>
       <c r="G99" s="35" t="s">
         <v>69</v>
@@ -14192,7 +14192,7 @@
         <v>60</v>
       </c>
       <c r="F107" s="34">
-        <v>5517</v>
+        <v>5505</v>
       </c>
       <c r="G107" s="35" t="s">
         <v>69</v>
@@ -14353,7 +14353,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="34">
-        <v>11016</v>
+        <v>11004</v>
       </c>
       <c r="G114" s="35" t="s">
         <v>69</v>
@@ -14675,7 +14675,7 @@
         <v>120</v>
       </c>
       <c r="F128" s="36">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="G128" s="37" t="s">
         <v>109</v>
@@ -14974,7 +14974,7 @@
         <v>120</v>
       </c>
       <c r="F141" s="34">
-        <v>4133</v>
+        <v>4127</v>
       </c>
       <c r="G141" s="35" t="s">
         <v>69</v>
@@ -15457,7 +15457,7 @@
         <v>120</v>
       </c>
       <c r="F162" s="34">
-        <v>4660</v>
+        <v>4648</v>
       </c>
       <c r="G162" s="35" t="s">
         <v>69</v>
@@ -15687,7 +15687,7 @@
         <v>120</v>
       </c>
       <c r="F172" s="34">
-        <v>2065</v>
+        <v>2053</v>
       </c>
       <c r="G172" s="35" t="s">
         <v>69</v>
@@ -16305,7 +16305,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="34">
-        <v>103184</v>
+        <v>102896</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>69</v>
@@ -16420,7 +16420,7 @@
         <v>144</v>
       </c>
       <c r="F12" s="34">
-        <v>14383</v>
+        <v>14243</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>69</v>
@@ -16535,7 +16535,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="34">
-        <v>94919</v>
+        <v>94853</v>
       </c>
       <c r="G17" s="35" t="s">
         <v>69</v>
@@ -17271,7 +17271,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="34">
-        <v>37843</v>
+        <v>37807</v>
       </c>
       <c r="G49" s="35" t="s">
         <v>69</v>
@@ -24852,7 +24852,7 @@
         <v>50</v>
       </c>
       <c r="F6" s="34">
-        <v>17813</v>
+        <v>17713</v>
       </c>
       <c r="G6" s="35" t="s">
         <v>69</v>
@@ -27451,7 +27451,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="34">
-        <v>17391</v>
+        <v>22791</v>
       </c>
       <c r="G119" s="35" t="s">
         <v>69</v>
@@ -28302,7 +28302,7 @@
         <v>6</v>
       </c>
       <c r="F156" s="34">
-        <v>900</v>
+        <v>870</v>
       </c>
       <c r="G156" s="35" t="s">
         <v>69</v>
@@ -28325,7 +28325,7 @@
         <v>6</v>
       </c>
       <c r="F157" s="34">
-        <v>179</v>
+        <v>119</v>
       </c>
       <c r="G157" s="35" t="s">
         <v>69</v>
@@ -31036,7 +31036,7 @@
         <v>400</v>
       </c>
       <c r="F8" s="34">
-        <v>16273</v>
+        <v>16023</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>
@@ -32088,7 +32088,7 @@
         <v>144</v>
       </c>
       <c r="F3" s="34">
-        <v>37073</v>
+        <v>36593</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -32594,7 +32594,7 @@
         <v>48</v>
       </c>
       <c r="F25" s="34">
-        <v>3647</v>
+        <v>3503</v>
       </c>
       <c r="G25" s="35" t="s">
         <v>69</v>
@@ -32617,7 +32617,7 @@
         <v>24</v>
       </c>
       <c r="F26" s="34">
-        <v>12943</v>
+        <v>12823</v>
       </c>
       <c r="G26" s="35" t="s">
         <v>69</v>
@@ -35420,7 +35420,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="34">
-        <v>226677</v>
+        <v>226077</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -35443,7 +35443,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="34">
-        <v>80312</v>
+        <v>80112</v>
       </c>
       <c r="G4" s="35" t="s">
         <v>69</v>
@@ -35535,7 +35535,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="34">
-        <v>68604</v>
+        <v>68599</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 10/03/2026, 16:48:18</t>
+    <t>Actualización: 10/03/2026, 17:28:56</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>
@@ -41,7 +41,7 @@
     <t>Unidades:</t>
   </si>
   <si>
-    <t>8,325,829</t>
+    <t>8,321,074</t>
   </si>
   <si>
     <t>Agotados:</t>
@@ -68,7 +68,7 @@
     <t>ACCESORIOS</t>
   </si>
   <si>
-    <t>934,154</t>
+    <t>932,927</t>
   </si>
   <si>
     <t>11.2%</t>
@@ -77,7 +77,7 @@
     <t>ARCHIVO</t>
   </si>
   <si>
-    <t>1,732,783</t>
+    <t>1,733,467</t>
   </si>
   <si>
     <t>20.8%</t>
@@ -86,7 +86,7 @@
     <t>DIBUJO</t>
   </si>
   <si>
-    <t>104,448</t>
+    <t>104,146</t>
   </si>
   <si>
     <t>1.3%</t>
@@ -104,7 +104,7 @@
     <t>ESCRITURA</t>
   </si>
   <si>
-    <t>1,421,844</t>
+    <t>1,421,068</t>
   </si>
   <si>
     <t>17.1%</t>
@@ -113,7 +113,7 @@
     <t>FORROS</t>
   </si>
   <si>
-    <t>832,410</t>
+    <t>831,305</t>
   </si>
   <si>
     <t>10.0%</t>
@@ -122,7 +122,7 @@
     <t>MANUALIDADES</t>
   </si>
   <si>
-    <t>425,993</t>
+    <t>425,848</t>
   </si>
   <si>
     <t>5.1%</t>
@@ -140,7 +140,7 @@
     <t>METALICA</t>
   </si>
   <si>
-    <t>244,752</t>
+    <t>244,352</t>
   </si>
   <si>
     <t>2.9%</t>
@@ -149,7 +149,7 @@
     <t>PEGAMENTOS</t>
   </si>
   <si>
-    <t>582,042</t>
+    <t>582,041</t>
   </si>
   <si>
     <t>7.0%</t>
@@ -158,7 +158,7 @@
     <t>PELOTAS</t>
   </si>
   <si>
-    <t>476,362</t>
+    <t>476,074</t>
   </si>
   <si>
     <t>5.7%</t>
@@ -167,7 +167,7 @@
     <t>PINTURA</t>
   </si>
   <si>
-    <t>1,223,313</t>
+    <t>1,222,122</t>
   </si>
   <si>
     <t>14.7%</t>
@@ -176,7 +176,7 @@
     <t>REPRESENTADAS</t>
   </si>
   <si>
-    <t>313,068</t>
+    <t>313,064</t>
   </si>
   <si>
     <t>3.8%</t>
@@ -10217,13 +10217,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="6">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="7">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -10817,7 +10817,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="34">
-        <v>38769</v>
+        <v>38369</v>
       </c>
       <c r="G15" s="35" t="s">
         <v>69</v>
@@ -11389,7 +11389,7 @@
         <v>144</v>
       </c>
       <c r="F8" s="34">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>
@@ -11800,7 +11800,7 @@
         <v>24</v>
       </c>
       <c r="F3" s="34">
-        <v>2032</v>
+        <v>2029</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -11915,7 +11915,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="34">
-        <v>5323</v>
+        <v>5320</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>
@@ -11961,7 +11961,7 @@
         <v>24</v>
       </c>
       <c r="F10" s="34">
-        <v>1495</v>
+        <v>1492</v>
       </c>
       <c r="G10" s="35" t="s">
         <v>69</v>
@@ -12007,7 +12007,7 @@
         <v>24</v>
       </c>
       <c r="F12" s="34">
-        <v>1425</v>
+        <v>1422</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>69</v>
@@ -12467,7 +12467,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="34">
-        <v>3504</v>
+        <v>3498</v>
       </c>
       <c r="G32" s="35" t="s">
         <v>69</v>
@@ -12490,7 +12490,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="34">
-        <v>2904</v>
+        <v>2901</v>
       </c>
       <c r="G33" s="35" t="s">
         <v>69</v>
@@ -12605,7 +12605,7 @@
         <v>48</v>
       </c>
       <c r="F38" s="34">
-        <v>1363</v>
+        <v>1351</v>
       </c>
       <c r="G38" s="35" t="s">
         <v>69</v>
@@ -12812,7 +12812,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="34">
-        <v>11737</v>
+        <v>11731</v>
       </c>
       <c r="G47" s="35" t="s">
         <v>69</v>
@@ -12881,7 +12881,7 @@
         <v>48</v>
       </c>
       <c r="F50" s="34">
-        <v>5474</v>
+        <v>5468</v>
       </c>
       <c r="G50" s="35" t="s">
         <v>69</v>
@@ -13042,7 +13042,7 @@
         <v>36</v>
       </c>
       <c r="F57" s="34">
-        <v>2190</v>
+        <v>2181</v>
       </c>
       <c r="G57" s="35" t="s">
         <v>69</v>
@@ -13410,7 +13410,7 @@
         <v>60</v>
       </c>
       <c r="F73" s="34">
-        <v>3170</v>
+        <v>3152</v>
       </c>
       <c r="G73" s="35" t="s">
         <v>69</v>
@@ -13433,7 +13433,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="34">
-        <v>1221</v>
+        <v>1203</v>
       </c>
       <c r="G74" s="35" t="s">
         <v>69</v>
@@ -13479,7 +13479,7 @@
         <v>60</v>
       </c>
       <c r="F76" s="34">
-        <v>8509</v>
+        <v>8491</v>
       </c>
       <c r="G76" s="35" t="s">
         <v>69</v>
@@ -13571,7 +13571,7 @@
         <v>60</v>
       </c>
       <c r="F80" s="36">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="G80" s="37" t="s">
         <v>109</v>
@@ -14031,7 +14031,7 @@
         <v>60</v>
       </c>
       <c r="F100" s="34">
-        <v>1513</v>
+        <v>1495</v>
       </c>
       <c r="G100" s="35" t="s">
         <v>69</v>
@@ -14353,7 +14353,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="34">
-        <v>10980</v>
+        <v>10968</v>
       </c>
       <c r="G114" s="35" t="s">
         <v>69</v>
@@ -14583,7 +14583,7 @@
         <v>12</v>
       </c>
       <c r="F124" s="34">
-        <v>2508</v>
+        <v>2460</v>
       </c>
       <c r="G124" s="35" t="s">
         <v>69</v>
@@ -14675,7 +14675,7 @@
         <v>120</v>
       </c>
       <c r="F128" s="36">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="G128" s="37" t="s">
         <v>109</v>
@@ -15181,7 +15181,7 @@
         <v>120</v>
       </c>
       <c r="F150" s="36">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="G150" s="37" t="s">
         <v>109</v>
@@ -15204,7 +15204,7 @@
         <v>120</v>
       </c>
       <c r="F151" s="34">
-        <v>2007</v>
+        <v>1995</v>
       </c>
       <c r="G151" s="35" t="s">
         <v>69</v>
@@ -15273,7 +15273,7 @@
         <v>120</v>
       </c>
       <c r="F154" s="34">
-        <v>3277</v>
+        <v>3265</v>
       </c>
       <c r="G154" s="35" t="s">
         <v>69</v>
@@ -15410,11 +15410,11 @@
       <c r="E160">
         <v>120</v>
       </c>
-      <c r="F160" s="36">
-        <v>6</v>
-      </c>
-      <c r="G160" s="37" t="s">
-        <v>109</v>
+      <c r="F160" s="32">
+        <v>0</v>
+      </c>
+      <c r="G160" s="33" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -15434,7 +15434,7 @@
         <v>120</v>
       </c>
       <c r="F161" s="34">
-        <v>1926</v>
+        <v>1914</v>
       </c>
       <c r="G161" s="35" t="s">
         <v>69</v>
@@ -15664,7 +15664,7 @@
         <v>120</v>
       </c>
       <c r="F171" s="34">
-        <v>7666</v>
+        <v>7654</v>
       </c>
       <c r="G171" s="35" t="s">
         <v>69</v>
@@ -15733,7 +15733,7 @@
         <v>1</v>
       </c>
       <c r="F174" s="34">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="G174" s="35" t="s">
         <v>69</v>
@@ -16305,7 +16305,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="34">
-        <v>102896</v>
+        <v>102895</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>69</v>
@@ -16420,7 +16420,7 @@
         <v>144</v>
       </c>
       <c r="F12" s="34">
-        <v>13881</v>
+        <v>13737</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>69</v>
@@ -16535,7 +16535,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="34">
-        <v>94832</v>
+        <v>94831</v>
       </c>
       <c r="G17" s="35" t="s">
         <v>69</v>
@@ -16558,7 +16558,7 @@
         <v>72</v>
       </c>
       <c r="F18" s="34">
-        <v>6427</v>
+        <v>6403</v>
       </c>
       <c r="G18" s="35" t="s">
         <v>69</v>
@@ -16765,7 +16765,7 @@
         <v>60</v>
       </c>
       <c r="F27" s="34">
-        <v>71144</v>
+        <v>70724</v>
       </c>
       <c r="G27" s="35" t="s">
         <v>69</v>
@@ -16926,7 +16926,7 @@
         <v>576</v>
       </c>
       <c r="F34" s="34">
-        <v>48805</v>
+        <v>48565</v>
       </c>
       <c r="G34" s="35" t="s">
         <v>69</v>
@@ -17064,7 +17064,7 @@
         <v>576</v>
       </c>
       <c r="F40" s="34">
-        <v>40056</v>
+        <v>39816</v>
       </c>
       <c r="G40" s="35" t="s">
         <v>69</v>
@@ -17156,7 +17156,7 @@
         <v>576</v>
       </c>
       <c r="F44" s="36">
-        <v>125</v>
+        <v>5</v>
       </c>
       <c r="G44" s="37" t="s">
         <v>109</v>
@@ -17271,7 +17271,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="34">
-        <v>37374</v>
+        <v>37373</v>
       </c>
       <c r="G49" s="35" t="s">
         <v>69</v>
@@ -18096,7 +18096,7 @@
         <v>120</v>
       </c>
       <c r="F7" s="34">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>69</v>
@@ -22555,7 +22555,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="34">
-        <v>2703</v>
+        <v>2653</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -22946,7 +22946,7 @@
         <v>36</v>
       </c>
       <c r="F20" s="34">
-        <v>5348</v>
+        <v>5312</v>
       </c>
       <c r="G20" s="35" t="s">
         <v>69</v>
@@ -23084,7 +23084,7 @@
         <v>36</v>
       </c>
       <c r="F26" s="34">
-        <v>5313</v>
+        <v>5277</v>
       </c>
       <c r="G26" s="35" t="s">
         <v>69</v>
@@ -23199,7 +23199,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="34">
-        <v>137620</v>
+        <v>137044</v>
       </c>
       <c r="G31" s="35" t="s">
         <v>69</v>
@@ -23245,7 +23245,7 @@
         <v>120</v>
       </c>
       <c r="F33" s="34">
-        <v>38071</v>
+        <v>37830</v>
       </c>
       <c r="G33" s="35" t="s">
         <v>69</v>
@@ -23406,7 +23406,7 @@
         <v>120</v>
       </c>
       <c r="F40" s="34">
-        <v>888</v>
+        <v>768</v>
       </c>
       <c r="G40" s="35" t="s">
         <v>69</v>
@@ -23429,7 +23429,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="34">
-        <v>6170</v>
+        <v>6134</v>
       </c>
       <c r="G41" s="35" t="s">
         <v>69</v>
@@ -23682,7 +23682,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="34">
-        <v>5734</v>
+        <v>5698</v>
       </c>
       <c r="G52" s="35" t="s">
         <v>69</v>
@@ -23889,7 +23889,7 @@
         <v>96</v>
       </c>
       <c r="F61" s="34">
-        <v>3053</v>
+        <v>2957</v>
       </c>
       <c r="G61" s="35" t="s">
         <v>69</v>
@@ -24829,7 +24829,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="34">
-        <v>15604</v>
+        <v>15454</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>69</v>
@@ -25266,7 +25266,7 @@
         <v>50</v>
       </c>
       <c r="F24" s="34">
-        <v>47692</v>
+        <v>49492</v>
       </c>
       <c r="G24" s="35" t="s">
         <v>69</v>
@@ -25289,7 +25289,7 @@
         <v>50</v>
       </c>
       <c r="F25" s="34">
-        <v>22981</v>
+        <v>22731</v>
       </c>
       <c r="G25" s="35" t="s">
         <v>69</v>
@@ -25312,7 +25312,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="34">
-        <v>8903</v>
+        <v>8803</v>
       </c>
       <c r="G26" s="35" t="s">
         <v>69</v>
@@ -25335,7 +25335,7 @@
         <v>50</v>
       </c>
       <c r="F27" s="34">
-        <v>6190</v>
+        <v>6090</v>
       </c>
       <c r="G27" s="35" t="s">
         <v>69</v>
@@ -25358,7 +25358,7 @@
         <v>50</v>
       </c>
       <c r="F28" s="34">
-        <v>23250</v>
+        <v>23249</v>
       </c>
       <c r="G28" s="35" t="s">
         <v>69</v>
@@ -25404,7 +25404,7 @@
         <v>50</v>
       </c>
       <c r="F30" s="34">
-        <v>9625</v>
+        <v>9525</v>
       </c>
       <c r="G30" s="35" t="s">
         <v>69</v>
@@ -25427,7 +25427,7 @@
         <v>50</v>
       </c>
       <c r="F31" s="34">
-        <v>1199</v>
+        <v>1149</v>
       </c>
       <c r="G31" s="35" t="s">
         <v>69</v>
@@ -25450,7 +25450,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="34">
-        <v>5477</v>
+        <v>5427</v>
       </c>
       <c r="G32" s="35" t="s">
         <v>69</v>
@@ -25496,7 +25496,7 @@
         <v>50</v>
       </c>
       <c r="F34" s="34">
-        <v>8399</v>
+        <v>8299</v>
       </c>
       <c r="G34" s="35" t="s">
         <v>69</v>
@@ -25519,7 +25519,7 @@
         <v>50</v>
       </c>
       <c r="F35" s="34">
-        <v>18661</v>
+        <v>18611</v>
       </c>
       <c r="G35" s="35" t="s">
         <v>69</v>
@@ -25588,7 +25588,7 @@
         <v>50</v>
       </c>
       <c r="F38" s="34">
-        <v>4261</v>
+        <v>4260</v>
       </c>
       <c r="G38" s="35" t="s">
         <v>69</v>
@@ -25611,7 +25611,7 @@
         <v>50</v>
       </c>
       <c r="F39" s="34">
-        <v>2722</v>
+        <v>2622</v>
       </c>
       <c r="G39" s="35" t="s">
         <v>69</v>
@@ -27634,11 +27634,11 @@
       <c r="E127">
         <v>24</v>
       </c>
-      <c r="F127" s="36">
-        <v>56</v>
-      </c>
-      <c r="G127" s="37" t="s">
-        <v>109</v>
+      <c r="F127" s="34">
+        <v>176</v>
+      </c>
+      <c r="G127" s="35" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -28164,7 +28164,7 @@
         <v>12</v>
       </c>
       <c r="F150" s="34">
-        <v>2559</v>
+        <v>2675</v>
       </c>
       <c r="G150" s="35" t="s">
         <v>69</v>
@@ -30579,7 +30579,7 @@
         <v>100</v>
       </c>
       <c r="F255" s="34">
-        <v>211487</v>
+        <v>211187</v>
       </c>
       <c r="G255" s="35" t="s">
         <v>69</v>
@@ -30967,7 +30967,7 @@
         <v>500</v>
       </c>
       <c r="F5" s="34">
-        <v>10493</v>
+        <v>10492</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>69</v>
@@ -31059,7 +31059,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="34">
-        <v>33522</v>
+        <v>33221</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>69</v>
@@ -33537,7 +33537,7 @@
         <v>200</v>
       </c>
       <c r="F66" s="34">
-        <v>5657</v>
+        <v>5457</v>
       </c>
       <c r="G66" s="35" t="s">
         <v>69</v>
@@ -34158,7 +34158,7 @@
         <v>576</v>
       </c>
       <c r="F93" s="34">
-        <v>14231</v>
+        <v>13655</v>
       </c>
       <c r="G93" s="35" t="s">
         <v>69</v>
@@ -35443,7 +35443,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="34">
-        <v>80112</v>
+        <v>79612</v>
       </c>
       <c r="G4" s="35" t="s">
         <v>69</v>
@@ -35535,7 +35535,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="34">
-        <v>68599</v>
+        <v>68359</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>
@@ -35558,7 +35558,7 @@
         <v>48</v>
       </c>
       <c r="F9" s="34">
-        <v>83665</v>
+        <v>83425</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>69</v>
@@ -35627,7 +35627,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="34">
-        <v>15378</v>
+        <v>15253</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>69</v>
@@ -35762,7 +35762,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="34">
-        <v>206681</v>
+        <v>206536</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
